--- a/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
@@ -68,7 +68,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,11 +78,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,17 +132,14 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -620,7 +612,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2358.65</v>
+        <v>2097.5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>46320</v>
@@ -638,7 +630,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>9577.99</v>
+        <v>9960.01</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>46307</v>
@@ -1102,7 +1094,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>-6739.96</v>
+        <v>-6172.62</v>
       </c>
     </row>
     <row r="46">
@@ -1112,7 +1104,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>-0</v>
+        <v>-185.32</v>
       </c>
     </row>
     <row r="47">
@@ -1207,7 +1199,7 @@
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>-2044.59</v>
+        <v>-2305.74</v>
       </c>
     </row>
     <row r="59">
@@ -1255,7 +1247,7 @@
         </is>
       </c>
       <c r="B64" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -1275,17 +1267,17 @@
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Divergências ALTA</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
-        <v>5</v>
+      <c r="B67" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1295,7 +1287,7 @@
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -7280,7 +7272,11 @@
       <c r="N11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="5" t="n"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P11" s="5" t="n">
         <v>0</v>
       </c>
@@ -7337,7 +7333,11 @@
       <c r="N12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="5" t="n"/>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P12" s="5" t="n">
         <v>0</v>
       </c>
@@ -7394,7 +7394,11 @@
       <c r="N13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="5" t="n"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P13" s="5" t="n">
         <v>0</v>
       </c>
@@ -7646,7 +7650,11 @@
       <c r="N17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="5" t="n"/>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P17" s="5" t="n">
         <v>0</v>
       </c>
@@ -8028,7 +8036,11 @@
       <c r="N23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="5" t="n"/>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P23" s="5" t="n">
         <v>0</v>
       </c>
@@ -8215,7 +8227,11 @@
       <c r="N26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="5" t="n"/>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P26" s="5" t="n">
         <v>0</v>
       </c>
@@ -9182,7 +9198,11 @@
       <c r="N41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="5" t="n"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P41" s="5" t="n">
         <v>0</v>
       </c>
@@ -11059,7 +11079,11 @@
       <c r="N70" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O70" s="5" t="n"/>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P70" s="5" t="n">
         <v>0</v>
       </c>
@@ -11311,7 +11335,11 @@
       <c r="N74" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O74" s="5" t="n"/>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P74" s="5" t="n">
         <v>0</v>
       </c>
@@ -11563,7 +11591,11 @@
       <c r="N78" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="5" t="n"/>
+      <c r="O78" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P78" s="5" t="n">
         <v>0</v>
       </c>
@@ -11620,7 +11652,11 @@
       <c r="N79" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O79" s="5" t="n"/>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P79" s="5" t="n">
         <v>0</v>
       </c>
@@ -11677,7 +11713,11 @@
       <c r="N80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O80" s="5" t="n"/>
+      <c r="O80" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P80" s="5" t="n">
         <v>0</v>
       </c>
@@ -12124,7 +12164,11 @@
       <c r="N87" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="5" t="n"/>
+      <c r="O87" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P87" s="5" t="n">
         <v>0</v>
       </c>
@@ -13018,7 +13062,11 @@
       <c r="N101" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O101" s="5" t="n"/>
+      <c r="O101" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P101" s="5" t="n">
         <v>0</v>
       </c>
@@ -13075,7 +13123,11 @@
       <c r="N102" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O102" s="5" t="n"/>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P102" s="5" t="n">
         <v>0</v>
       </c>
@@ -13522,7 +13574,11 @@
       <c r="N109" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O109" s="5" t="n"/>
+      <c r="O109" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P109" s="5" t="n">
         <v>0</v>
       </c>
@@ -16492,7 +16548,11 @@
       <c r="N155" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O155" s="5" t="n"/>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P155" s="5" t="n">
         <v>0</v>
       </c>
@@ -16614,7 +16674,11 @@
       <c r="N157" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O157" s="5" t="n"/>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P157" s="5" t="n">
         <v>0</v>
       </c>
@@ -16671,7 +16735,11 @@
       <c r="N158" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O158" s="5" t="n"/>
+      <c r="O158" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P158" s="5" t="n">
         <v>0</v>
       </c>
@@ -16728,7 +16796,11 @@
       <c r="N159" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O159" s="5" t="n"/>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P159" s="5" t="n">
         <v>0</v>
       </c>
@@ -16915,7 +16987,11 @@
       <c r="N162" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O162" s="5" t="n"/>
+      <c r="O162" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P162" s="5" t="n">
         <v>0</v>
       </c>
@@ -16972,7 +17048,11 @@
       <c r="N163" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O163" s="5" t="n"/>
+      <c r="O163" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P163" s="5" t="n">
         <v>0</v>
       </c>
@@ -17029,7 +17109,11 @@
       <c r="N164" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O164" s="5" t="n"/>
+      <c r="O164" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P164" s="5" t="n">
         <v>0</v>
       </c>
@@ -17151,7 +17235,11 @@
       <c r="N166" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O166" s="5" t="n"/>
+      <c r="O166" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P166" s="5" t="n">
         <v>0</v>
       </c>
@@ -17273,7 +17361,11 @@
       <c r="N168" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O168" s="5" t="n"/>
+      <c r="O168" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P168" s="5" t="n">
         <v>0</v>
       </c>
@@ -17460,7 +17552,11 @@
       <c r="N171" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O171" s="5" t="n"/>
+      <c r="O171" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P171" s="5" t="n">
         <v>0</v>
       </c>
@@ -17517,7 +17613,11 @@
       <c r="N172" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O172" s="5" t="n"/>
+      <c r="O172" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P172" s="5" t="n">
         <v>0</v>
       </c>
@@ -17899,7 +17999,11 @@
       <c r="N178" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O178" s="5" t="n"/>
+      <c r="O178" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P178" s="5" t="n">
         <v>0</v>
       </c>
@@ -18021,7 +18125,11 @@
       <c r="N180" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O180" s="5" t="n"/>
+      <c r="O180" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P180" s="5" t="n">
         <v>0</v>
       </c>
@@ -18078,7 +18186,11 @@
       <c r="N181" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O181" s="5" t="n"/>
+      <c r="O181" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P181" s="5" t="n">
         <v>0</v>
       </c>
@@ -18200,7 +18312,11 @@
       <c r="N183" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O183" s="5" t="n"/>
+      <c r="O183" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P183" s="5" t="n">
         <v>0</v>
       </c>
@@ -18582,7 +18698,11 @@
       <c r="N189" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O189" s="5" t="n"/>
+      <c r="O189" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P189" s="5" t="n">
         <v>0</v>
       </c>
@@ -18899,7 +19019,11 @@
       <c r="N194" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O194" s="5" t="n"/>
+      <c r="O194" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P194" s="5" t="n">
         <v>0</v>
       </c>
@@ -20776,7 +20900,11 @@
       <c r="N223" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O223" s="5" t="n"/>
+      <c r="O223" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P223" s="5" t="n">
         <v>0</v>
       </c>
@@ -21353,7 +21481,11 @@
       <c r="N232" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O232" s="5" t="n"/>
+      <c r="O232" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P232" s="5" t="n">
         <v>0</v>
       </c>
@@ -24140,7 +24272,11 @@
       <c r="N275" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O275" s="5" t="n"/>
+      <c r="O275" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P275" s="5" t="n">
         <v>0</v>
       </c>
@@ -24197,7 +24333,11 @@
       <c r="N276" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O276" s="5" t="n"/>
+      <c r="O276" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P276" s="5" t="n">
         <v>0</v>
       </c>
@@ -24384,7 +24524,11 @@
       <c r="N279" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O279" s="5" t="n"/>
+      <c r="O279" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P279" s="5" t="n">
         <v>0</v>
       </c>
@@ -24506,7 +24650,11 @@
       <c r="N281" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O281" s="5" t="n"/>
+      <c r="O281" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P281" s="5" t="n">
         <v>0</v>
       </c>
@@ -24693,7 +24841,11 @@
       <c r="N284" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O284" s="5" t="n"/>
+      <c r="O284" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P284" s="5" t="n">
         <v>0</v>
       </c>
@@ -24750,7 +24902,11 @@
       <c r="N285" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O285" s="5" t="n"/>
+      <c r="O285" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P285" s="5" t="n">
         <v>0</v>
       </c>
@@ -24807,7 +24963,11 @@
       <c r="N286" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O286" s="5" t="n"/>
+      <c r="O286" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P286" s="5" t="n">
         <v>0</v>
       </c>
@@ -24994,7 +25154,11 @@
       <c r="N289" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O289" s="5" t="n"/>
+      <c r="O289" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P289" s="5" t="n">
         <v>0</v>
       </c>
@@ -25376,7 +25540,11 @@
       <c r="N295" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O295" s="5" t="n"/>
+      <c r="O295" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P295" s="5" t="n">
         <v>0</v>
       </c>
@@ -25433,7 +25601,11 @@
       <c r="N296" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O296" s="5" t="n"/>
+      <c r="O296" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P296" s="5" t="n">
         <v>0</v>
       </c>
@@ -25620,7 +25792,11 @@
       <c r="N299" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O299" s="5" t="n"/>
+      <c r="O299" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P299" s="5" t="n">
         <v>0</v>
       </c>
@@ -25677,7 +25853,11 @@
       <c r="N300" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O300" s="5" t="n"/>
+      <c r="O300" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P300" s="5" t="n">
         <v>0</v>
       </c>
@@ -25734,7 +25914,11 @@
       <c r="N301" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O301" s="5" t="n"/>
+      <c r="O301" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P301" s="5" t="n">
         <v>0</v>
       </c>
@@ -25791,7 +25975,11 @@
       <c r="N302" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O302" s="5" t="n"/>
+      <c r="O302" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P302" s="5" t="n">
         <v>0</v>
       </c>
@@ -26303,7 +26491,11 @@
       <c r="N310" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O310" s="5" t="n"/>
+      <c r="O310" s="5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P310" s="5" t="n">
         <v>0</v>
       </c>
@@ -26355,7 +26547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coluna "Regra": aprendido = mesma classificação do SPED anterior; regra padrão = fornecedor novo (confirmar). Preencha as colunas amarelas se discordar.</t>
+          <t>Coluna "Regra": natureza do item e de onde veio (SPED anterior, NCM ou CFOP). Laranja = sem histórico, conferir. Detalhe completo na planilha de créditos.</t>
         </is>
       </c>
     </row>
@@ -26447,67 +26639,67 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="12" t="n">
         <v>46266</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>04993269000177</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="13" t="n">
         <v>41731</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>ALCOOL ETILICO 99 - ONU 1170 ETANOL (ALCOOL ETILICO) 3 GE II BOMBONA DIPANOL 99</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>22071010</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="14" t="n">
         <v>1870</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="14" t="n">
         <v>224.41</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="14" t="n">
         <v>224.41</v>
       </c>
-      <c r="M5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P5" s="17" t="inlineStr"/>
-      <c r="Q5" s="17" t="inlineStr"/>
+      <c r="M5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (álcool etílico) [NCM 22071010]</t>
+        </is>
+      </c>
+      <c r="P5" s="15" t="inlineStr"/>
+      <c r="Q5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -26556,7 +26748,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>0</v>
@@ -26566,11 +26758,11 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P6" s="17" t="inlineStr"/>
-      <c r="Q6" s="17" t="inlineStr"/>
+          <t>Embalagem (rótulo adesivo) [NCM 39191090]</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr"/>
+      <c r="Q6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -26619,7 +26811,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0</v>
+        <v>20.59</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>0</v>
@@ -26629,137 +26821,137 @@
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P7" s="17" t="inlineStr"/>
-      <c r="Q7" s="17" t="inlineStr"/>
+          <t>Embalagem (rótulo adesivo) [NCM 39191090]</t>
+        </is>
+      </c>
+      <c r="P7" s="15" t="inlineStr"/>
+      <c r="Q7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="13" t="n">
         <v>22837</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>SULFITO DE SODIO ANIDRO PA 1000G - CARBON</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>28321010</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="L8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P8" s="17" t="inlineStr"/>
-      <c r="Q8" s="17" t="inlineStr"/>
+      <c r="L8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (químico inorgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr"/>
+      <c r="Q8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="13" t="n">
         <v>22837</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>PIROFOSFATO DE SODIO (TETRABASICO) DECAHIDRATADO PA 1000G - CARBON</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>28353920</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P9" s="17" t="inlineStr"/>
-      <c r="Q9" s="17" t="inlineStr"/>
+      <c r="L9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (químico inorgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
+        </is>
+      </c>
+      <c r="P9" s="15" t="inlineStr"/>
+      <c r="Q9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -26798,7 +26990,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="J10" s="6" t="n">
@@ -26818,515 +27010,515 @@
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P10" s="17" t="inlineStr"/>
-      <c r="Q10" s="17" t="inlineStr"/>
+          <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
+        </is>
+      </c>
+      <c r="P10" s="15" t="inlineStr"/>
+      <c r="Q10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Agar Triptico de soja (TSA) pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="n">
         <v>250.39</v>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K11" s="14" t="n">
         <v>48.83</v>
       </c>
-      <c r="L11" s="16" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="M11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P11" s="17" t="inlineStr"/>
-      <c r="Q11" s="17" t="inlineStr"/>
+      <c r="L11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P11" s="15" t="inlineStr"/>
+      <c r="Q11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Agar Sabouraud Dextrose pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="n">
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="n">
         <v>222.56</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="14" t="n">
         <v>43.4</v>
       </c>
-      <c r="L12" s="16" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="inlineStr"/>
-      <c r="Q12" s="17" t="inlineStr"/>
+      <c r="L12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P12" s="15" t="inlineStr"/>
+      <c r="Q12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Agar PCA pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="n">
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="n">
         <v>35.06</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="14" t="n">
         <v>6.84</v>
       </c>
-      <c r="L13" s="16" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="M13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P13" s="17" t="inlineStr"/>
-      <c r="Q13" s="17" t="inlineStr"/>
+      <c r="L13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P13" s="15" t="inlineStr"/>
+      <c r="Q13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Agar Mac Conkey pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="n">
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="n">
         <v>35.15</v>
       </c>
-      <c r="K14" s="16" t="n">
+      <c r="K14" s="14" t="n">
         <v>6.85</v>
       </c>
-      <c r="L14" s="16" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P14" s="17" t="inlineStr"/>
-      <c r="Q14" s="17" t="inlineStr"/>
+      <c r="L14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P14" s="15" t="inlineStr"/>
+      <c r="Q14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Agar Cetrimide pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="n">
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="n">
         <v>226.01</v>
       </c>
-      <c r="K15" s="16" t="n">
+      <c r="K15" s="14" t="n">
         <v>44.07</v>
       </c>
-      <c r="L15" s="16" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P15" s="17" t="inlineStr"/>
-      <c r="Q15" s="17" t="inlineStr"/>
+      <c r="L15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P15" s="15" t="inlineStr"/>
+      <c r="Q15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Agar Baird Parker pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="n">
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="n">
         <v>317.89</v>
       </c>
-      <c r="K16" s="16" t="n">
+      <c r="K16" s="14" t="n">
         <v>61.99</v>
       </c>
-      <c r="L16" s="16" t="n">
-        <v>61.99</v>
-      </c>
-      <c r="M16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P16" s="17" t="inlineStr"/>
-      <c r="Q16" s="17" t="inlineStr"/>
+      <c r="L16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P16" s="15" t="inlineStr"/>
+      <c r="Q16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Acquaplus I sachê c/ 10 testes</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="n">
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="n">
         <v>915.08</v>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="14" t="n">
         <v>178.44</v>
       </c>
-      <c r="L17" s="16" t="n">
-        <v>178.44</v>
-      </c>
-      <c r="M17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P17" s="17" t="inlineStr"/>
-      <c r="Q17" s="17" t="inlineStr"/>
+      <c r="L17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P17" s="15" t="inlineStr"/>
+      <c r="Q17" s="15" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="12" t="n">
         <v>46267</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="13" t="n">
         <v>160326</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Caldo BHI cx c/ 10 tubos</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="n">
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="n">
         <v>246.51</v>
       </c>
-      <c r="K18" s="16" t="n">
+      <c r="K18" s="14" t="n">
         <v>48.07</v>
       </c>
-      <c r="L18" s="16" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="M18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P18" s="17" t="inlineStr"/>
-      <c r="Q18" s="17" t="inlineStr"/>
+      <c r="L18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="inlineStr"/>
+      <c r="Q18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -27365,7 +27557,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
@@ -27385,11 +27577,11 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P19" s="17" t="inlineStr"/>
-      <c r="Q19" s="17" t="inlineStr"/>
+          <t>Matéria-prima (químico orgânico) [NCM 29221100]</t>
+        </is>
+      </c>
+      <c r="P19" s="15" t="inlineStr"/>
+      <c r="Q19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -27428,7 +27620,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
@@ -27448,11 +27640,11 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P20" s="17" t="inlineStr"/>
-      <c r="Q20" s="17" t="inlineStr"/>
+          <t>Uso e consumo (peça de manutenção) [NCM 85334099]</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="inlineStr"/>
+      <c r="Q20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -27491,7 +27683,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J21" s="6" t="n">
@@ -27511,11 +27703,11 @@
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P21" s="17" t="inlineStr"/>
-      <c r="Q21" s="17" t="inlineStr"/>
+          <t>Uso e consumo (peça de manutenção) [NCM 85334099]</t>
+        </is>
+      </c>
+      <c r="P21" s="15" t="inlineStr"/>
+      <c r="Q21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -27574,11 +27766,11 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P22" s="17" t="inlineStr"/>
-      <c r="Q22" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P22" s="15" t="inlineStr"/>
+      <c r="Q22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -27637,11 +27829,11 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P23" s="17" t="inlineStr"/>
-      <c r="Q23" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P23" s="15" t="inlineStr"/>
+      <c r="Q23" s="15" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -27700,11 +27892,11 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P24" s="17" t="inlineStr"/>
-      <c r="Q24" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P24" s="15" t="inlineStr"/>
+      <c r="Q24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -27763,11 +27955,11 @@
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P25" s="17" t="inlineStr"/>
-      <c r="Q25" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P25" s="15" t="inlineStr"/>
+      <c r="Q25" s="15" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -27826,11 +28018,11 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P26" s="17" t="inlineStr"/>
-      <c r="Q26" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P26" s="15" t="inlineStr"/>
+      <c r="Q26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -27889,11 +28081,11 @@
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P27" s="17" t="inlineStr"/>
-      <c r="Q27" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P27" s="15" t="inlineStr"/>
+      <c r="Q27" s="15" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -27932,7 +28124,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
@@ -27952,11 +28144,11 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P28" s="17" t="inlineStr"/>
-      <c r="Q28" s="17" t="inlineStr"/>
+          <t>Uso e consumo (luva/artigo plástico) [NCM 39262000]</t>
+        </is>
+      </c>
+      <c r="P28" s="15" t="inlineStr"/>
+      <c r="Q28" s="15" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -27995,7 +28187,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
@@ -28015,11 +28207,11 @@
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P29" s="17" t="inlineStr"/>
-      <c r="Q29" s="17" t="inlineStr"/>
+          <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
+        </is>
+      </c>
+      <c r="P29" s="15" t="inlineStr"/>
+      <c r="Q29" s="15" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -28078,11 +28270,11 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P30" s="17" t="inlineStr"/>
-      <c r="Q30" s="17" t="inlineStr"/>
+          <t>Uso e consumo (pincel) - mas CFOP 6949 (outras saídas: amostra/brinde/remessa) [CFOP 6949]</t>
+        </is>
+      </c>
+      <c r="P30" s="15" t="inlineStr"/>
+      <c r="Q30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -28141,11 +28333,11 @@
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P31" s="17" t="inlineStr"/>
-      <c r="Q31" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
+        </is>
+      </c>
+      <c r="P31" s="15" t="inlineStr"/>
+      <c r="Q31" s="15" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -28204,11 +28396,11 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P32" s="17" t="inlineStr"/>
-      <c r="Q32" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P32" s="15" t="inlineStr"/>
+      <c r="Q32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -28267,11 +28459,11 @@
       </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P33" s="17" t="inlineStr"/>
-      <c r="Q33" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P33" s="15" t="inlineStr"/>
+      <c r="Q33" s="15" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -28330,11 +28522,11 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P34" s="17" t="inlineStr"/>
-      <c r="Q34" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
+        </is>
+      </c>
+      <c r="P34" s="15" t="inlineStr"/>
+      <c r="Q34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -28373,7 +28565,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
@@ -28393,11 +28585,11 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P35" s="17" t="inlineStr"/>
-      <c r="Q35" s="17" t="inlineStr"/>
+          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232110]</t>
+        </is>
+      </c>
+      <c r="P35" s="15" t="inlineStr"/>
+      <c r="Q35" s="15" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -28436,7 +28628,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
@@ -28456,11 +28648,11 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P36" s="17" t="inlineStr"/>
-      <c r="Q36" s="17" t="inlineStr"/>
+          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
+        </is>
+      </c>
+      <c r="P36" s="15" t="inlineStr"/>
+      <c r="Q36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -28499,7 +28691,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
@@ -28519,11 +28711,11 @@
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P37" s="17" t="inlineStr"/>
-      <c r="Q37" s="17" t="inlineStr"/>
+          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
+        </is>
+      </c>
+      <c r="P37" s="15" t="inlineStr"/>
+      <c r="Q37" s="15" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -28562,7 +28754,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
@@ -28582,11 +28774,11 @@
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P38" s="17" t="inlineStr"/>
-      <c r="Q38" s="17" t="inlineStr"/>
+          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
+        </is>
+      </c>
+      <c r="P38" s="15" t="inlineStr"/>
+      <c r="Q38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -28645,11 +28837,11 @@
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P39" s="17" t="inlineStr"/>
-      <c r="Q39" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
+        </is>
+      </c>
+      <c r="P39" s="15" t="inlineStr"/>
+      <c r="Q39" s="15" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -28708,11 +28900,11 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P40" s="17" t="inlineStr"/>
-      <c r="Q40" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
+        </is>
+      </c>
+      <c r="P40" s="15" t="inlineStr"/>
+      <c r="Q40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -28771,11 +28963,11 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P41" s="17" t="inlineStr"/>
-      <c r="Q41" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
+        </is>
+      </c>
+      <c r="P41" s="15" t="inlineStr"/>
+      <c r="Q41" s="15" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -28814,7 +29006,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J42" s="6" t="n">
@@ -28834,11 +29026,11 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P42" s="17" t="inlineStr"/>
-      <c r="Q42" s="17" t="inlineStr"/>
+          <t>Uso e consumo (calçado/EPI) [NCM 64039190]</t>
+        </is>
+      </c>
+      <c r="P42" s="15" t="inlineStr"/>
+      <c r="Q42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -28877,7 +29069,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
@@ -28897,11 +29089,11 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P43" s="17" t="inlineStr"/>
-      <c r="Q43" s="17" t="inlineStr"/>
+          <t>Uso e consumo (calçado/EPI) [NCM 64019200]</t>
+        </is>
+      </c>
+      <c r="P43" s="15" t="inlineStr"/>
+      <c r="Q43" s="15" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -28940,7 +29132,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
@@ -28960,11 +29152,11 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P44" s="17" t="inlineStr"/>
-      <c r="Q44" s="17" t="inlineStr"/>
+          <t>Uso e consumo (calçado/EPI) [NCM 64019990]</t>
+        </is>
+      </c>
+      <c r="P44" s="15" t="inlineStr"/>
+      <c r="Q44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -29003,7 +29195,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
@@ -29023,11 +29215,11 @@
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P45" s="17" t="inlineStr"/>
-      <c r="Q45" s="17" t="inlineStr"/>
+          <t>Uso e consumo (pano/TNT/EPI) [NCM 56031190]</t>
+        </is>
+      </c>
+      <c r="P45" s="15" t="inlineStr"/>
+      <c r="Q45" s="15" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -29066,7 +29258,7 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
@@ -29086,11 +29278,11 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P46" s="17" t="inlineStr"/>
-      <c r="Q46" s="17" t="inlineStr"/>
+          <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
+        </is>
+      </c>
+      <c r="P46" s="15" t="inlineStr"/>
+      <c r="Q46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -29149,11 +29341,11 @@
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P47" s="17" t="inlineStr"/>
-      <c r="Q47" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
+        </is>
+      </c>
+      <c r="P47" s="15" t="inlineStr"/>
+      <c r="Q47" s="15" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -29212,11 +29404,11 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P48" s="17" t="inlineStr"/>
-      <c r="Q48" s="17" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P48" s="15" t="inlineStr"/>
+      <c r="Q48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -29275,263 +29467,263 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P49" s="17" t="inlineStr"/>
-      <c r="Q49" s="17" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P49" s="15" t="inlineStr"/>
+      <c r="Q49" s="15" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="12" t="n">
         <v>46282</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>ALTEC IND.COM.IMP.E EXP.LTDA.</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>67598292000187</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="13" t="n">
         <v>30338</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E50" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>TAMPA ALUM.20MM RV PRATA 320580</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>83099000</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J50" s="16" t="n">
+      <c r="J50" s="14" t="n">
         <v>2506.56</v>
       </c>
-      <c r="K50" s="16" t="n">
+      <c r="K50" s="14" t="n">
         <v>300.79</v>
       </c>
-      <c r="L50" s="16" t="n">
+      <c r="L50" s="14" t="n">
         <v>300.79</v>
       </c>
-      <c r="M50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P50" s="17" t="inlineStr"/>
-      <c r="Q50" s="17" t="inlineStr"/>
+      <c r="M50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="13" t="inlineStr">
+        <is>
+          <t>Embalagem (tampa metálica) [NCM 83099000]</t>
+        </is>
+      </c>
+      <c r="P50" s="15" t="inlineStr"/>
+      <c r="Q50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="n">
+      <c r="A51" s="12" t="n">
         <v>46282</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="13" t="n">
         <v>23127</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="15" t="inlineStr">
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>MONOETANOLAMINA PA 1000ML - CARBON lote 11622</t>
         </is>
       </c>
-      <c r="G51" s="15" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>29221100</t>
         </is>
       </c>
-      <c r="H51" s="15" t="inlineStr">
+      <c r="H51" s="13" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="I51" s="13" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J51" s="16" t="n">
+      <c r="J51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="16" t="n">
+      <c r="K51" s="14" t="n">
         <v>0.2</v>
       </c>
-      <c r="L51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P51" s="17" t="inlineStr"/>
-      <c r="Q51" s="17" t="inlineStr"/>
+      <c r="L51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (químico orgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
+        </is>
+      </c>
+      <c r="P51" s="15" t="inlineStr"/>
+      <c r="Q51" s="15" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="14" t="n">
+      <c r="A52" s="12" t="n">
         <v>46282</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>49547438000183</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="13" t="n">
         <v>6782</v>
       </c>
-      <c r="E52" s="15" t="n">
+      <c r="E52" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>PANO ROLO MULTIUSO BRANCO 28x240 INOVEN</t>
         </is>
       </c>
-      <c r="G52" s="15" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>56039240</t>
         </is>
       </c>
-      <c r="H52" s="15" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="n">
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="n">
         <v>799</v>
       </c>
-      <c r="K52" s="16" t="n">
+      <c r="K52" s="14" t="n">
         <v>95.88</v>
       </c>
-      <c r="L52" s="16" t="n">
-        <v>95.88</v>
-      </c>
-      <c r="M52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P52" s="17" t="inlineStr"/>
-      <c r="Q52" s="17" t="inlineStr"/>
+      <c r="L52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (pano/TNT/EPI) [NCM 56039240]</t>
+        </is>
+      </c>
+      <c r="P52" s="15" t="inlineStr"/>
+      <c r="Q52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="n">
+      <c r="A53" s="12" t="n">
         <v>46282</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>49547438000183</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="13" t="n">
         <v>6782</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="E53" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>CABO ALUMINIO S ROSCA NOBRE 22MM X 1,40M</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>76082090</t>
         </is>
       </c>
-      <c r="H53" s="15" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="J53" s="16" t="n">
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="n">
         <v>34.9</v>
       </c>
-      <c r="K53" s="16" t="n">
+      <c r="K53" s="14" t="n">
         <v>6.81</v>
       </c>
-      <c r="L53" s="16" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="M53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P53" s="17" t="inlineStr"/>
-      <c r="Q53" s="17" t="inlineStr"/>
+      <c r="L53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (ferramenta/limpeza) [NCM 76082090]</t>
+        </is>
+      </c>
+      <c r="P53" s="15" t="inlineStr"/>
+      <c r="Q53" s="15" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -29590,11 +29782,11 @@
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P54" s="17" t="inlineStr"/>
-      <c r="Q54" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P54" s="15" t="inlineStr"/>
+      <c r="Q54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -29653,11 +29845,11 @@
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P55" s="17" t="inlineStr"/>
-      <c r="Q55" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P55" s="15" t="inlineStr"/>
+      <c r="Q55" s="15" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -29696,7 +29888,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
@@ -29716,11 +29908,11 @@
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P56" s="17" t="inlineStr"/>
-      <c r="Q56" s="17" t="inlineStr"/>
+          <t>Uso e consumo (filme stretch - embalagem de transporte) [NCM 39201099]</t>
+        </is>
+      </c>
+      <c r="P56" s="15" t="inlineStr"/>
+      <c r="Q56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -29759,7 +29951,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
@@ -29779,11 +29971,11 @@
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P57" s="17" t="inlineStr"/>
-      <c r="Q57" s="17" t="inlineStr"/>
+          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39239090]</t>
+        </is>
+      </c>
+      <c r="P57" s="15" t="inlineStr"/>
+      <c r="Q57" s="15" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -29842,11 +30034,11 @@
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P58" s="17" t="inlineStr"/>
-      <c r="Q58" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P58" s="15" t="inlineStr"/>
+      <c r="Q58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -29905,11 +30097,11 @@
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P59" s="17" t="inlineStr"/>
-      <c r="Q59" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P59" s="15" t="inlineStr"/>
+      <c r="Q59" s="15" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -29968,11 +30160,11 @@
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P60" s="17" t="inlineStr"/>
-      <c r="Q60" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P60" s="15" t="inlineStr"/>
+      <c r="Q60" s="15" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -30031,11 +30223,11 @@
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P61" s="17" t="inlineStr"/>
-      <c r="Q61" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P61" s="15" t="inlineStr"/>
+      <c r="Q61" s="15" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -30094,74 +30286,74 @@
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P62" s="17" t="inlineStr"/>
-      <c r="Q62" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P62" s="15" t="inlineStr"/>
+      <c r="Q62" s="15" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="n">
+      <c r="A63" s="12" t="n">
         <v>46286</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>BISPHARMA EMBALAGENS LTDA</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>59610485000188</t>
         </is>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="13" t="n">
         <v>117690</v>
       </c>
-      <c r="E63" s="15" t="n">
+      <c r="E63" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="15" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>COLORACAO HIDRATANTE PROFISSIONAL 60G Item.Ped.:       OP:119087 Cod.Externo:345566</t>
         </is>
       </c>
-      <c r="G63" s="15" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>76121000</t>
         </is>
       </c>
-      <c r="H63" s="15" t="inlineStr">
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J63" s="16" t="n">
+      <c r="J63" s="14" t="n">
         <v>26515.5</v>
       </c>
-      <c r="K63" s="16" t="n">
+      <c r="K63" s="14" t="n">
         <v>2987.66</v>
       </c>
-      <c r="L63" s="16" t="n">
+      <c r="L63" s="14" t="n">
         <v>2987.66</v>
       </c>
-      <c r="M63" s="16" t="n">
+      <c r="M63" s="14" t="n">
         <v>1618.32</v>
       </c>
-      <c r="N63" s="16" t="n">
+      <c r="N63" s="14" t="n">
         <v>1618.32</v>
       </c>
-      <c r="O63" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P63" s="17" t="inlineStr"/>
-      <c r="Q63" s="17" t="inlineStr"/>
+      <c r="O63" s="13" t="inlineStr">
+        <is>
+          <t>Embalagem (tubo de alumínio) [NCM 76121000]</t>
+        </is>
+      </c>
+      <c r="P63" s="15" t="inlineStr"/>
+      <c r="Q63" s="15" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -30220,11 +30412,11 @@
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P64" s="17" t="inlineStr"/>
-      <c r="Q64" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
+        </is>
+      </c>
+      <c r="P64" s="15" t="inlineStr"/>
+      <c r="Q64" s="15" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -30283,11 +30475,11 @@
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P65" s="17" t="inlineStr"/>
-      <c r="Q65" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
+        </is>
+      </c>
+      <c r="P65" s="15" t="inlineStr"/>
+      <c r="Q65" s="15" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -30346,137 +30538,137 @@
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P66" s="17" t="inlineStr"/>
-      <c r="Q66" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P66" s="15" t="inlineStr"/>
+      <c r="Q66" s="15" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="n">
+      <c r="A67" s="12" t="n">
         <v>46287</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>MCASSAB COMERCIO E INDUSTRIA LTDA</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>49698723003110</t>
         </is>
       </c>
-      <c r="D67" s="15" t="n">
+      <c r="D67" s="13" t="n">
         <v>275966</v>
       </c>
-      <c r="E67" s="15" t="n">
+      <c r="E67" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="15" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>TRANSCUTOL CG - TB 25 KG</t>
         </is>
       </c>
-      <c r="G67" s="15" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>29094429</t>
         </is>
       </c>
-      <c r="H67" s="15" t="inlineStr">
+      <c r="H67" s="13" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I67" s="15" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
-      </c>
-      <c r="J67" s="16" t="n">
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="n">
         <v>3873.74</v>
       </c>
-      <c r="K67" s="16" t="n">
+      <c r="K67" s="14" t="n">
         <v>154.95</v>
       </c>
-      <c r="L67" s="16" t="n">
+      <c r="L67" s="14" t="n">
         <v>154.95</v>
       </c>
-      <c r="M67" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P67" s="17" t="inlineStr"/>
-      <c r="Q67" s="17" t="inlineStr"/>
+      <c r="M67" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (químico orgânico) [NCM 29094429]</t>
+        </is>
+      </c>
+      <c r="P67" s="15" t="inlineStr"/>
+      <c r="Q67" s="15" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="14" t="n">
+      <c r="A68" s="12" t="n">
         <v>46288</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>HS INKLASER LTDA</t>
         </is>
       </c>
-      <c r="C68" s="15" t="inlineStr">
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>18858535000163</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D68" s="13" t="n">
         <v>48241</v>
       </c>
-      <c r="E68" s="15" t="n">
+      <c r="E68" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="15" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>CARTUCHO BLK 13 PRETO</t>
         </is>
       </c>
-      <c r="G68" s="15" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>84439923</t>
         </is>
       </c>
-      <c r="H68" s="15" t="inlineStr">
+      <c r="H68" s="13" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I68" s="15" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
-      </c>
-      <c r="J68" s="16" t="n">
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="n">
         <v>1074.5</v>
       </c>
-      <c r="K68" s="16" t="n">
+      <c r="K68" s="14" t="n">
         <v>125.11</v>
       </c>
-      <c r="L68" s="16" t="n">
-        <v>125.11</v>
-      </c>
-      <c r="M68" s="16" t="n">
+      <c r="L68" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="14" t="n">
         <v>31.95</v>
       </c>
-      <c r="N68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P68" s="17" t="inlineStr"/>
-      <c r="Q68" s="17" t="inlineStr"/>
+      <c r="N68" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="13" t="inlineStr">
+        <is>
+          <t>Uso e consumo (suprimento de impressora) [NCM 84439923]</t>
+        </is>
+      </c>
+      <c r="P68" s="15" t="inlineStr"/>
+      <c r="Q68" s="15" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -30535,11 +30727,11 @@
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P69" s="17" t="inlineStr"/>
-      <c r="Q69" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 6901]</t>
+        </is>
+      </c>
+      <c r="P69" s="15" t="inlineStr"/>
+      <c r="Q69" s="15" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -30598,74 +30790,74 @@
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P70" s="17" t="inlineStr"/>
-      <c r="Q70" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P70" s="15" t="inlineStr"/>
+      <c r="Q70" s="15" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="n">
+      <c r="A71" s="12" t="n">
         <v>46288</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>62514971000107</t>
         </is>
       </c>
-      <c r="D71" s="15" t="n">
+      <c r="D71" s="13" t="n">
         <v>141811</v>
       </c>
-      <c r="E71" s="15" t="n">
+      <c r="E71" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="15" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>CASHMERE - 204510</t>
         </is>
       </c>
-      <c r="G71" s="15" t="inlineStr">
+      <c r="G71" s="13" t="inlineStr">
         <is>
           <t>33029019</t>
         </is>
       </c>
-      <c r="H71" s="15" t="inlineStr">
+      <c r="H71" s="13" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I71" s="15" t="inlineStr">
+      <c r="I71" s="13" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J71" s="16" t="n">
+      <c r="J71" s="14" t="n">
         <v>4794.99</v>
       </c>
-      <c r="K71" s="16" t="n">
+      <c r="K71" s="14" t="n">
         <v>557.29</v>
       </c>
-      <c r="L71" s="16" t="n">
+      <c r="L71" s="14" t="n">
         <v>557.29</v>
       </c>
-      <c r="M71" s="16" t="n">
+      <c r="M71" s="14" t="n">
         <v>150.93</v>
       </c>
-      <c r="N71" s="16" t="n">
+      <c r="N71" s="14" t="n">
         <v>150.93</v>
       </c>
-      <c r="O71" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P71" s="17" t="inlineStr"/>
-      <c r="Q71" s="17" t="inlineStr"/>
+      <c r="O71" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (fragrância/essência) [NCM 33029019]</t>
+        </is>
+      </c>
+      <c r="P71" s="15" t="inlineStr"/>
+      <c r="Q71" s="15" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -30692,7 +30884,11 @@
           <t>Antecipação de Pagamento (Adiantamento)</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
           <t>6949</t>
@@ -30720,11 +30916,11 @@
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P72" s="17" t="inlineStr"/>
-      <c r="Q72" s="17" t="inlineStr"/>
+          <t>Nota sem mercadoria (antecipação/financeira) [CFOP 6949 / NCM 00000000]</t>
+        </is>
+      </c>
+      <c r="P72" s="15" t="inlineStr"/>
+      <c r="Q72" s="15" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -30751,7 +30947,11 @@
           <t>Antecipação de Pagamento (Adiantamento)</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
           <t>6949</t>
@@ -30779,74 +30979,74 @@
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P73" s="17" t="inlineStr"/>
-      <c r="Q73" s="17" t="inlineStr"/>
+          <t>Nota sem mercadoria (antecipação/financeira) [CFOP 6949 / NCM 00000000]</t>
+        </is>
+      </c>
+      <c r="P73" s="15" t="inlineStr"/>
+      <c r="Q73" s="15" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="n">
+      <c r="A74" s="12" t="n">
         <v>46294</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>CHEMYUNION LTDA</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>58309709000820</t>
         </is>
       </c>
-      <c r="D74" s="5" t="n">
+      <c r="D74" s="13" t="n">
         <v>19303</v>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E74" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="13" t="inlineStr">
         <is>
           <t>Uniox C (20,000)</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>34024200</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" s="13" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="n">
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="n">
         <v>8747.379999999999</v>
       </c>
-      <c r="K74" s="6" t="n">
+      <c r="K74" s="14" t="n">
         <v>1016.64</v>
       </c>
-      <c r="L74" s="6" t="n">
+      <c r="L74" s="14" t="n">
         <v>1016.64</v>
       </c>
-      <c r="M74" s="6" t="n">
+      <c r="M74" s="14" t="n">
         <v>275.34</v>
       </c>
-      <c r="N74" s="6" t="n">
+      <c r="N74" s="14" t="n">
         <v>275.34</v>
       </c>
-      <c r="O74" s="5" t="inlineStr">
-        <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P74" s="17" t="inlineStr"/>
-      <c r="Q74" s="17" t="inlineStr"/>
+      <c r="O74" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (tensoativo) [NCM 34024200]</t>
+        </is>
+      </c>
+      <c r="P74" s="15" t="inlineStr"/>
+      <c r="Q74" s="15" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -30885,7 +31085,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J75" s="6" t="n">
@@ -30905,11 +31105,11 @@
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P75" s="17" t="inlineStr"/>
-      <c r="Q75" s="17" t="inlineStr"/>
+          <t>Matéria-prima (óleos e gorduras) [NCM 15159090]</t>
+        </is>
+      </c>
+      <c r="P75" s="15" t="inlineStr"/>
+      <c r="Q75" s="15" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -30948,7 +31148,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="J76" s="6" t="n">
@@ -30968,11 +31168,11 @@
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P76" s="17" t="inlineStr"/>
-      <c r="Q76" s="17" t="inlineStr"/>
+          <t>Embalagem (rótulo/etiqueta) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
+        </is>
+      </c>
+      <c r="P76" s="15" t="inlineStr"/>
+      <c r="Q76" s="15" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -31031,11 +31231,11 @@
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P77" s="17" t="inlineStr"/>
-      <c r="Q77" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 6901]</t>
+        </is>
+      </c>
+      <c r="P77" s="15" t="inlineStr"/>
+      <c r="Q77" s="15" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -31094,74 +31294,74 @@
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P78" s="17" t="inlineStr"/>
-      <c r="Q78" s="17" t="inlineStr"/>
+          <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
+        </is>
+      </c>
+      <c r="P78" s="15" t="inlineStr"/>
+      <c r="Q78" s="15" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="14" t="n">
+      <c r="A79" s="12" t="n">
         <v>46294</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="13" t="inlineStr">
         <is>
           <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="C79" s="13" t="inlineStr">
         <is>
           <t>11340087000162</t>
         </is>
       </c>
-      <c r="D79" s="15" t="n">
+      <c r="D79" s="13" t="n">
         <v>42285</v>
       </c>
-      <c r="E79" s="15" t="n">
+      <c r="E79" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="15" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>KERANUTRI</t>
         </is>
       </c>
-      <c r="G79" s="15" t="inlineStr">
+      <c r="G79" s="13" t="inlineStr">
         <is>
           <t>38249989</t>
         </is>
       </c>
-      <c r="H79" s="15" t="inlineStr">
+      <c r="H79" s="13" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
-      </c>
-      <c r="J79" s="16" t="n">
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="J79" s="14" t="n">
         <v>4278.84</v>
       </c>
-      <c r="K79" s="16" t="n">
+      <c r="K79" s="14" t="n">
         <v>160.71</v>
       </c>
-      <c r="L79" s="16" t="n">
+      <c r="L79" s="14" t="n">
         <v>160.71</v>
       </c>
-      <c r="M79" s="16" t="n">
+      <c r="M79" s="14" t="n">
         <v>261.15</v>
       </c>
-      <c r="N79" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="15" t="inlineStr">
-        <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P79" s="17" t="inlineStr"/>
-      <c r="Q79" s="17" t="inlineStr"/>
+      <c r="N79" s="14" t="n">
+        <v>261.15</v>
+      </c>
+      <c r="O79" s="13" t="inlineStr">
+        <is>
+          <t>Matéria-prima (preparação química) [NCM 38249989]</t>
+        </is>
+      </c>
+      <c r="P79" s="15" t="inlineStr"/>
+      <c r="Q79" s="15" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -31220,11 +31420,11 @@
       </c>
       <c r="O80" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P80" s="17" t="inlineStr"/>
-      <c r="Q80" s="17" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P80" s="15" t="inlineStr"/>
+      <c r="Q80" s="15" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -31263,7 +31463,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="J81" s="6" t="n">
@@ -31283,11 +31483,11 @@
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>regra padrão (fornecedor novo)</t>
-        </is>
-      </c>
-      <c r="P81" s="17" t="inlineStr"/>
-      <c r="Q81" s="17" t="inlineStr"/>
+          <t>Matéria-prima (químico inorgânico) [NCM 28321010]</t>
+        </is>
+      </c>
+      <c r="P81" s="15" t="inlineStr"/>
+      <c r="Q81" s="15" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -31316,7 +31516,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>9030090</t>
+          <t>09030090</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
@@ -31346,11 +31546,11 @@
       </c>
       <c r="O82" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P82" s="17" t="inlineStr"/>
-      <c r="Q82" s="17" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P82" s="15" t="inlineStr"/>
+      <c r="Q82" s="15" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -31409,11 +31609,11 @@
       </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P83" s="17" t="inlineStr"/>
-      <c r="Q83" s="17" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P83" s="15" t="inlineStr"/>
+      <c r="Q83" s="15" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -31442,7 +31642,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>9012100</t>
+          <t>09012100</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -31472,11 +31672,11 @@
       </c>
       <c r="O84" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor)</t>
-        </is>
-      </c>
-      <c r="P84" s="17" t="inlineStr"/>
-      <c r="Q84" s="17" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P84" s="15" t="inlineStr"/>
+      <c r="Q84" s="15" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -31535,11 +31735,11 @@
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>aprendido (fornecedor+NCM)</t>
-        </is>
-      </c>
-      <c r="P85" s="17" t="inlineStr"/>
-      <c r="Q85" s="17" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P85" s="15" t="inlineStr"/>
+      <c r="Q85" s="15" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -31596,7 +31796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -31683,35 +31883,275 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>00428307000600</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5597996</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>RS-PR</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>301.49</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>36.18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>25709</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>116.03</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>13.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>25910</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>812.3</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>812.3</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>97.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>26411</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>15.12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TRANS TOMAZ TRANSPORTES RODOV DE CARGAS EIREL</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>03867083000290</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>26730</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>6353</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>SP-PR</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>188.49</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>188.49</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>22.62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr"/>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="9">
-        <f>SUM(H4:H3)</f>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="9">
+        <f>SUM(H4:H8)</f>
         <v/>
       </c>
-      <c r="I4" s="9">
-        <f>SUM(I4:I3)</f>
+      <c r="I9" s="9">
+        <f>SUM(I4:I8)</f>
         <v/>
       </c>
-      <c r="J4" s="9">
-        <f>SUM(J4:J3)</f>
+      <c r="J9" s="9">
+        <f>SUM(J4:J8)</f>
         <v/>
       </c>
-      <c r="K4" s="9">
-        <f>SUM(K4:K3)</f>
+      <c r="K9" s="9">
+        <f>SUM(K4:K8)</f>
         <v/>
       </c>
-      <c r="L4" s="9">
-        <f>SUM(L4:L3)</f>
+      <c r="L9" s="9">
+        <f>SUM(L4:L8)</f>
         <v/>
       </c>
     </row>
@@ -31726,7 +32166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31790,383 +32230,743 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Numeração</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>NF 8948/1</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Número sem XML no período (nem cancelada nem inutilizada) - pedir o XML</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr"/>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Fornecedor sem histórico</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>ALTEC IND.COM.IMP.E EXP.LTDA. (67598292000187)</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="15" t="inlineStr"/>
+      <c r="G5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Numeração</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>NF 8951/1</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Número sem XML no período (nem cancelada nem inutilizada) - pedir o XML</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Fornecedor sem histórico</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>BISPHARMA EMBALAGENS LTDA (59610485000188)</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="15" t="inlineStr"/>
+      <c r="G6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Numeração</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>NF 8956/1</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Número sem XML no período (nem cancelada nem inutilizada) - pedir o XML</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Fornecedor sem histórico</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>CHEMYUNION LTDA (58309709000820)</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="15" t="inlineStr"/>
+      <c r="G7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Numeração</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>NF 8965/1</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>Número sem XML no período (nem cancelada nem inutilizada) - pedir o XML</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Fornecedor sem histórico</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA (04993269000177)</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Numeração</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>NF 8972/1</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>Número sem XML no período (nem cancelada nem inutilizada) - pedir o XML</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Fornecedor sem histórico</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="15" t="inlineStr"/>
+      <c r="G9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>ALTEC IND.COM.IMP.E EXP.LTDA. (67598292000187)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>HS INKLASER LTDA (18858535000163)</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="15" t="inlineStr"/>
+      <c r="G10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>BISPHARMA EMBALAGENS LTDA (59610485000188)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Lunaflexo Tecnologia Adesiva Eireli (06015875000143)</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="15" t="inlineStr"/>
+      <c r="G11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>CARBON CIENTIFICA LTDA (44114040000130)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>MCASSAB COMERCIO E INDUSTRIA LTDA (49698723003110)</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="15" t="inlineStr"/>
+      <c r="G12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA (04993269000177)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="15" t="inlineStr"/>
+      <c r="G13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA (11340087000162)</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="inlineStr"/>
+      <c r="G14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>HS INKLASER LTDA (18858535000163)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="inlineStr"/>
+      <c r="G15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>MCASSAB COMERCIO E INDUSTRIA LTDA (49698723003110)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>VOLUMES: 4 CAIXAS</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="15" t="inlineStr"/>
+      <c r="G16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="15" t="inlineStr"/>
+      <c r="G17" s="15" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA (11340087000162)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="15" t="inlineStr"/>
+      <c r="G18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>Crédito de ICMS/IPI pela regra padrão do CFOP - confirmar se é insumo (1101/2101) ou uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="15" t="inlineStr"/>
+      <c r="G19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="15" t="inlineStr"/>
+      <c r="G20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="15" t="inlineStr"/>
+      <c r="G21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="15" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="15" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="15" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="15" t="inlineStr"/>
+      <c r="G26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="15" t="inlineStr"/>
+      <c r="G27" s="15" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="15" t="inlineStr"/>
+      <c r="G28" s="15" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="15" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>PESO BRUTO: 300,000</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="15" t="inlineStr"/>
+      <c r="G30" s="15" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="15" t="inlineStr"/>
+      <c r="G31" s="15" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="15" t="inlineStr"/>
+      <c r="G32" s="15" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="15" t="inlineStr"/>
+      <c r="G33" s="15" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="15" t="inlineStr"/>
+      <c r="G34" s="15" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="15" t="inlineStr"/>
+      <c r="G35" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32194,7 +32994,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>1. Vendas de NCM fora da lista monofásica (Lei 10.147/2000, art. 1º, I, b) somam R$ 5,475.65 e estão na base de 2,2%/10,3%, como na planilha de 08/2026: 28470000 (R$ 5,475.65). Se forem tributadas a 0,65%/3%, a diferença é PIS R$ 84.87 e COFINS R$ 399.72 a menor. Confirmar com a contadora.</t>
         </is>
@@ -32211,7 +33011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -32301,11 +33101,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Cancelada (fornecedor)</t>
+          <t>Cancelada</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>794</v>
+        <v>8952</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -32313,30 +33113,30 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>YAHWEH PRINT BRASIL LTDA</t>
+          <t>GUIDI COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4370.44</v>
+        <v>6307.1</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>41260952680145000184550010000007941049258979</t>
+          <t>41260933039048000162550010000089521000162996</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Cancelada (fornecedor)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>8952</v>
+        <v>794</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -32344,21 +33144,135 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>GUIDI COSMETICOS LTDA</t>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>6307.1</v>
+        <v>4370.44</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>41260933039048000162550010000089521000162996</t>
-        </is>
-      </c>
+          <t>41260952680145000184550010000007941049258979</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>8938</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>8948</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8951</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>8956</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8965</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8972</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
@@ -8,19 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saídas por acumulador" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas de saída" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Itens de saída" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entradas e créditos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT-e" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergências" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observações" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canceladas e inutilizadas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saídas por acumulador" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas de saída" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Itens de saída" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entradas e créditos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT-e" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Divergências" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observações" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canceladas e inutilizadas" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Notas de saída'!$A$3:$M$94</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Itens de saída'!$A$3:$Q$310</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Entradas e créditos'!$A$4:$Q$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Notas de saída'!$A$3:$M$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Itens de saída'!$A$3:$Q$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Entradas e créditos'!$A$4:$Q$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,7 +69,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,12 +83,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,16 +143,29 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -630,7 +654,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>9960.01</v>
+        <v>9996.190000000001</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>46307</v>
@@ -1104,7 +1128,7 @@
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>-185.32</v>
+        <v>-149.14</v>
       </c>
     </row>
     <row r="47">
@@ -1271,13 +1295,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>Divergências ALTA</t>
         </is>
       </c>
-      <c r="B67" s="11" t="n">
-        <v>0</v>
+      <c r="B67" s="13" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -1287,7 +1311,7 @@
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
@@ -1297,8 +1321,282 @@
         </is>
       </c>
       <c r="B69" s="11" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Notas canceladas e números inutilizados no mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Série</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Emissão</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Destinatário/Emitente</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Chave</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Cancelada</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>8940</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>R&amp;S COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>7368</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>41260933039048000162550010000089401000115920</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Cancelada</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>8952</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>GUIDI COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>6307.1</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>41260933039048000162550010000089521000162996</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Cancelada (fornecedor)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>794</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>4370.44</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>41260952680145000184550010000007941049258979</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>8938</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>8948</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8951</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>8956</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8965</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Inutilizada</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8972</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1306,6 +1604,544 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Checklist da conferência automática do mês</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>OK = cruzamento feito sem ocorrência; VERIFICAR = ver a aba Divergências; NÃO EXECUTADO = faltou o arquivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Verificação</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Base legal</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Conferido por</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Numeração sequencial (buraco sem cancelamento/inutilização)</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Ajuste SINIEF 07/05</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>ICMS e IPI recalculados (BC x alíquota) e CST x valor</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>LC 87/96 art. 13; RIPI art. 190</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>CFOP x UF do destinatário e alíquota interestadual</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>1 ALTA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Res. Senado 22/89 e 13/12</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>CFOP com/sem ST x ST destacada</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>RICMS/PR Anexo IX</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Contribuinte com IE tratado como consumidor final</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>1 ALTA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>LC 87/96 art. 6º e RICMS/PR Anexo IX (ST nas saídas para revenda); Ajuste SINIEF 07/05 (indIEDest/indFinal); LC 87/96 art. 13 §2º (IPI fora da base só entre contribuintes)</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>CFOP de revenda (5102) em produto de fabricação própria</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>13 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Tabela CFOP (Ajuste SINIEF 07/01): 5101 produção do estabelecimento, 5102 mercadoria de terceiros; RIPI art. 35</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Industrialização 5124/6124 x retorno 5902/6902 x remessa do cliente</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>5 ALTA, 2 MÉDIA, 1 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>RICMS/PR (industrialização por encomenda: 5124 pela industrialização + 5902 retorno simbólico do insumo); Lei 10.147/2000 (5124 fora do monofásico: 0,65%/3%)</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Diferimento nas 5124 internas</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>1 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>RICMS/PR (diferimento)</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Grupo de IPI nos produtos</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>3 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>RIPI/2010 (Decreto 7.212) - grupo IPI obrigatório para produto industrializado (NT 2016.002)</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>NCM x PIS/COFINS monofásico</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Lei 10.147/2000</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Entradas</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Fornecedor sem histórico (insumo x uso e consumo)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>11 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>LC 87/96 art. 20 e 33, I</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Entradas</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Notas desconhecidas/manifestadas</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Ajuste SINIEF 07/05</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Entradas</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Remessas recebidas sem retorno (estoque de terceiros)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>12 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>RICMS/PR (industrialização por encomenda)</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>CT-e</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Crédito do frete segue a natureza da NF-e transportada</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>1 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>LC 87/96 art. 20 e 33, I</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>NFS-e tomadas: retenção de IRRF e PIS/COFINS/CSLL</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>1 MÉDIA, 1 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Lei 10.833/2003 art. 30 e 31 §3º (dispensa até R$ 10); RIR/2018 art. 714 e 716; IN SRF 459/2004</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>SPED</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>XML x SPED (notas faltando de um lado ou do outro)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>SPED do mês ainda não existe</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>NÃO EXECUTADO</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Guia Prático EFD ICMS/IPI</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1693,7 +2529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6654,7 +7490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26509,7 +27345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26639,67 +27475,67 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="22" t="n">
         <v>46266</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>04993269000177</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="18" t="n">
         <v>41731</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>ALCOOL ETILICO 99 - ONU 1170 ETANOL (ALCOOL ETILICO) 3 GE II BOMBONA DIPANOL 99</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>22071010</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="23" t="n">
         <v>1870</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="23" t="n">
         <v>224.41</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="L5" s="23" t="n">
         <v>224.41</v>
       </c>
-      <c r="M5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="M5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (álcool etílico) [NCM 22071010]</t>
         </is>
       </c>
-      <c r="P5" s="15" t="inlineStr"/>
-      <c r="Q5" s="15" t="inlineStr"/>
+      <c r="P5" s="16" t="inlineStr"/>
+      <c r="Q5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -26761,8 +27597,8 @@
           <t>Embalagem (rótulo adesivo) [NCM 39191090]</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr"/>
-      <c r="Q6" s="15" t="inlineStr"/>
+      <c r="P6" s="16" t="inlineStr"/>
+      <c r="Q6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -26824,134 +27660,134 @@
           <t>Embalagem (rótulo adesivo) [NCM 39191090]</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr"/>
-      <c r="Q7" s="15" t="inlineStr"/>
+      <c r="P7" s="16" t="inlineStr"/>
+      <c r="Q7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="18" t="n">
         <v>22837</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>SULFITO DE SODIO ANIDRO PA 1000G - CARBON</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>28321010</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="L8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="L8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (químico inorgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P8" s="15" t="inlineStr"/>
-      <c r="Q8" s="15" t="inlineStr"/>
+      <c r="P8" s="16" t="inlineStr"/>
+      <c r="Q8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="18" t="n">
         <v>22837</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>PIROFOSFATO DE SODIO (TETRABASICO) DECAHIDRATADO PA 1000G - CARBON</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>28353920</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="L9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (químico inorgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P9" s="15" t="inlineStr"/>
-      <c r="Q9" s="15" t="inlineStr"/>
+      <c r="P9" s="16" t="inlineStr"/>
+      <c r="Q9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -27013,512 +27849,512 @@
           <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
         </is>
       </c>
-      <c r="P10" s="15" t="inlineStr"/>
-      <c r="Q10" s="15" t="inlineStr"/>
+      <c r="P10" s="16" t="inlineStr"/>
+      <c r="Q10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Agar Triptico de soja (TSA) pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="23" t="n">
         <v>250.39</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="23" t="n">
         <v>48.83</v>
       </c>
-      <c r="L11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
+      <c r="L11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr"/>
-      <c r="Q11" s="15" t="inlineStr"/>
+      <c r="P11" s="16" t="inlineStr"/>
+      <c r="Q11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>Agar Sabouraud Dextrose pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="23" t="n">
         <v>222.56</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="23" t="n">
         <v>43.4</v>
       </c>
-      <c r="L12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13" t="inlineStr">
+      <c r="L12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P12" s="15" t="inlineStr"/>
-      <c r="Q12" s="15" t="inlineStr"/>
+      <c r="P12" s="16" t="inlineStr"/>
+      <c r="Q12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Agar PCA pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="23" t="n">
         <v>35.06</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="23" t="n">
         <v>6.84</v>
       </c>
-      <c r="L13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
+      <c r="L13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P13" s="15" t="inlineStr"/>
-      <c r="Q13" s="15" t="inlineStr"/>
+      <c r="P13" s="16" t="inlineStr"/>
+      <c r="Q13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>Agar Mac Conkey pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="23" t="n">
         <v>35.15</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="23" t="n">
         <v>6.85</v>
       </c>
-      <c r="L14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="L14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr"/>
-      <c r="Q14" s="15" t="inlineStr"/>
+      <c r="P14" s="16" t="inlineStr"/>
+      <c r="Q14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Agar Cetrimide pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="23" t="n">
         <v>226.01</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="23" t="n">
         <v>44.07</v>
       </c>
-      <c r="L15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="13" t="inlineStr">
+      <c r="L15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P15" s="15" t="inlineStr"/>
-      <c r="Q15" s="15" t="inlineStr"/>
+      <c r="P15" s="16" t="inlineStr"/>
+      <c r="Q15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Agar Baird Parker pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="23" t="n">
         <v>317.89</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="23" t="n">
         <v>61.99</v>
       </c>
-      <c r="L16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="13" t="inlineStr">
+      <c r="L16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P16" s="15" t="inlineStr"/>
-      <c r="Q16" s="15" t="inlineStr"/>
+      <c r="P16" s="16" t="inlineStr"/>
+      <c r="Q16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>Acquaplus I sachê c/ 10 testes</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="23" t="n">
         <v>915.08</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="23" t="n">
         <v>178.44</v>
       </c>
-      <c r="L17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="13" t="inlineStr">
+      <c r="L17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P17" s="15" t="inlineStr"/>
-      <c r="Q17" s="15" t="inlineStr"/>
+      <c r="P17" s="16" t="inlineStr"/>
+      <c r="Q17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="22" t="n">
         <v>46267</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="18" t="n">
         <v>160326</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>Caldo BHI cx c/ 10 tubos</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="J18" s="23" t="n">
         <v>246.51</v>
       </c>
-      <c r="K18" s="14" t="n">
+      <c r="K18" s="23" t="n">
         <v>48.07</v>
       </c>
-      <c r="L18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13" t="inlineStr">
+      <c r="L18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P18" s="15" t="inlineStr"/>
-      <c r="Q18" s="15" t="inlineStr"/>
+      <c r="P18" s="16" t="inlineStr"/>
+      <c r="Q18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -27580,8 +28416,8 @@
           <t>Matéria-prima (químico orgânico) [NCM 29221100]</t>
         </is>
       </c>
-      <c r="P19" s="15" t="inlineStr"/>
-      <c r="Q19" s="15" t="inlineStr"/>
+      <c r="P19" s="16" t="inlineStr"/>
+      <c r="Q19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -27643,8 +28479,8 @@
           <t>Uso e consumo (peça de manutenção) [NCM 85334099]</t>
         </is>
       </c>
-      <c r="P20" s="15" t="inlineStr"/>
-      <c r="Q20" s="15" t="inlineStr"/>
+      <c r="P20" s="16" t="inlineStr"/>
+      <c r="Q20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -27706,8 +28542,8 @@
           <t>Uso e consumo (peça de manutenção) [NCM 85334099]</t>
         </is>
       </c>
-      <c r="P21" s="15" t="inlineStr"/>
-      <c r="Q21" s="15" t="inlineStr"/>
+      <c r="P21" s="16" t="inlineStr"/>
+      <c r="Q21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -27769,8 +28605,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P22" s="15" t="inlineStr"/>
-      <c r="Q22" s="15" t="inlineStr"/>
+      <c r="P22" s="16" t="inlineStr"/>
+      <c r="Q22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -27832,8 +28668,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P23" s="15" t="inlineStr"/>
-      <c r="Q23" s="15" t="inlineStr"/>
+      <c r="P23" s="16" t="inlineStr"/>
+      <c r="Q23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -27895,8 +28731,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P24" s="15" t="inlineStr"/>
-      <c r="Q24" s="15" t="inlineStr"/>
+      <c r="P24" s="16" t="inlineStr"/>
+      <c r="Q24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -27958,8 +28794,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P25" s="15" t="inlineStr"/>
-      <c r="Q25" s="15" t="inlineStr"/>
+      <c r="P25" s="16" t="inlineStr"/>
+      <c r="Q25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -28021,8 +28857,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P26" s="15" t="inlineStr"/>
-      <c r="Q26" s="15" t="inlineStr"/>
+      <c r="P26" s="16" t="inlineStr"/>
+      <c r="Q26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -28084,8 +28920,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P27" s="15" t="inlineStr"/>
-      <c r="Q27" s="15" t="inlineStr"/>
+      <c r="P27" s="16" t="inlineStr"/>
+      <c r="Q27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -28147,8 +28983,8 @@
           <t>Uso e consumo (luva/artigo plástico) [NCM 39262000]</t>
         </is>
       </c>
-      <c r="P28" s="15" t="inlineStr"/>
-      <c r="Q28" s="15" t="inlineStr"/>
+      <c r="P28" s="16" t="inlineStr"/>
+      <c r="Q28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -28210,8 +29046,8 @@
           <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
         </is>
       </c>
-      <c r="P29" s="15" t="inlineStr"/>
-      <c r="Q29" s="15" t="inlineStr"/>
+      <c r="P29" s="16" t="inlineStr"/>
+      <c r="Q29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -28273,8 +29109,8 @@
           <t>Uso e consumo (pincel) - mas CFOP 6949 (outras saídas: amostra/brinde/remessa) [CFOP 6949]</t>
         </is>
       </c>
-      <c r="P30" s="15" t="inlineStr"/>
-      <c r="Q30" s="15" t="inlineStr"/>
+      <c r="P30" s="16" t="inlineStr"/>
+      <c r="Q30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -28336,8 +29172,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P31" s="15" t="inlineStr"/>
-      <c r="Q31" s="15" t="inlineStr"/>
+      <c r="P31" s="16" t="inlineStr"/>
+      <c r="Q31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -28399,8 +29235,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P32" s="15" t="inlineStr"/>
-      <c r="Q32" s="15" t="inlineStr"/>
+      <c r="P32" s="16" t="inlineStr"/>
+      <c r="Q32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -28462,8 +29298,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P33" s="15" t="inlineStr"/>
-      <c r="Q33" s="15" t="inlineStr"/>
+      <c r="P33" s="16" t="inlineStr"/>
+      <c r="Q33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -28525,8 +29361,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
         </is>
       </c>
-      <c r="P34" s="15" t="inlineStr"/>
-      <c r="Q34" s="15" t="inlineStr"/>
+      <c r="P34" s="16" t="inlineStr"/>
+      <c r="Q34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -28588,8 +29424,8 @@
           <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232110]</t>
         </is>
       </c>
-      <c r="P35" s="15" t="inlineStr"/>
-      <c r="Q35" s="15" t="inlineStr"/>
+      <c r="P35" s="16" t="inlineStr"/>
+      <c r="Q35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -28651,8 +29487,8 @@
           <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
         </is>
       </c>
-      <c r="P36" s="15" t="inlineStr"/>
-      <c r="Q36" s="15" t="inlineStr"/>
+      <c r="P36" s="16" t="inlineStr"/>
+      <c r="Q36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -28714,8 +29550,8 @@
           <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
         </is>
       </c>
-      <c r="P37" s="15" t="inlineStr"/>
-      <c r="Q37" s="15" t="inlineStr"/>
+      <c r="P37" s="16" t="inlineStr"/>
+      <c r="Q37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -28777,8 +29613,8 @@
           <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
         </is>
       </c>
-      <c r="P38" s="15" t="inlineStr"/>
-      <c r="Q38" s="15" t="inlineStr"/>
+      <c r="P38" s="16" t="inlineStr"/>
+      <c r="Q38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -28840,8 +29676,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P39" s="15" t="inlineStr"/>
-      <c r="Q39" s="15" t="inlineStr"/>
+      <c r="P39" s="16" t="inlineStr"/>
+      <c r="Q39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -28903,8 +29739,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
         </is>
       </c>
-      <c r="P40" s="15" t="inlineStr"/>
-      <c r="Q40" s="15" t="inlineStr"/>
+      <c r="P40" s="16" t="inlineStr"/>
+      <c r="Q40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -28966,8 +29802,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
         </is>
       </c>
-      <c r="P41" s="15" t="inlineStr"/>
-      <c r="Q41" s="15" t="inlineStr"/>
+      <c r="P41" s="16" t="inlineStr"/>
+      <c r="Q41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -29029,8 +29865,8 @@
           <t>Uso e consumo (calçado/EPI) [NCM 64039190]</t>
         </is>
       </c>
-      <c r="P42" s="15" t="inlineStr"/>
-      <c r="Q42" s="15" t="inlineStr"/>
+      <c r="P42" s="16" t="inlineStr"/>
+      <c r="Q42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -29092,8 +29928,8 @@
           <t>Uso e consumo (calçado/EPI) [NCM 64019200]</t>
         </is>
       </c>
-      <c r="P43" s="15" t="inlineStr"/>
-      <c r="Q43" s="15" t="inlineStr"/>
+      <c r="P43" s="16" t="inlineStr"/>
+      <c r="Q43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -29155,8 +29991,8 @@
           <t>Uso e consumo (calçado/EPI) [NCM 64019990]</t>
         </is>
       </c>
-      <c r="P44" s="15" t="inlineStr"/>
-      <c r="Q44" s="15" t="inlineStr"/>
+      <c r="P44" s="16" t="inlineStr"/>
+      <c r="Q44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -29218,8 +30054,8 @@
           <t>Uso e consumo (pano/TNT/EPI) [NCM 56031190]</t>
         </is>
       </c>
-      <c r="P45" s="15" t="inlineStr"/>
-      <c r="Q45" s="15" t="inlineStr"/>
+      <c r="P45" s="16" t="inlineStr"/>
+      <c r="Q45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -29281,8 +30117,8 @@
           <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
         </is>
       </c>
-      <c r="P46" s="15" t="inlineStr"/>
-      <c r="Q46" s="15" t="inlineStr"/>
+      <c r="P46" s="16" t="inlineStr"/>
+      <c r="Q46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -29344,8 +30180,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P47" s="15" t="inlineStr"/>
-      <c r="Q47" s="15" t="inlineStr"/>
+      <c r="P47" s="16" t="inlineStr"/>
+      <c r="Q47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -29407,8 +30243,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P48" s="15" t="inlineStr"/>
-      <c r="Q48" s="15" t="inlineStr"/>
+      <c r="P48" s="16" t="inlineStr"/>
+      <c r="Q48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -29470,260 +30306,260 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P49" s="15" t="inlineStr"/>
-      <c r="Q49" s="15" t="inlineStr"/>
+      <c r="P49" s="16" t="inlineStr"/>
+      <c r="Q49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="n">
+      <c r="A50" s="22" t="n">
         <v>46282</v>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>ALTEC IND.COM.IMP.E EXP.LTDA.</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>67598292000187</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="18" t="n">
         <v>30338</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>TAMPA ALUM.20MM RV PRATA 320580</t>
         </is>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G50" s="18" t="inlineStr">
         <is>
           <t>83099000</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
+      <c r="H50" s="18" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J50" s="14" t="n">
+      <c r="J50" s="23" t="n">
         <v>2506.56</v>
       </c>
-      <c r="K50" s="14" t="n">
+      <c r="K50" s="23" t="n">
         <v>300.79</v>
       </c>
-      <c r="L50" s="14" t="n">
+      <c r="L50" s="23" t="n">
         <v>300.79</v>
       </c>
-      <c r="M50" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="13" t="inlineStr">
+      <c r="M50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="18" t="inlineStr">
         <is>
           <t>Embalagem (tampa metálica) [NCM 83099000]</t>
         </is>
       </c>
-      <c r="P50" s="15" t="inlineStr"/>
-      <c r="Q50" s="15" t="inlineStr"/>
+      <c r="P50" s="16" t="inlineStr"/>
+      <c r="Q50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="22" t="n">
         <v>46282</v>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="18" t="n">
         <v>23127</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>MONOETANOLAMINA PA 1000ML - CARBON lote 11622</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="G51" s="18" t="inlineStr">
         <is>
           <t>29221100</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I51" s="13" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="J51" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K51" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="L51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="13" t="inlineStr">
+      <c r="L51" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (químico orgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P51" s="15" t="inlineStr"/>
-      <c r="Q51" s="15" t="inlineStr"/>
+      <c r="P51" s="16" t="inlineStr"/>
+      <c r="Q51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="n">
+      <c r="A52" s="22" t="n">
         <v>46282</v>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>49547438000183</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="18" t="n">
         <v>6782</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="13" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>PANO ROLO MULTIUSO BRANCO 28x240 INOVEN</t>
         </is>
       </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="G52" s="18" t="inlineStr">
         <is>
           <t>56039240</t>
         </is>
       </c>
-      <c r="H52" s="13" t="inlineStr">
+      <c r="H52" s="18" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J52" s="14" t="n">
+      <c r="J52" s="23" t="n">
         <v>799</v>
       </c>
-      <c r="K52" s="14" t="n">
+      <c r="K52" s="23" t="n">
         <v>95.88</v>
       </c>
-      <c r="L52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="13" t="inlineStr">
+      <c r="L52" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (pano/TNT/EPI) [NCM 56039240]</t>
         </is>
       </c>
-      <c r="P52" s="15" t="inlineStr"/>
-      <c r="Q52" s="15" t="inlineStr"/>
+      <c r="P52" s="16" t="inlineStr"/>
+      <c r="Q52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="n">
+      <c r="A53" s="22" t="n">
         <v>46282</v>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>49547438000183</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="18" t="n">
         <v>6782</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="F53" s="18" t="inlineStr">
         <is>
           <t>CABO ALUMINIO S ROSCA NOBRE 22MM X 1,40M</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>76082090</t>
         </is>
       </c>
-      <c r="H53" s="13" t="inlineStr">
+      <c r="H53" s="18" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="I53" s="13" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J53" s="14" t="n">
+      <c r="J53" s="23" t="n">
         <v>34.9</v>
       </c>
-      <c r="K53" s="14" t="n">
+      <c r="K53" s="23" t="n">
         <v>6.81</v>
       </c>
-      <c r="L53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="13" t="inlineStr">
+      <c r="L53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (ferramenta/limpeza) [NCM 76082090]</t>
         </is>
       </c>
-      <c r="P53" s="15" t="inlineStr"/>
-      <c r="Q53" s="15" t="inlineStr"/>
+      <c r="P53" s="16" t="inlineStr"/>
+      <c r="Q53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -29785,8 +30621,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P54" s="15" t="inlineStr"/>
-      <c r="Q54" s="15" t="inlineStr"/>
+      <c r="P54" s="16" t="inlineStr"/>
+      <c r="Q54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -29848,8 +30684,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P55" s="15" t="inlineStr"/>
-      <c r="Q55" s="15" t="inlineStr"/>
+      <c r="P55" s="16" t="inlineStr"/>
+      <c r="Q55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -29911,8 +30747,8 @@
           <t>Uso e consumo (filme stretch - embalagem de transporte) [NCM 39201099]</t>
         </is>
       </c>
-      <c r="P56" s="15" t="inlineStr"/>
-      <c r="Q56" s="15" t="inlineStr"/>
+      <c r="P56" s="16" t="inlineStr"/>
+      <c r="Q56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -29974,8 +30810,8 @@
           <t>Embalagem (frasco/tampa/pote plástico) [NCM 39239090]</t>
         </is>
       </c>
-      <c r="P57" s="15" t="inlineStr"/>
-      <c r="Q57" s="15" t="inlineStr"/>
+      <c r="P57" s="16" t="inlineStr"/>
+      <c r="Q57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -30037,8 +30873,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P58" s="15" t="inlineStr"/>
-      <c r="Q58" s="15" t="inlineStr"/>
+      <c r="P58" s="16" t="inlineStr"/>
+      <c r="Q58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -30100,8 +30936,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P59" s="15" t="inlineStr"/>
-      <c r="Q59" s="15" t="inlineStr"/>
+      <c r="P59" s="16" t="inlineStr"/>
+      <c r="Q59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -30163,8 +30999,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P60" s="15" t="inlineStr"/>
-      <c r="Q60" s="15" t="inlineStr"/>
+      <c r="P60" s="16" t="inlineStr"/>
+      <c r="Q60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -30226,8 +31062,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P61" s="15" t="inlineStr"/>
-      <c r="Q61" s="15" t="inlineStr"/>
+      <c r="P61" s="16" t="inlineStr"/>
+      <c r="Q61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -30289,71 +31125,71 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P62" s="15" t="inlineStr"/>
-      <c r="Q62" s="15" t="inlineStr"/>
+      <c r="P62" s="16" t="inlineStr"/>
+      <c r="Q62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="n">
+      <c r="A63" s="22" t="n">
         <v>46286</v>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="18" t="inlineStr">
         <is>
           <t>BISPHARMA EMBALAGENS LTDA</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="18" t="inlineStr">
         <is>
           <t>59610485000188</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="18" t="n">
         <v>117690</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="13" t="inlineStr">
+      <c r="F63" s="18" t="inlineStr">
         <is>
           <t>COLORACAO HIDRATANTE PROFISSIONAL 60G Item.Ped.:       OP:119087 Cod.Externo:345566</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t>76121000</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I63" s="13" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J63" s="14" t="n">
+      <c r="J63" s="23" t="n">
         <v>26515.5</v>
       </c>
-      <c r="K63" s="14" t="n">
+      <c r="K63" s="23" t="n">
         <v>2987.66</v>
       </c>
-      <c r="L63" s="14" t="n">
+      <c r="L63" s="23" t="n">
         <v>2987.66</v>
       </c>
-      <c r="M63" s="14" t="n">
+      <c r="M63" s="23" t="n">
         <v>1618.32</v>
       </c>
-      <c r="N63" s="14" t="n">
+      <c r="N63" s="23" t="n">
         <v>1618.32</v>
       </c>
-      <c r="O63" s="13" t="inlineStr">
+      <c r="O63" s="18" t="inlineStr">
         <is>
           <t>Embalagem (tubo de alumínio) [NCM 76121000]</t>
         </is>
       </c>
-      <c r="P63" s="15" t="inlineStr"/>
-      <c r="Q63" s="15" t="inlineStr"/>
+      <c r="P63" s="16" t="inlineStr"/>
+      <c r="Q63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -30415,8 +31251,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P64" s="15" t="inlineStr"/>
-      <c r="Q64" s="15" t="inlineStr"/>
+      <c r="P64" s="16" t="inlineStr"/>
+      <c r="Q64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -30478,8 +31314,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P65" s="15" t="inlineStr"/>
-      <c r="Q65" s="15" t="inlineStr"/>
+      <c r="P65" s="16" t="inlineStr"/>
+      <c r="Q65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -30541,134 +31377,134 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P66" s="15" t="inlineStr"/>
-      <c r="Q66" s="15" t="inlineStr"/>
+      <c r="P66" s="16" t="inlineStr"/>
+      <c r="Q66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="n">
+      <c r="A67" s="22" t="n">
         <v>46287</v>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="18" t="inlineStr">
         <is>
           <t>MCASSAB COMERCIO E INDUSTRIA LTDA</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="18" t="inlineStr">
         <is>
           <t>49698723003110</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="18" t="n">
         <v>275966</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="F67" s="18" t="inlineStr">
         <is>
           <t>TRANSCUTOL CG - TB 25 KG</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>29094429</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I67" s="13" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J67" s="14" t="n">
+      <c r="J67" s="23" t="n">
         <v>3873.74</v>
       </c>
-      <c r="K67" s="14" t="n">
+      <c r="K67" s="23" t="n">
         <v>154.95</v>
       </c>
-      <c r="L67" s="14" t="n">
+      <c r="L67" s="23" t="n">
         <v>154.95</v>
       </c>
-      <c r="M67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="13" t="inlineStr">
+      <c r="M67" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (químico orgânico) [NCM 29094429]</t>
         </is>
       </c>
-      <c r="P67" s="15" t="inlineStr"/>
-      <c r="Q67" s="15" t="inlineStr"/>
+      <c r="P67" s="16" t="inlineStr"/>
+      <c r="Q67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="n">
+      <c r="A68" s="22" t="n">
         <v>46288</v>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="18" t="inlineStr">
         <is>
           <t>HS INKLASER LTDA</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="18" t="inlineStr">
         <is>
           <t>18858535000163</t>
         </is>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="18" t="n">
         <v>48241</v>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F68" s="18" t="inlineStr">
         <is>
           <t>CARTUCHO BLK 13 PRETO</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G68" s="18" t="inlineStr">
         <is>
           <t>84439923</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>2556</t>
         </is>
       </c>
-      <c r="J68" s="14" t="n">
+      <c r="J68" s="23" t="n">
         <v>1074.5</v>
       </c>
-      <c r="K68" s="14" t="n">
+      <c r="K68" s="23" t="n">
         <v>125.11</v>
       </c>
-      <c r="L68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="14" t="n">
+      <c r="L68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="23" t="n">
         <v>31.95</v>
       </c>
-      <c r="N68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="13" t="inlineStr">
+      <c r="N68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="18" t="inlineStr">
         <is>
           <t>Uso e consumo (suprimento de impressora) [NCM 84439923]</t>
         </is>
       </c>
-      <c r="P68" s="15" t="inlineStr"/>
-      <c r="Q68" s="15" t="inlineStr"/>
+      <c r="P68" s="16" t="inlineStr"/>
+      <c r="Q68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -30730,8 +31566,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 6901]</t>
         </is>
       </c>
-      <c r="P69" s="15" t="inlineStr"/>
-      <c r="Q69" s="15" t="inlineStr"/>
+      <c r="P69" s="16" t="inlineStr"/>
+      <c r="Q69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -30793,71 +31629,71 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P70" s="15" t="inlineStr"/>
-      <c r="Q70" s="15" t="inlineStr"/>
+      <c r="P70" s="16" t="inlineStr"/>
+      <c r="Q70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="n">
+      <c r="A71" s="22" t="n">
         <v>46288</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="18" t="inlineStr">
         <is>
           <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="18" t="inlineStr">
         <is>
           <t>62514971000107</t>
         </is>
       </c>
-      <c r="D71" s="13" t="n">
+      <c r="D71" s="18" t="n">
         <v>141811</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="13" t="inlineStr">
+      <c r="F71" s="18" t="inlineStr">
         <is>
           <t>CASHMERE - 204510</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="G71" s="18" t="inlineStr">
         <is>
           <t>33029019</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
+      <c r="H71" s="18" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I71" s="13" t="inlineStr">
+      <c r="I71" s="18" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J71" s="14" t="n">
+      <c r="J71" s="23" t="n">
         <v>4794.99</v>
       </c>
-      <c r="K71" s="14" t="n">
+      <c r="K71" s="23" t="n">
         <v>557.29</v>
       </c>
-      <c r="L71" s="14" t="n">
+      <c r="L71" s="23" t="n">
         <v>557.29</v>
       </c>
-      <c r="M71" s="14" t="n">
+      <c r="M71" s="23" t="n">
         <v>150.93</v>
       </c>
-      <c r="N71" s="14" t="n">
+      <c r="N71" s="23" t="n">
         <v>150.93</v>
       </c>
-      <c r="O71" s="13" t="inlineStr">
+      <c r="O71" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (fragrância/essência) [NCM 33029019]</t>
         </is>
       </c>
-      <c r="P71" s="15" t="inlineStr"/>
-      <c r="Q71" s="15" t="inlineStr"/>
+      <c r="P71" s="16" t="inlineStr"/>
+      <c r="Q71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -30919,8 +31755,8 @@
           <t>Nota sem mercadoria (antecipação/financeira) [CFOP 6949 / NCM 00000000]</t>
         </is>
       </c>
-      <c r="P72" s="15" t="inlineStr"/>
-      <c r="Q72" s="15" t="inlineStr"/>
+      <c r="P72" s="16" t="inlineStr"/>
+      <c r="Q72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -30982,71 +31818,71 @@
           <t>Nota sem mercadoria (antecipação/financeira) [CFOP 6949 / NCM 00000000]</t>
         </is>
       </c>
-      <c r="P73" s="15" t="inlineStr"/>
-      <c r="Q73" s="15" t="inlineStr"/>
+      <c r="P73" s="16" t="inlineStr"/>
+      <c r="Q73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="n">
+      <c r="A74" s="22" t="n">
         <v>46294</v>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B74" s="18" t="inlineStr">
         <is>
           <t>CHEMYUNION LTDA</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C74" s="18" t="inlineStr">
         <is>
           <t>58309709000820</t>
         </is>
       </c>
-      <c r="D74" s="13" t="n">
+      <c r="D74" s="18" t="n">
         <v>19303</v>
       </c>
-      <c r="E74" s="13" t="n">
+      <c r="E74" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="13" t="inlineStr">
+      <c r="F74" s="18" t="inlineStr">
         <is>
           <t>Uniox C (20,000)</t>
         </is>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>34024200</t>
         </is>
       </c>
-      <c r="H74" s="13" t="inlineStr">
+      <c r="H74" s="18" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I74" s="13" t="inlineStr">
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J74" s="14" t="n">
+      <c r="J74" s="23" t="n">
         <v>8747.379999999999</v>
       </c>
-      <c r="K74" s="14" t="n">
+      <c r="K74" s="23" t="n">
         <v>1016.64</v>
       </c>
-      <c r="L74" s="14" t="n">
+      <c r="L74" s="23" t="n">
         <v>1016.64</v>
       </c>
-      <c r="M74" s="14" t="n">
+      <c r="M74" s="23" t="n">
         <v>275.34</v>
       </c>
-      <c r="N74" s="14" t="n">
+      <c r="N74" s="23" t="n">
         <v>275.34</v>
       </c>
-      <c r="O74" s="13" t="inlineStr">
+      <c r="O74" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (tensoativo) [NCM 34024200]</t>
         </is>
       </c>
-      <c r="P74" s="15" t="inlineStr"/>
-      <c r="Q74" s="15" t="inlineStr"/>
+      <c r="P74" s="16" t="inlineStr"/>
+      <c r="Q74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -31108,8 +31944,8 @@
           <t>Matéria-prima (óleos e gorduras) [NCM 15159090]</t>
         </is>
       </c>
-      <c r="P75" s="15" t="inlineStr"/>
-      <c r="Q75" s="15" t="inlineStr"/>
+      <c r="P75" s="16" t="inlineStr"/>
+      <c r="Q75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -31171,8 +32007,8 @@
           <t>Embalagem (rótulo/etiqueta) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P76" s="15" t="inlineStr"/>
-      <c r="Q76" s="15" t="inlineStr"/>
+      <c r="P76" s="16" t="inlineStr"/>
+      <c r="Q76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -31234,8 +32070,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 6901]</t>
         </is>
       </c>
-      <c r="P77" s="15" t="inlineStr"/>
-      <c r="Q77" s="15" t="inlineStr"/>
+      <c r="P77" s="16" t="inlineStr"/>
+      <c r="Q77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -31297,71 +32133,71 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P78" s="15" t="inlineStr"/>
-      <c r="Q78" s="15" t="inlineStr"/>
+      <c r="P78" s="16" t="inlineStr"/>
+      <c r="Q78" s="16" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="n">
+      <c r="A79" s="22" t="n">
         <v>46294</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
+      <c r="B79" s="18" t="inlineStr">
         <is>
           <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C79" s="18" t="inlineStr">
         <is>
           <t>11340087000162</t>
         </is>
       </c>
-      <c r="D79" s="13" t="n">
+      <c r="D79" s="18" t="n">
         <v>42285</v>
       </c>
-      <c r="E79" s="13" t="n">
+      <c r="E79" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="F79" s="18" t="inlineStr">
         <is>
           <t>KERANUTRI</t>
         </is>
       </c>
-      <c r="G79" s="13" t="inlineStr">
+      <c r="G79" s="18" t="inlineStr">
         <is>
           <t>38249989</t>
         </is>
       </c>
-      <c r="H79" s="13" t="inlineStr">
+      <c r="H79" s="18" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I79" s="13" t="inlineStr">
+      <c r="I79" s="18" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J79" s="14" t="n">
+      <c r="J79" s="23" t="n">
         <v>4278.84</v>
       </c>
-      <c r="K79" s="14" t="n">
+      <c r="K79" s="23" t="n">
         <v>160.71</v>
       </c>
-      <c r="L79" s="14" t="n">
+      <c r="L79" s="23" t="n">
         <v>160.71</v>
       </c>
-      <c r="M79" s="14" t="n">
+      <c r="M79" s="23" t="n">
         <v>261.15</v>
       </c>
-      <c r="N79" s="14" t="n">
+      <c r="N79" s="23" t="n">
         <v>261.15</v>
       </c>
-      <c r="O79" s="13" t="inlineStr">
+      <c r="O79" s="18" t="inlineStr">
         <is>
           <t>Matéria-prima (preparação química) [NCM 38249989]</t>
         </is>
       </c>
-      <c r="P79" s="15" t="inlineStr"/>
-      <c r="Q79" s="15" t="inlineStr"/>
+      <c r="P79" s="16" t="inlineStr"/>
+      <c r="Q79" s="16" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -31423,8 +32259,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P80" s="15" t="inlineStr"/>
-      <c r="Q80" s="15" t="inlineStr"/>
+      <c r="P80" s="16" t="inlineStr"/>
+      <c r="Q80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -31486,8 +32322,8 @@
           <t>Matéria-prima (químico inorgânico) [NCM 28321010]</t>
         </is>
       </c>
-      <c r="P81" s="15" t="inlineStr"/>
-      <c r="Q81" s="15" t="inlineStr"/>
+      <c r="P81" s="16" t="inlineStr"/>
+      <c r="Q81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -31549,8 +32385,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P82" s="15" t="inlineStr"/>
-      <c r="Q82" s="15" t="inlineStr"/>
+      <c r="P82" s="16" t="inlineStr"/>
+      <c r="Q82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -31612,8 +32448,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P83" s="15" t="inlineStr"/>
-      <c r="Q83" s="15" t="inlineStr"/>
+      <c r="P83" s="16" t="inlineStr"/>
+      <c r="Q83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -31675,8 +32511,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P84" s="15" t="inlineStr"/>
-      <c r="Q84" s="15" t="inlineStr"/>
+      <c r="P84" s="16" t="inlineStr"/>
+      <c r="Q84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -31738,8 +32574,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P85" s="15" t="inlineStr"/>
-      <c r="Q85" s="15" t="inlineStr"/>
+      <c r="P85" s="16" t="inlineStr"/>
+      <c r="Q85" s="16" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -31790,13 +32626,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -31811,6 +32647,8 @@
     <col width="6" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31881,6 +32719,16 @@
           <t>Crédito</t>
         </is>
       </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>NF-e transportada</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Análise</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -31927,7 +32775,17 @@
         <v>36.18</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>36.18</v>
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>NF 2564 (outras)</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Frete de compra de outras: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -31977,6 +32835,16 @@
       <c r="L5" s="6" t="n">
         <v>13.92</v>
       </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>NF 30338 (insumo)</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Frete de compra de insumo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -32025,6 +32893,16 @@
       <c r="L6" s="6" t="n">
         <v>97.48</v>
       </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>NF 117690 (insumo)</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Frete de compra de insumo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -32073,6 +32951,16 @@
       <c r="L7" s="6" t="n">
         <v>15.12</v>
       </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>NF 141811 (insumo)</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Frete de compra de insumo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -32120,6 +33008,16 @@
       </c>
       <c r="L8" s="6" t="n">
         <v>22.62</v>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>NF 19303 (insumo)</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Frete de compra de insumo</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -32160,13 +33058,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -32230,777 +33128,1868 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Contribuinte como consumidor final</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>GULA COSMETICOS LTDA (30415972000108, IE 9084324601)</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>16 nota(s) com indIEDest=9/indFinal=1 (NF 8966, 8967, 8968, 8969, 8978, 8980, 8981, 8982, 9003, 9006, 9009, 9011, 9013, 9014, 9018, 9019; CFOP 5101, 5102, 6102), sem ICMS-ST, ICMS cheio e IPI na base do ICMS; nas 1 nota(s) do mês como contribuinte houve ST de R$ 865.16. Se o cliente revende, a ST não foi retida - confirmar o cadastro/finalidade com o cliente</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>35221.15</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Destinatário x UF</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>GULA COSMETICOS LTDA (30415972000108)</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Mesmo CNPJ com endereço em UFs diferentes no mês: PR: NF 8955, 8968, 8969, 8978, 8980, 8981, 8982, 9003, 9006, 9009, 9011, 9013, 9014, 9018, 9019; SP: NF 8966, 8967 - CFOP 6xxx e DIFAL dependem da UF; conferir o cadastro</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Industrialização x retorno</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>NF 8989/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 8993 (5902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>600</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Industrialização x retorno</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>NF 8999/1 22/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9005 (6902). Retorno de insumo é 5902/6902; como está, R$ 948.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>948</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Industrialização x retorno</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>NF 9000/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9002 (5902). Retorno de insumo é 5902/6902; como está, R$ 556.50 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Industrialização x retorno</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>NF 9020/1 29/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9026 (6902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>600</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Industrialização x retorno</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>NF 9021/1 29/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9024 (5902). Retorno de insumo é 5902/6902; como está, R$ 300.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>NF 8967/1 11/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>1 item(ns) com CFOP 6102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>NF 8969/1 14/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>811.99</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>NF 8978/1 16/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>9 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>1698.59</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>19 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>11620.79</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>NF 8981/1 17/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>1691.57</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr"/>
+      <c r="G16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>NF 8982/1 18/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>6901.45</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>NF 9003/1 23/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>4 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>156.77</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>NF 9006/1 23/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>302.73</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>NF 9009/1 23/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>5 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>1529.47</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>NF 9013/1 28/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>618.45</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>NF 9014/1 28/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>148.13</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>NF 9018/1 29/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="n">
+        <v>139.49</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>CFOP revenda x produção</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>NF 9019/1 29/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>41 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="n">
+        <v>6020.39</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>CT-e sem crédito</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>CT-e 5597996 CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Frete de compra de outras: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="F25" s="16" t="inlineStr"/>
+      <c r="G25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Diferimento 5124</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>5124 para PR com CST 00 (ICMS R$ 108.44) enquanto 35 itens 5124 do mês saíram com diferimento (CST 51). Conferir se o diferimento se aplica a este cliente</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="n">
+        <v>108.44</v>
+      </c>
+      <c r="F26" s="16" t="inlineStr"/>
+      <c r="G26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>ALTEC IND.COM.IMP.E EXP.LTDA. (67598292000187)</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="15" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="16" t="inlineStr"/>
+      <c r="G27" s="16" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>BISPHARMA EMBALAGENS LTDA (59610485000188)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="15" t="inlineStr"/>
-      <c r="G6" s="15" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="16" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>CHEMYUNION LTDA (58309709000820)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="15" t="inlineStr"/>
-      <c r="G7" s="15" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="16" t="inlineStr"/>
+      <c r="G29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA (04993269000177)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="15" t="inlineStr"/>
-      <c r="G8" s="15" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="16" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="15" t="inlineStr"/>
-      <c r="G9" s="15" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="16" t="inlineStr"/>
+      <c r="G31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>HS INKLASER LTDA (18858535000163)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="15" t="inlineStr"/>
-      <c r="G10" s="15" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="16" t="inlineStr"/>
+      <c r="G32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>Lunaflexo Tecnologia Adesiva Eireli (06015875000143)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="15" t="inlineStr"/>
-      <c r="G11" s="15" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="16" t="inlineStr"/>
+      <c r="G33" s="16" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>MCASSAB COMERCIO E INDUSTRIA LTDA (49698723003110)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="15" t="inlineStr"/>
-      <c r="G12" s="15" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="16" t="inlineStr"/>
+      <c r="G34" s="16" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="15" t="inlineStr"/>
-      <c r="G13" s="15" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="16" t="inlineStr"/>
+      <c r="G35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA (11340087000162)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="15" t="inlineStr"/>
-      <c r="G14" s="15" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="16" t="inlineStr"/>
+      <c r="G36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="15" t="inlineStr"/>
-      <c r="G15" s="15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="16" t="inlineStr"/>
+      <c r="G37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Industrialização sem insumo</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 39.61) e IPI tributado</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="n">
+        <v>556.05</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr"/>
+      <c r="G38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Industrialização sem insumo</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>NF 8979/1 17/09 BARBARA KAROLAINY DE SOUZA SILVA</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 337.29) e IPI tributado</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>4098</v>
+      </c>
+      <c r="F39" s="16" t="inlineStr"/>
+      <c r="G39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>NFS-e retenções</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>NFS-e 18 01/09/2026 GENESIS ALIANCA</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Serviço 0401 (medicina) de R$ 728.14, prestador fora do Simples: reter IRRF 1.5% R$ 10.92 + PIS/COFINS/CSLL 4,65% R$ 33.86 = R$ 44.78; descontado na nota R$ 10.92 (diferença R$ 33.86). Conferir pagamento e DARF 1708/5952</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F40" s="16" t="inlineStr"/>
+      <c r="G40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>VOLUMES: 4 CAIXAS</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="15" t="inlineStr"/>
-      <c r="G16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="16" t="inlineStr"/>
+      <c r="G41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="15" t="inlineStr"/>
-      <c r="G17" s="15" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="16" t="inlineStr"/>
+      <c r="G42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="15" t="inlineStr"/>
-      <c r="G18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="16" t="inlineStr"/>
+      <c r="G43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="15" t="inlineStr"/>
-      <c r="G19" s="15" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="16" t="inlineStr"/>
+      <c r="G44" s="16" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="15" t="inlineStr"/>
-      <c r="G20" s="15" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="16" t="inlineStr"/>
+      <c r="G45" s="16" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="15" t="inlineStr"/>
-      <c r="G21" s="15" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="16" t="inlineStr"/>
+      <c r="G46" s="16" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="15" t="inlineStr"/>
-      <c r="G22" s="15" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="16" t="inlineStr"/>
+      <c r="G47" s="16" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="15" t="inlineStr"/>
-      <c r="G23" s="15" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="16" t="inlineStr"/>
+      <c r="G48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="15" t="inlineStr"/>
-      <c r="G24" s="15" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="16" t="inlineStr"/>
+      <c r="G49" s="16" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="15" t="inlineStr"/>
-      <c r="G25" s="15" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="16" t="inlineStr"/>
+      <c r="G50" s="16" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="15" t="inlineStr"/>
-      <c r="G26" s="15" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="16" t="inlineStr"/>
+      <c r="G51" s="16" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="15" t="inlineStr"/>
-      <c r="G27" s="15" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="D52" s="20" t="inlineStr"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="16" t="inlineStr"/>
+      <c r="G52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D53" s="20" t="inlineStr">
         <is>
           <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="15" t="inlineStr"/>
-      <c r="G28" s="15" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="16" t="inlineStr"/>
+      <c r="G53" s="16" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="15" t="inlineStr"/>
-      <c r="G29" s="15" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D54" s="20" t="inlineStr"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="16" t="inlineStr"/>
+      <c r="G54" s="16" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D55" s="20" t="inlineStr">
         <is>
           <t>PESO BRUTO: 300,000</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="15" t="inlineStr"/>
-      <c r="G30" s="15" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="16" t="inlineStr"/>
+      <c r="G55" s="16" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="15" t="inlineStr"/>
-      <c r="G31" s="15" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="D56" s="20" t="inlineStr"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="16" t="inlineStr"/>
+      <c r="G56" s="16" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D57" s="20" t="inlineStr">
         <is>
           <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="15" t="inlineStr"/>
-      <c r="G32" s="15" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="16" t="inlineStr"/>
+      <c r="G57" s="16" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="15" t="inlineStr"/>
-      <c r="G33" s="15" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="D58" s="20" t="inlineStr"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="16" t="inlineStr"/>
+      <c r="G58" s="16" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D59" s="20" t="inlineStr">
         <is>
           <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="15" t="inlineStr"/>
-      <c r="G34" s="15" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="16" t="inlineStr"/>
+      <c r="G59" s="16" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>BAIXA</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Carta de correção</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="15" t="inlineStr"/>
-      <c r="G35" s="15" t="inlineStr"/>
+      <c r="D60" s="20" t="inlineStr"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="16" t="inlineStr"/>
+      <c r="G60" s="16" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Grupo IPI</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="16" t="inlineStr"/>
+      <c r="G61" s="16" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Grupo IPI</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="16" t="inlineStr"/>
+      <c r="G62" s="16" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Grupo IPI</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="16" t="inlineStr"/>
+      <c r="G63" s="16" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Industrialização x retorno</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - corrigir por CC-e</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="16" t="inlineStr"/>
+      <c r="G64" s="16" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>NFS-e retenções</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>NFS-e 9227 01/09/2026 PLUS SANTE</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>Serviço 0421 (atendimento médico móvel) de R$ 342.30: confirmar se há retenção de IRRF/CSRF; descontado R$ 0.00</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="16" t="inlineStr"/>
+      <c r="G65" s="16" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>5700</v>
+      </c>
+      <c r="F66" s="16" t="inlineStr"/>
+      <c r="G66" s="16" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F67" s="16" t="inlineStr"/>
+      <c r="G67" s="16" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="F68" s="16" t="inlineStr"/>
+      <c r="G68" s="16" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1964</v>
+      </c>
+      <c r="F69" s="16" t="inlineStr"/>
+      <c r="G69" s="16" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>5670</v>
+      </c>
+      <c r="F70" s="16" t="inlineStr"/>
+      <c r="G70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>2136</v>
+      </c>
+      <c r="F71" s="16" t="inlineStr"/>
+      <c r="G71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>1112</v>
+      </c>
+      <c r="F72" s="16" t="inlineStr"/>
+      <c r="G72" s="16" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>667.2</v>
+      </c>
+      <c r="F73" s="16" t="inlineStr"/>
+      <c r="G73" s="16" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>2420.01</v>
+      </c>
+      <c r="F74" s="16" t="inlineStr"/>
+      <c r="G74" s="16" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="F75" s="16" t="inlineStr"/>
+      <c r="G75" s="16" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>1408.12</v>
+      </c>
+      <c r="F76" s="16" t="inlineStr"/>
+      <c r="G76" s="16" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>2462.03</v>
+      </c>
+      <c r="F77" s="16" t="inlineStr"/>
+      <c r="G77" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="140" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pontos para a contadora decidir (não alteram a apuração sem confirmação)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>1. Vendas de NCM fora da lista monofásica (Lei 10.147/2000, art. 1º, I, b) somam R$ 5,475.65 e estão na base de 2,2%/10,3%, como na planilha de 08/2026: 28470000 (R$ 5,475.65). Se forem tributadas a 0,65%/3%, a diferença é PIS R$ 84.87 e COFINS R$ 399.72 a menor. Confirmar com a contadora.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33011,268 +35000,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notas canceladas e números inutilizados no mês</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Número</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Série</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Emissão</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Destinatário/Emitente</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Chave</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Cancelada</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>8940</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>46267</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>R&amp;S COMERCIO DE COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>7368</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>41260933039048000162550010000089401000115920</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Cancelada</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>8952</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>GUIDI COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>6307.1</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>41260933039048000162550010000089521000162996</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Cancelada (fornecedor)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>794</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>46274</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>YAHWEH PRINT BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>4370.44</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>41260952680145000184550010000007941049258979</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Inutilizada</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>8938</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Inutilizada</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>8948</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Inutilizada</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>8951</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Inutilizada</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>8956</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Inutilizada</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>8965</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Inutilizada</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>8972</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="inlineStr"/>
+          <t>Pontos para a contadora decidir (não alteram a apuração sem confirmação)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>1. Vendas de NCM fora da lista monofásica (Lei 10.147/2000, art. 1º, I, b) somam R$ 5,475.65 e estão na base de 2,2%/10,3%, como na planilha de 08/2026: 28470000 (R$ 5,475.65). Se forem tributadas a 0,65%/3%, a diferença é PIS R$ 84.87 e COFINS R$ 399.72 a menor. Confirmar com a contadora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>2. Insumo de cliente emitido com CFOP 5124/6124 soma R$ 3,004.50 (aba Divergências, "Industrialização x retorno"). Está na base do PIS/COFINS (0,65%/3% = R$ 19.53 + R$ 90.13) e do IRPJ/CSLL. Se a contadora confirmar que é retorno em duplicidade, tirar da base e pedir ao cliente a regularização (CC-e do CFOP não altera valores - Ajuste SINIEF 01/07; senão, nota de entrada/anulação conforme RICMS/PR).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B67" s="13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
@@ -1609,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1934,116 +1934,116 @@
       <c r="G13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>NCM x PIS/COFINS monofásico</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Nenhuma ocorrência</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Lei 10.147/2000</t>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Mesmo produto com NCM/IPI diferentes no mês</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>1 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>TIPI (Decreto 11.158/2022); RIPI art. 189</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr"/>
       <c r="G14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Entradas</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico (insumo x uso e consumo)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>11 MÉDIA (aba Divergências)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>LC 87/96 art. 20 e 33, I</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>PIS/COFINS informado no XML x apuração</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>1 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Lei 10.147/2000; Lei 11.051/2004 art. 10</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr"/>
       <c r="G15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Entradas</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>Notas desconhecidas/manifestadas</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Nenhuma ocorrência</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>Ajuste SINIEF 07/05</t>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>XML x Registro de Saídas do ERP (nota a nota: UF, CFOP, valores, ICMS, IPI, ST)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>2 ALTA, 1 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Ajuste SINIEF 02/09 (EFD)</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr"/>
       <c r="G16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Entradas</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Remessas recebidas sem retorno (estoque de terceiros)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>12 BAIXA (aba Divergências)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>INFORMATIVO</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>RICMS/PR (industrialização por encomenda)</t>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Saídas</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>NCM x PIS/COFINS monofásico</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Lei 10.147/2000</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr"/>
@@ -2052,17 +2052,17 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>CT-e</t>
+          <t>Entradas</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Crédito do frete segue a natureza da NF-e transportada</t>
+          <t>Fornecedor sem histórico (insumo x uso e consumo)</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>1 MÉDIA (aba Divergências)</t>
+          <t>11 MÉDIA (aba Divergências)</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -2079,62 +2079,149 @@
       <c r="G18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Serviços</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>NFS-e tomadas: retenção de IRRF e PIS/COFINS/CSLL</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>1 MÉDIA, 1 BAIXA (aba Divergências)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>Lei 10.833/2003 art. 30 e 31 §3º (dispensa até R$ 10); RIR/2018 art. 714 e 716; IN SRF 459/2004</t>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Entradas</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Notas desconhecidas/manifestadas</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Ajuste SINIEF 07/05</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr"/>
       <c r="G19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>SPED</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>XML x SPED (notas faltando de um lado ou do outro)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>SPED do mês ainda não existe</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>NÃO EXECUTADO</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>Guia Prático EFD ICMS/IPI</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Entradas</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Remessas recebidas sem retorno (estoque de terceiros)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>12 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>RICMS/PR (industrialização por encomenda)</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr"/>
       <c r="G20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>CT-e</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Crédito do frete segue a natureza da NF-e transportada</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>1 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>LC 87/96 art. 20 e 33, I</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>NFS-e tomadas: retenção de IRRF e PIS/COFINS/CSLL</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>1 MÉDIA, 1 BAIXA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>VERIFICAR</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Lei 10.833/2003 art. 30 e 31 §3º (dispensa até R$ 10); RIR/2018 art. 714 e 716; IN SRF 459/2004</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>SPED</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>XML x SPED (notas faltando de um lado ou do outro)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>SPED do mês ainda não existe</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>NÃO EXECUTADO</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Guia Prático EFD ICMS/IPI</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33064,7 +33151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33315,56 +33402,52 @@
       <c r="G11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>CFOP revenda x produção</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>NF 8967/1 11/09 GULA COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>1 item(ns) com CFOP 6102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>370.33</v>
-      </c>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>XML x Registro ERP</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>NF 8966/1 10/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>UF no XML SP x ERP PR</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n"/>
       <c r="F12" s="16" t="inlineStr"/>
       <c r="G12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>CFOP revenda x produção</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>NF 8969/1 14/09 GULA COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>811.99</v>
-      </c>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>XML x Registro ERP</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>NF 8967/1 11/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>UF no XML SP x ERP PR</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n"/>
       <c r="F13" s="16" t="inlineStr"/>
       <c r="G13" s="16" t="inlineStr"/>
     </row>
@@ -33381,16 +33464,16 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>NF 8978/1 16/09 GULA COSMETICOS LTDA</t>
+          <t>NF 8967/1 11/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>9 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>1 item(ns) com CFOP 6102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E14" s="23" t="n">
-        <v>1698.59</v>
+        <v>370.33</v>
       </c>
       <c r="F14" s="16" t="inlineStr"/>
       <c r="G14" s="16" t="inlineStr"/>
@@ -33408,16 +33491,16 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
+          <t>NF 8969/1 14/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>19 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E15" s="23" t="n">
-        <v>11620.79</v>
+        <v>811.99</v>
       </c>
       <c r="F15" s="16" t="inlineStr"/>
       <c r="G15" s="16" t="inlineStr"/>
@@ -33435,16 +33518,16 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>NF 8981/1 17/09 GULA COSMETICOS LTDA</t>
+          <t>NF 8978/1 16/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>9 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E16" s="23" t="n">
-        <v>1691.57</v>
+        <v>1698.59</v>
       </c>
       <c r="F16" s="16" t="inlineStr"/>
       <c r="G16" s="16" t="inlineStr"/>
@@ -33462,16 +33545,16 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>NF 8982/1 18/09 GULA COSMETICOS LTDA</t>
+          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>19 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E17" s="23" t="n">
-        <v>6901.45</v>
+        <v>11620.79</v>
       </c>
       <c r="F17" s="16" t="inlineStr"/>
       <c r="G17" s="16" t="inlineStr"/>
@@ -33489,16 +33572,16 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>NF 9003/1 23/09 GULA COSMETICOS LTDA</t>
+          <t>NF 8981/1 17/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>4 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E18" s="23" t="n">
-        <v>156.77</v>
+        <v>1691.57</v>
       </c>
       <c r="F18" s="16" t="inlineStr"/>
       <c r="G18" s="16" t="inlineStr"/>
@@ -33516,7 +33599,7 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>NF 9006/1 23/09 GULA COSMETICOS LTDA</t>
+          <t>NF 8982/1 18/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -33525,7 +33608,7 @@
         </is>
       </c>
       <c r="E19" s="23" t="n">
-        <v>302.73</v>
+        <v>6901.45</v>
       </c>
       <c r="F19" s="16" t="inlineStr"/>
       <c r="G19" s="16" t="inlineStr"/>
@@ -33543,16 +33626,16 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>NF 9009/1 23/09 GULA COSMETICOS LTDA</t>
+          <t>NF 9003/1 23/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>5 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>4 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>1529.47</v>
+        <v>156.77</v>
       </c>
       <c r="F20" s="16" t="inlineStr"/>
       <c r="G20" s="16" t="inlineStr"/>
@@ -33570,16 +33653,16 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>NF 9013/1 28/09 GULA COSMETICOS LTDA</t>
+          <t>NF 9006/1 23/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E21" s="23" t="n">
-        <v>618.45</v>
+        <v>302.73</v>
       </c>
       <c r="F21" s="16" t="inlineStr"/>
       <c r="G21" s="16" t="inlineStr"/>
@@ -33597,16 +33680,16 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>NF 9014/1 28/09 GULA COSMETICOS LTDA</t>
+          <t>NF 9009/1 23/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>5 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E22" s="23" t="n">
-        <v>148.13</v>
+        <v>1529.47</v>
       </c>
       <c r="F22" s="16" t="inlineStr"/>
       <c r="G22" s="16" t="inlineStr"/>
@@ -33624,16 +33707,16 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>NF 9018/1 29/09 GULA COSMETICOS LTDA</t>
+          <t>NF 9013/1 28/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E23" s="23" t="n">
-        <v>139.49</v>
+        <v>618.45</v>
       </c>
       <c r="F23" s="16" t="inlineStr"/>
       <c r="G23" s="16" t="inlineStr"/>
@@ -33651,16 +33734,16 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>NF 9019/1 29/09 GULA COSMETICOS LTDA</t>
+          <t>NF 9014/1 28/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>41 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E24" s="23" t="n">
-        <v>6020.39</v>
+        <v>148.13</v>
       </c>
       <c r="F24" s="16" t="inlineStr"/>
       <c r="G24" s="16" t="inlineStr"/>
@@ -33673,21 +33756,21 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>CT-e sem crédito</t>
+          <t>CFOP revenda x produção</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>CT-e 5597996 CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
+          <t>NF 9018/1 29/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>Frete de compra de outras: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
+          <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E25" s="23" t="n">
-        <v>36.18</v>
+        <v>139.49</v>
       </c>
       <c r="F25" s="16" t="inlineStr"/>
       <c r="G25" s="16" t="inlineStr"/>
@@ -33700,21 +33783,21 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Diferimento 5124</t>
+          <t>CFOP revenda x produção</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+          <t>NF 9019/1 29/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>5124 para PR com CST 00 (ICMS R$ 108.44) enquanto 35 itens 5124 do mês saíram com diferimento (CST 51). Conferir se o diferimento se aplica a este cliente</t>
+          <t>41 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
       <c r="E26" s="23" t="n">
-        <v>108.44</v>
+        <v>6020.39</v>
       </c>
       <c r="F26" s="16" t="inlineStr"/>
       <c r="G26" s="16" t="inlineStr"/>
@@ -33727,20 +33810,22 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Fornecedor sem histórico</t>
+          <t>CT-e sem crédito</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>ALTEC IND.COM.IMP.E EXP.LTDA. (67598292000187)</t>
+          <t>CT-e 5597996 CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="n"/>
+          <t>Frete de compra de outras: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="n">
+        <v>36.18</v>
+      </c>
       <c r="F27" s="16" t="inlineStr"/>
       <c r="G27" s="16" t="inlineStr"/>
     </row>
@@ -33752,20 +33837,22 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Fornecedor sem histórico</t>
+          <t>Diferimento 5124</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>BISPHARMA EMBALAGENS LTDA (59610485000188)</t>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="n"/>
+          <t>5124 para PR com CST 00 (ICMS R$ 108.44) enquanto 35 itens 5124 do mês saíram com diferimento (CST 51). Conferir se o diferimento se aplica a este cliente</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="n">
+        <v>108.44</v>
+      </c>
       <c r="F28" s="16" t="inlineStr"/>
       <c r="G28" s="16" t="inlineStr"/>
     </row>
@@ -33782,7 +33869,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>CHEMYUNION LTDA (58309709000820)</t>
+          <t>ALTEC IND.COM.IMP.E EXP.LTDA. (67598292000187)</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -33807,7 +33894,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA (04993269000177)</t>
+          <t>BISPHARMA EMBALAGENS LTDA (59610485000188)</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
@@ -33832,7 +33919,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
+          <t>CHEMYUNION LTDA (58309709000820)</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -33857,7 +33944,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>HS INKLASER LTDA (18858535000163)</t>
+          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA (04993269000177)</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
@@ -33882,7 +33969,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>Lunaflexo Tecnologia Adesiva Eireli (06015875000143)</t>
+          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -33907,7 +33994,7 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>MCASSAB COMERCIO E INDUSTRIA LTDA (49698723003110)</t>
+          <t>HS INKLASER LTDA (18858535000163)</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -33932,7 +34019,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
+          <t>Lunaflexo Tecnologia Adesiva Eireli (06015875000143)</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -33957,7 +34044,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA (11340087000162)</t>
+          <t>MCASSAB COMERCIO E INDUSTRIA LTDA (49698723003110)</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -33982,7 +34069,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
+          <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -34002,22 +34089,20 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Industrialização sem insumo</t>
+          <t>Fornecedor sem histórico</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA (11340087000162)</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 39.61) e IPI tributado</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="n">
-        <v>556.05</v>
-      </c>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="n"/>
       <c r="F38" s="16" t="inlineStr"/>
       <c r="G38" s="16" t="inlineStr"/>
     </row>
@@ -34029,22 +34114,20 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Industrialização sem insumo</t>
+          <t>Fornecedor sem histórico</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>NF 8979/1 17/09 BARBARA KAROLAINY DE SOUZA SILVA</t>
+          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 337.29) e IPI tributado</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>4098</v>
-      </c>
+          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="n"/>
       <c r="F39" s="16" t="inlineStr"/>
       <c r="G39" s="16" t="inlineStr"/>
     </row>
@@ -34056,93 +34139,101 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>NFS-e retenções</t>
+          <t>Industrialização sem insumo</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>NFS-e 18 01/09/2026 GENESIS ALIANCA</t>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>Serviço 0401 (medicina) de R$ 728.14, prestador fora do Simples: reter IRRF 1.5% R$ 10.92 + PIS/COFINS/CSLL 4,65% R$ 33.86 = R$ 44.78; descontado na nota R$ 10.92 (diferença R$ 33.86). Conferir pagamento e DARF 1708/5952</t>
+          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 39.61) e IPI tributado</t>
         </is>
       </c>
       <c r="E40" s="23" t="n">
-        <v>33.86</v>
+        <v>556.05</v>
       </c>
       <c r="F40" s="16" t="inlineStr"/>
       <c r="G40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Carta de correção</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr">
-        <is>
-          <t>VOLUMES: 4 CAIXAS</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="n"/>
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Industrialização sem insumo</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>NF 8979/1 17/09 BARBARA KAROLAINY DE SOUZA SILVA</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 337.29) e IPI tributado</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>4098</v>
+      </c>
       <c r="F41" s="16" t="inlineStr"/>
       <c r="G41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Carta de correção</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="inlineStr"/>
-      <c r="E42" s="6" t="n"/>
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>NFS-e retenções</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>NFS-e 18 01/09/2026 GENESIS ALIANCA</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Serviço 0401 (medicina) de R$ 728.14, prestador fora do Simples: reter IRRF 1.5% R$ 10.92 + PIS/COFINS/CSLL 4,65% R$ 33.86 = R$ 44.78; descontado na nota R$ 10.92 (diferença R$ 33.86). Conferir pagamento e DARF 1708/5952</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>33.86</v>
+      </c>
       <c r="F42" s="16" t="inlineStr"/>
       <c r="G42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Carta de correção</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="inlineStr">
-        <is>
-          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="n"/>
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>MÉDIA</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Produto com tratamento diferente</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>NEUTRALIZANTE ALL NATURE - 500ML (cód. 51)</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Mesmo produto vendido no mês com NCM/IPI diferentes: NCM 33059000 IPI CST 51 0% (NF 8966); NCM 33059000 IPI CST 50 14.3% (NF 8980) - conferir o cadastro do produto (IPI a menor se a alíquota correta for a maior)</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="n"/>
       <c r="F43" s="16" t="inlineStr"/>
       <c r="G43" s="16" t="inlineStr"/>
     </row>
@@ -34159,10 +34250,14 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr"/>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>VOLUMES: 4 CAIXAS</t>
+        </is>
+      </c>
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="16" t="inlineStr"/>
       <c r="G44" s="16" t="inlineStr"/>
@@ -34180,14 +34275,10 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
-        </is>
-      </c>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr"/>
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="16" t="inlineStr"/>
       <c r="G45" s="16" t="inlineStr"/>
@@ -34205,10 +34296,14 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr"/>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
+        </is>
+      </c>
       <c r="E46" s="6" t="n"/>
       <c r="F46" s="16" t="inlineStr"/>
       <c r="G46" s="16" t="inlineStr"/>
@@ -34226,14 +34321,10 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr">
-        <is>
-          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
-        </is>
-      </c>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr"/>
       <c r="E47" s="6" t="n"/>
       <c r="F47" s="16" t="inlineStr"/>
       <c r="G47" s="16" t="inlineStr"/>
@@ -34251,10 +34342,14 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="inlineStr"/>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
+        </is>
+      </c>
       <c r="E48" s="6" t="n"/>
       <c r="F48" s="16" t="inlineStr"/>
       <c r="G48" s="16" t="inlineStr"/>
@@ -34272,14 +34367,10 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
-        </is>
-      </c>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr"/>
       <c r="E49" s="6" t="n"/>
       <c r="F49" s="16" t="inlineStr"/>
       <c r="G49" s="16" t="inlineStr"/>
@@ -34297,10 +34388,14 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="inlineStr"/>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
+        </is>
+      </c>
       <c r="E50" s="6" t="n"/>
       <c r="F50" s="16" t="inlineStr"/>
       <c r="G50" s="16" t="inlineStr"/>
@@ -34318,14 +34413,10 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="inlineStr">
-        <is>
-          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
-        </is>
-      </c>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr"/>
       <c r="E51" s="6" t="n"/>
       <c r="F51" s="16" t="inlineStr"/>
       <c r="G51" s="16" t="inlineStr"/>
@@ -34343,10 +34434,14 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="inlineStr"/>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
+        </is>
+      </c>
       <c r="E52" s="6" t="n"/>
       <c r="F52" s="16" t="inlineStr"/>
       <c r="G52" s="16" t="inlineStr"/>
@@ -34364,14 +34459,10 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
-        </is>
-      </c>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr"/>
       <c r="E53" s="6" t="n"/>
       <c r="F53" s="16" t="inlineStr"/>
       <c r="G53" s="16" t="inlineStr"/>
@@ -34389,10 +34480,14 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="inlineStr"/>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
+        </is>
+      </c>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="16" t="inlineStr"/>
       <c r="G54" s="16" t="inlineStr"/>
@@ -34410,14 +34505,10 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr">
-        <is>
-          <t>PESO BRUTO: 300,000</t>
-        </is>
-      </c>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr"/>
       <c r="E55" s="6" t="n"/>
       <c r="F55" s="16" t="inlineStr"/>
       <c r="G55" s="16" t="inlineStr"/>
@@ -34435,10 +34526,14 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr"/>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
+        </is>
+      </c>
       <c r="E56" s="6" t="n"/>
       <c r="F56" s="16" t="inlineStr"/>
       <c r="G56" s="16" t="inlineStr"/>
@@ -34456,14 +34551,10 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="inlineStr">
-        <is>
-          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
-        </is>
-      </c>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr"/>
       <c r="E57" s="6" t="n"/>
       <c r="F57" s="16" t="inlineStr"/>
       <c r="G57" s="16" t="inlineStr"/>
@@ -34481,10 +34572,14 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr"/>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>PESO BRUTO: 300,000</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n"/>
       <c r="F58" s="16" t="inlineStr"/>
       <c r="G58" s="16" t="inlineStr"/>
@@ -34502,14 +34597,10 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr">
-        <is>
-          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
-        </is>
-      </c>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr"/>
       <c r="E59" s="6" t="n"/>
       <c r="F59" s="16" t="inlineStr"/>
       <c r="G59" s="16" t="inlineStr"/>
@@ -34527,10 +34618,14 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr"/>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
+        </is>
+      </c>
       <c r="E60" s="6" t="n"/>
       <c r="F60" s="16" t="inlineStr"/>
       <c r="G60" s="16" t="inlineStr"/>
@@ -34543,19 +34638,15 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>Carta de correção</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr">
-        <is>
-          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
-        </is>
-      </c>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr"/>
       <c r="E61" s="6" t="n"/>
       <c r="F61" s="16" t="inlineStr"/>
       <c r="G61" s="16" t="inlineStr"/>
@@ -34568,17 +34659,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>Carta de correção</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
         </is>
       </c>
       <c r="E62" s="6" t="n"/>
@@ -34593,19 +34684,15 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>Carta de correção</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D63" s="20" t="inlineStr">
-        <is>
-          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
-        </is>
-      </c>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr"/>
       <c r="E63" s="6" t="n"/>
       <c r="F63" s="16" t="inlineStr"/>
       <c r="G63" s="16" t="inlineStr"/>
@@ -34618,17 +34705,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Industrialização x retorno</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - corrigir por CC-e</t>
+          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
       <c r="E64" s="6" t="n"/>
@@ -34643,17 +34730,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>NFS-e retenções</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>NFS-e 9227 01/09/2026 PLUS SANTE</t>
+          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>Serviço 0421 (atendimento médico móvel) de R$ 342.30: confirmar se há retenção de IRRF/CSRF; descontado R$ 0.00</t>
+          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
       <c r="E65" s="6" t="n"/>
@@ -34668,22 +34755,20 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Remessa sem retorno</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
+          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>5700</v>
-      </c>
+          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n"/>
       <c r="F66" s="16" t="inlineStr"/>
       <c r="G66" s="16" t="inlineStr"/>
     </row>
@@ -34695,22 +34780,20 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Remessa sem retorno</t>
+          <t>Industrialização x retorno</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
+          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>65</v>
-      </c>
+          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - corrigir por CC-e</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n"/>
       <c r="F67" s="16" t="inlineStr"/>
       <c r="G67" s="16" t="inlineStr"/>
     </row>
@@ -34722,22 +34805,20 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Remessa sem retorno</t>
+          <t>NFS-e retenções</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NFS-e 9227 01/09/2026 PLUS SANTE</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>600</v>
-      </c>
+          <t>Serviço 0421 (atendimento médico móvel) de R$ 342.30: confirmar se há retenção de IRRF/CSRF; descontado R$ 0.00</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n"/>
       <c r="F68" s="16" t="inlineStr"/>
       <c r="G68" s="16" t="inlineStr"/>
     </row>
@@ -34749,22 +34830,20 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Remessa sem retorno</t>
+          <t>PIS/COFINS no XML</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>35 notas 5124/6124</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>1964</v>
-      </c>
+          <t>O XML informa PIS/COFINS monofásico (CST 02, 2.2%) em R$ 115,057.65 de industrialização (PIS R$ 2,531.30 / COFINS R$ 11,850.96); a apuração usa 0,65%/3% sobre a industrialização, como nos DARFs pagos. Na encomenda de produto monofásico a alíquota concentrada é do encomendante (Lei 11.051/2004, art. 10) - corrigir o cadastro fiscal do ERP (CST 01) e confirmar o entendimento com a contadora</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n"/>
       <c r="F69" s="16" t="inlineStr"/>
       <c r="G69" s="16" t="inlineStr"/>
     </row>
@@ -34781,16 +34860,16 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5670</v>
+        <v>5700</v>
       </c>
       <c r="F70" s="16" t="inlineStr"/>
       <c r="G70" s="16" t="inlineStr"/>
@@ -34808,16 +34887,16 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>2136</v>
+        <v>65</v>
       </c>
       <c r="F71" s="16" t="inlineStr"/>
       <c r="G71" s="16" t="inlineStr"/>
@@ -34835,16 +34914,16 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1112</v>
+        <v>600</v>
       </c>
       <c r="F72" s="16" t="inlineStr"/>
       <c r="G72" s="16" t="inlineStr"/>
@@ -34862,16 +34941,16 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>667.2</v>
+        <v>1964</v>
       </c>
       <c r="F73" s="16" t="inlineStr"/>
       <c r="G73" s="16" t="inlineStr"/>
@@ -34889,16 +34968,16 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>2420.01</v>
+        <v>5670</v>
       </c>
       <c r="F74" s="16" t="inlineStr"/>
       <c r="G74" s="16" t="inlineStr"/>
@@ -34916,16 +34995,16 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>1760</v>
+        <v>2136</v>
       </c>
       <c r="F75" s="16" t="inlineStr"/>
       <c r="G75" s="16" t="inlineStr"/>
@@ -34943,16 +35022,16 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
+          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1408.12</v>
+        <v>1112</v>
       </c>
       <c r="F76" s="16" t="inlineStr"/>
       <c r="G76" s="16" t="inlineStr"/>
@@ -34970,23 +35049,158 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
+          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>2462.03</v>
+        <v>667.2</v>
       </c>
       <c r="F77" s="16" t="inlineStr"/>
       <c r="G77" s="16" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>2420.01</v>
+      </c>
+      <c r="F78" s="16" t="inlineStr"/>
+      <c r="G78" s="16" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="F79" s="16" t="inlineStr"/>
+      <c r="G79" s="16" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>1408.12</v>
+      </c>
+      <c r="F80" s="16" t="inlineStr"/>
+      <c r="G80" s="16" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Remessa sem retorno</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>2462.03</v>
+      </c>
+      <c r="F81" s="16" t="inlineStr"/>
+      <c r="G81" s="16" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>XML x Registro ERP</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>30 notas de retorno 5902/6902</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>O Registro de Saídas do ERP não lista as notas de retorno simbólico (R$ 13,253.13); no livro/SPED elas entram (C100/C190 com CFOP 5902/6902, sem débito) - conferir no Domínio</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>13253.13</v>
+      </c>
+      <c r="F82" s="16" t="inlineStr"/>
+      <c r="G82" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -128,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +147,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -534,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -636,7 +642,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2097.5</v>
+        <v>2065.55</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>46320</v>
@@ -654,7 +660,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>9996.190000000001</v>
+        <v>9957.17</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>46307</v>
@@ -1108,7 +1114,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>0</v>
+        <v>86.09</v>
       </c>
     </row>
     <row r="45">
@@ -1118,7 +1124,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>-6172.62</v>
+        <v>-6297.73</v>
       </c>
     </row>
     <row r="46">
@@ -1162,165 +1168,209 @@
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>ICMS-ST (substituto) por UF de destino</t>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Ajuste a debito PR000081: Diferencial de alíquota - uso e consumo/ativo de outra UF - R$ 86.09 (NF 2564 AGATHA INDUSTRIA DE MANUFATURADOS LTDA: 86.09)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>ICMS-ST retido - PR</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>865.16</v>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>ICMS antecipado - entradas interestaduais a 4% (importado): 8% da base</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>(-) ST de devoluções</t>
+          <t>NF 275966 MCASSAB COMERCIO E INDUSTRIA LTDA - TRANSCUTOL CG - TB 25 KG - base 3,873.74</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>-0</v>
+        <v>309.9</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>ICMS-ST a recolher PR</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n">
-        <v>865.16</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>IPI</t>
-        </is>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>NF 42285 PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA - KERANUTRI - base 4,017.69</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>321.42</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Total antecipado (guia própria; no SPED: E111 PR000080 débito + PR020212 crédito, E113 por nota)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>631.3200000000001</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Débitos (saídas)</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
-        <v>4403.24</v>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>ICMS-ST (substituto) por UF de destino</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>(-) Créditos (entradas)</t>
+          <t>ICMS-ST retido - PR</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>-2305.74</v>
+        <v>865.16</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>IPI a recolher (negativo = saldo credor)</t>
-        </is>
-      </c>
-      <c r="B59" s="9">
-        <f>B57+B58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Conferência dos documentos</t>
-        </is>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>(-) ST de devoluções</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ICMS-ST a recolher PR</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>865.16</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Notas de saída autorizadas</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n">
-        <v>91</v>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Notas canceladas (saída e entrada)</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="n">
-        <v>3</v>
+          <t>Débitos (saídas)</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>4403.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Números inutilizados</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>6</v>
+          <t>(-) Créditos (entradas)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>-2337.69</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Notas de entrada</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>CT-e tomados</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>5</v>
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>IPI a recolher (negativo = saldo credor)</t>
+        </is>
+      </c>
+      <c r="B65" s="9">
+        <f>B63+B64</f>
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Divergências ALTA</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="n">
-        <v>9</v>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Conferência dos documentos</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Divergências (total)</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>78</v>
+          <t>Notas de saída autorizadas</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
+          <t>Notas canceladas (saída e entrada)</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Números inutilizados</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Notas de entrada</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>CT-e tomados</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Divergências ALTA</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Divergências (total)</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>Observações para a contadora</t>
         </is>
       </c>
-      <c r="B69" s="11" t="n">
+      <c r="B75" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1673,236 +1723,236 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Numeração sequencial (buraco sem cancelamento/inutilização)</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Nenhuma ocorrência</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Ajuste SINIEF 07/05</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>ICMS e IPI recalculados (BC x alíquota) e CST x valor</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Nenhuma ocorrência</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>LC 87/96 art. 13; RIPI art. 190</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>CFOP x UF do destinatário e alíquota interestadual</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>1 ALTA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Res. Senado 22/89 e 13/12</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>CFOP com/sem ST x ST destacada</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Nenhuma ocorrência</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>RICMS/PR Anexo IX</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Contribuinte com IE tratado como consumidor final</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>1 ALTA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>LC 87/96 art. 6º e RICMS/PR Anexo IX (ST nas saídas para revenda); Ajuste SINIEF 07/05 (indIEDest/indFinal); LC 87/96 art. 13 §2º (IPI fora da base só entre contribuintes)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>CFOP de revenda (5102) em produto de fabricação própria</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>13 MÉDIA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Tabela CFOP (Ajuste SINIEF 07/01): 5101 produção do estabelecimento, 5102 mercadoria de terceiros; RIPI art. 35</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr"/>
+      <c r="F10" s="17" t="inlineStr"/>
+      <c r="G10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Industrialização 5124/6124 x retorno 5902/6902 x remessa do cliente</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>5 ALTA, 2 MÉDIA, 1 BAIXA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>RICMS/PR (industrialização por encomenda: 5124 pela industrialização + 5902 retorno simbólico do insumo); Lei 10.147/2000 (5124 fora do monofásico: 0,65%/3%)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Diferimento nas 5124 internas</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>1 MÉDIA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>RICMS/PR (diferimento)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1910,12 +1960,12 @@
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Grupo de IPI nos produtos</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>3 BAIXA (aba Divergências)</t>
         </is>
@@ -1925,42 +1975,42 @@
           <t>INFORMATIVO</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>RIPI/2010 (Decreto 7.212) - grupo IPI obrigatório para produto industrializado (NT 2016.002)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Mesmo produto com NCM/IPI diferentes no mês</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>1 MÉDIA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>TIPI (Decreto 11.158/2022); RIPI art. 189</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr"/>
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1968,12 +2018,12 @@
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>PIS/COFINS informado no XML x apuração</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>1 BAIXA (aba Divergências)</t>
         </is>
@@ -1983,129 +2033,129 @@
           <t>INFORMATIVO</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>Lei 10.147/2000; Lei 11.051/2004 art. 10</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
+      <c r="F15" s="17" t="inlineStr"/>
+      <c r="G15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>XML x Registro de Saídas do ERP (nota a nota: UF, CFOP, valores, ICMS, IPI, ST)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>2 ALTA, 1 BAIXA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Ajuste SINIEF 02/09 (EFD)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Saídas</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>NCM x PIS/COFINS monofásico</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Nenhuma ocorrência</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>Lei 10.147/2000</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Entradas</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico (insumo x uso e consumo)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>11 MÉDIA (aba Divergências)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>7 MÉDIA (aba Divergências)</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>LC 87/96 art. 20 e 33, I</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Entradas</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Notas desconhecidas/manifestadas</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Nenhuma ocorrência</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Ajuste SINIEF 07/05</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
+      <c r="F19" s="17" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2113,12 +2163,12 @@
           <t>Entradas</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Remessas recebidas sem retorno (estoque de terceiros)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>12 BAIXA (aba Divergências)</t>
         </is>
@@ -2128,100 +2178,100 @@
           <t>INFORMATIVO</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>RICMS/PR (industrialização por encomenda)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="16" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>CT-e</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Crédito do frete segue a natureza da NF-e transportada</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>1 MÉDIA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>LC 87/96 art. 20 e 33, I</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Serviços</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>NFS-e tomadas: retenção de IRRF e PIS/COFINS/CSLL</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>1 MÉDIA, 1 BAIXA (aba Divergências)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>VERIFICAR</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Lei 10.833/2003 art. 30 e 31 §3º (dispensa até R$ 10); RIR/2018 art. 714 e 716; IN SRF 459/2004</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="16" t="inlineStr"/>
+      <c r="F22" s="17" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>SPED</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>XML x SPED (notas faltando de um lado ou do outro)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>SPED do mês ainda não existe</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>NÃO EXECUTADO</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>Guia Prático EFD ICMS/IPI</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr"/>
+      <c r="G23" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27562,67 +27612,67 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n">
+      <c r="A5" s="7" t="n">
         <v>46266</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>04993269000177</t>
         </is>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="5" t="n">
         <v>41731</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>ALCOOL ETILICO 99 - ONU 1170 ETANOL (ALCOOL ETILICO) 3 GE II BOMBONA DIPANOL 99</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>22071010</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="6" t="n">
         <v>1870</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="6" t="n">
         <v>224.41</v>
       </c>
-      <c r="L5" s="23" t="n">
+      <c r="L5" s="6" t="n">
         <v>224.41</v>
       </c>
-      <c r="M5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="18" t="inlineStr">
-        <is>
-          <t>Matéria-prima (álcool etílico) [NCM 22071010]</t>
-        </is>
-      </c>
-      <c r="P5" s="16" t="inlineStr"/>
-      <c r="Q5" s="16" t="inlineStr"/>
+      <c r="M5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P5" s="17" t="inlineStr"/>
+      <c r="Q5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -27684,8 +27734,8 @@
           <t>Embalagem (rótulo adesivo) [NCM 39191090]</t>
         </is>
       </c>
-      <c r="P6" s="16" t="inlineStr"/>
-      <c r="Q6" s="16" t="inlineStr"/>
+      <c r="P6" s="17" t="inlineStr"/>
+      <c r="Q6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -27747,134 +27797,134 @@
           <t>Embalagem (rótulo adesivo) [NCM 39191090]</t>
         </is>
       </c>
-      <c r="P7" s="16" t="inlineStr"/>
-      <c r="Q7" s="16" t="inlineStr"/>
+      <c r="P7" s="17" t="inlineStr"/>
+      <c r="Q7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="19" t="n">
         <v>22837</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>SULFITO DE SODIO ANIDRO PA 1000G - CARBON</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>28321010</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="L8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18" t="inlineStr">
+      <c r="L8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
         <is>
           <t>Matéria-prima (químico inorgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P8" s="16" t="inlineStr"/>
-      <c r="Q8" s="16" t="inlineStr"/>
+      <c r="P8" s="17" t="inlineStr"/>
+      <c r="Q8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="19" t="n">
         <v>22837</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>PIROFOSFATO DE SODIO (TETRABASICO) DECAHIDRATADO PA 1000G - CARBON</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>28353920</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="L9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>Matéria-prima (químico inorgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P9" s="16" t="inlineStr"/>
-      <c r="Q9" s="16" t="inlineStr"/>
+      <c r="P9" s="17" t="inlineStr"/>
+      <c r="Q9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -27936,512 +27986,512 @@
           <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
         </is>
       </c>
-      <c r="P10" s="16" t="inlineStr"/>
-      <c r="Q10" s="16" t="inlineStr"/>
+      <c r="P10" s="17" t="inlineStr"/>
+      <c r="Q10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>Agar Triptico de soja (TSA) pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="24" t="n">
         <v>250.39</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="24" t="n">
         <v>48.83</v>
       </c>
-      <c r="L11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="L11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P11" s="16" t="inlineStr"/>
-      <c r="Q11" s="16" t="inlineStr"/>
+      <c r="P11" s="17" t="inlineStr"/>
+      <c r="Q11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>Agar Sabouraud Dextrose pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="J12" s="24" t="n">
         <v>222.56</v>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="24" t="n">
         <v>43.4</v>
       </c>
-      <c r="L12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18" t="inlineStr">
+      <c r="L12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P12" s="16" t="inlineStr"/>
-      <c r="Q12" s="16" t="inlineStr"/>
+      <c r="P12" s="17" t="inlineStr"/>
+      <c r="Q12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>Agar PCA pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="24" t="n">
         <v>35.06</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="24" t="n">
         <v>6.84</v>
       </c>
-      <c r="L13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
+      <c r="L13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P13" s="16" t="inlineStr"/>
-      <c r="Q13" s="16" t="inlineStr"/>
+      <c r="P13" s="17" t="inlineStr"/>
+      <c r="Q13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>Agar Mac Conkey pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I14" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J14" s="23" t="n">
+      <c r="J14" s="24" t="n">
         <v>35.15</v>
       </c>
-      <c r="K14" s="23" t="n">
+      <c r="K14" s="24" t="n">
         <v>6.85</v>
       </c>
-      <c r="L14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18" t="inlineStr">
+      <c r="L14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P14" s="16" t="inlineStr"/>
-      <c r="Q14" s="16" t="inlineStr"/>
+      <c r="P14" s="17" t="inlineStr"/>
+      <c r="Q14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>Agar Cetrimide pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="24" t="n">
         <v>226.01</v>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="24" t="n">
         <v>44.07</v>
       </c>
-      <c r="L15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="L15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P15" s="16" t="inlineStr"/>
-      <c r="Q15" s="16" t="inlineStr"/>
+      <c r="P15" s="17" t="inlineStr"/>
+      <c r="Q15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Agar Baird Parker pcte c/ 10 placas 90x15mm</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="I16" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="24" t="n">
         <v>317.89</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="24" t="n">
         <v>61.99</v>
       </c>
-      <c r="L16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="L16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P16" s="16" t="inlineStr"/>
-      <c r="Q16" s="16" t="inlineStr"/>
+      <c r="P16" s="17" t="inlineStr"/>
+      <c r="Q16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>Acquaplus I sachê c/ 10 testes</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I17" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="24" t="n">
         <v>915.08</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K17" s="24" t="n">
         <v>178.44</v>
       </c>
-      <c r="L17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="18" t="inlineStr">
+      <c r="L17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P17" s="16" t="inlineStr"/>
-      <c r="Q17" s="16" t="inlineStr"/>
+      <c r="P17" s="17" t="inlineStr"/>
+      <c r="Q17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n">
+      <c r="A18" s="23" t="n">
         <v>46267</v>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>NewProv - Produtos para Laboratório Ltda</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>73636391000109</t>
         </is>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <v>160326</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Caldo BHI cx c/ 10 tubos</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>38221990</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="I18" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="J18" s="24" t="n">
         <v>246.51</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="24" t="n">
         <v>48.07</v>
       </c>
-      <c r="L18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="18" t="inlineStr">
+      <c r="L18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (reagente de laboratório) [NCM 38221990]</t>
         </is>
       </c>
-      <c r="P18" s="16" t="inlineStr"/>
-      <c r="Q18" s="16" t="inlineStr"/>
+      <c r="P18" s="17" t="inlineStr"/>
+      <c r="Q18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -28480,7 +28530,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
@@ -28500,11 +28550,11 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>Matéria-prima (químico orgânico) [NCM 29221100]</t>
-        </is>
-      </c>
-      <c r="P19" s="16" t="inlineStr"/>
-      <c r="Q19" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P19" s="17" t="inlineStr"/>
+      <c r="Q19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -28566,8 +28616,8 @@
           <t>Uso e consumo (peça de manutenção) [NCM 85334099]</t>
         </is>
       </c>
-      <c r="P20" s="16" t="inlineStr"/>
-      <c r="Q20" s="16" t="inlineStr"/>
+      <c r="P20" s="17" t="inlineStr"/>
+      <c r="Q20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -28629,8 +28679,8 @@
           <t>Uso e consumo (peça de manutenção) [NCM 85334099]</t>
         </is>
       </c>
-      <c r="P21" s="16" t="inlineStr"/>
-      <c r="Q21" s="16" t="inlineStr"/>
+      <c r="P21" s="17" t="inlineStr"/>
+      <c r="Q21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -28692,8 +28742,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P22" s="16" t="inlineStr"/>
-      <c r="Q22" s="16" t="inlineStr"/>
+      <c r="P22" s="17" t="inlineStr"/>
+      <c r="Q22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -28755,8 +28805,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P23" s="16" t="inlineStr"/>
-      <c r="Q23" s="16" t="inlineStr"/>
+      <c r="P23" s="17" t="inlineStr"/>
+      <c r="Q23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -28818,8 +28868,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P24" s="16" t="inlineStr"/>
-      <c r="Q24" s="16" t="inlineStr"/>
+      <c r="P24" s="17" t="inlineStr"/>
+      <c r="Q24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -28881,8 +28931,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P25" s="16" t="inlineStr"/>
-      <c r="Q25" s="16" t="inlineStr"/>
+      <c r="P25" s="17" t="inlineStr"/>
+      <c r="Q25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -28944,8 +28994,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P26" s="16" t="inlineStr"/>
-      <c r="Q26" s="16" t="inlineStr"/>
+      <c r="P26" s="17" t="inlineStr"/>
+      <c r="Q26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -29007,8 +29057,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P27" s="16" t="inlineStr"/>
-      <c r="Q27" s="16" t="inlineStr"/>
+      <c r="P27" s="17" t="inlineStr"/>
+      <c r="Q27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -29070,8 +29120,8 @@
           <t>Uso e consumo (luva/artigo plástico) [NCM 39262000]</t>
         </is>
       </c>
-      <c r="P28" s="16" t="inlineStr"/>
-      <c r="Q28" s="16" t="inlineStr"/>
+      <c r="P28" s="17" t="inlineStr"/>
+      <c r="Q28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -29133,8 +29183,8 @@
           <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
         </is>
       </c>
-      <c r="P29" s="16" t="inlineStr"/>
-      <c r="Q29" s="16" t="inlineStr"/>
+      <c r="P29" s="17" t="inlineStr"/>
+      <c r="Q29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -29173,7 +29223,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
@@ -29193,11 +29243,11 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>Uso e consumo (pincel) - mas CFOP 6949 (outras saídas: amostra/brinde/remessa) [CFOP 6949]</t>
-        </is>
-      </c>
-      <c r="P30" s="16" t="inlineStr"/>
-      <c r="Q30" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 2556]</t>
+        </is>
+      </c>
+      <c r="P30" s="17" t="inlineStr"/>
+      <c r="Q30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -29259,8 +29309,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P31" s="16" t="inlineStr"/>
-      <c r="Q31" s="16" t="inlineStr"/>
+      <c r="P31" s="17" t="inlineStr"/>
+      <c r="Q31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -29322,8 +29372,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P32" s="16" t="inlineStr"/>
-      <c r="Q32" s="16" t="inlineStr"/>
+      <c r="P32" s="17" t="inlineStr"/>
+      <c r="Q32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -29385,8 +29435,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P33" s="16" t="inlineStr"/>
-      <c r="Q33" s="16" t="inlineStr"/>
+      <c r="P33" s="17" t="inlineStr"/>
+      <c r="Q33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -29448,8 +29498,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
         </is>
       </c>
-      <c r="P34" s="16" t="inlineStr"/>
-      <c r="Q34" s="16" t="inlineStr"/>
+      <c r="P34" s="17" t="inlineStr"/>
+      <c r="Q34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -29508,11 +29558,11 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232110]</t>
-        </is>
-      </c>
-      <c r="P35" s="16" t="inlineStr"/>
-      <c r="Q35" s="16" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P35" s="17" t="inlineStr"/>
+      <c r="Q35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -29571,11 +29621,11 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
-        </is>
-      </c>
-      <c r="P36" s="16" t="inlineStr"/>
-      <c r="Q36" s="16" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P36" s="17" t="inlineStr"/>
+      <c r="Q36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -29634,11 +29684,11 @@
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
-        </is>
-      </c>
-      <c r="P37" s="16" t="inlineStr"/>
-      <c r="Q37" s="16" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P37" s="17" t="inlineStr"/>
+      <c r="Q37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -29697,11 +29747,11 @@
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39232190]</t>
-        </is>
-      </c>
-      <c r="P38" s="16" t="inlineStr"/>
-      <c r="Q38" s="16" t="inlineStr"/>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
+        </is>
+      </c>
+      <c r="P38" s="17" t="inlineStr"/>
+      <c r="Q38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -29763,8 +29813,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P39" s="16" t="inlineStr"/>
-      <c r="Q39" s="16" t="inlineStr"/>
+      <c r="P39" s="17" t="inlineStr"/>
+      <c r="Q39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -29826,8 +29876,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
         </is>
       </c>
-      <c r="P40" s="16" t="inlineStr"/>
-      <c r="Q40" s="16" t="inlineStr"/>
+      <c r="P40" s="17" t="inlineStr"/>
+      <c r="Q40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -29889,8 +29939,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 6924]</t>
         </is>
       </c>
-      <c r="P41" s="16" t="inlineStr"/>
-      <c r="Q41" s="16" t="inlineStr"/>
+      <c r="P41" s="17" t="inlineStr"/>
+      <c r="Q41" s="17" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -29949,11 +29999,11 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>Uso e consumo (calçado/EPI) [NCM 64039190]</t>
-        </is>
-      </c>
-      <c r="P42" s="16" t="inlineStr"/>
-      <c r="Q42" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P42" s="17" t="inlineStr"/>
+      <c r="Q42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -30012,11 +30062,11 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>Uso e consumo (calçado/EPI) [NCM 64019200]</t>
-        </is>
-      </c>
-      <c r="P43" s="16" t="inlineStr"/>
-      <c r="Q43" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P43" s="17" t="inlineStr"/>
+      <c r="Q43" s="17" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -30075,11 +30125,11 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>Uso e consumo (calçado/EPI) [NCM 64019990]</t>
-        </is>
-      </c>
-      <c r="P44" s="16" t="inlineStr"/>
-      <c r="Q44" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P44" s="17" t="inlineStr"/>
+      <c r="Q44" s="17" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -30138,11 +30188,11 @@
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>Uso e consumo (pano/TNT/EPI) [NCM 56031190]</t>
-        </is>
-      </c>
-      <c r="P45" s="16" t="inlineStr"/>
-      <c r="Q45" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P45" s="17" t="inlineStr"/>
+      <c r="Q45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -30204,8 +30254,8 @@
           <t>Remessa por conta e ordem de terceiros em venda à ordem (a venda vem em outra nota) [CFOP 5923]</t>
         </is>
       </c>
-      <c r="P46" s="16" t="inlineStr"/>
-      <c r="Q46" s="16" t="inlineStr"/>
+      <c r="P46" s="17" t="inlineStr"/>
+      <c r="Q46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -30267,8 +30317,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P47" s="16" t="inlineStr"/>
-      <c r="Q47" s="16" t="inlineStr"/>
+      <c r="P47" s="17" t="inlineStr"/>
+      <c r="Q47" s="17" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -30330,8 +30380,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P48" s="16" t="inlineStr"/>
-      <c r="Q48" s="16" t="inlineStr"/>
+      <c r="P48" s="17" t="inlineStr"/>
+      <c r="Q48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -30393,260 +30443,260 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P49" s="16" t="inlineStr"/>
-      <c r="Q49" s="16" t="inlineStr"/>
+      <c r="P49" s="17" t="inlineStr"/>
+      <c r="Q49" s="17" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n">
+      <c r="A50" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>ALTEC IND.COM.IMP.E EXP.LTDA.</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>67598292000187</t>
         </is>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="D50" s="19" t="n">
         <v>30338</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E50" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>TAMPA ALUM.20MM RV PRATA 320580</t>
         </is>
       </c>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="G50" s="19" t="inlineStr">
         <is>
           <t>83099000</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I50" s="18" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J50" s="23" t="n">
+      <c r="J50" s="24" t="n">
         <v>2506.56</v>
       </c>
-      <c r="K50" s="23" t="n">
+      <c r="K50" s="24" t="n">
         <v>300.79</v>
       </c>
-      <c r="L50" s="23" t="n">
+      <c r="L50" s="24" t="n">
         <v>300.79</v>
       </c>
-      <c r="M50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="18" t="inlineStr">
+      <c r="M50" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="19" t="inlineStr">
         <is>
           <t>Embalagem (tampa metálica) [NCM 83099000]</t>
         </is>
       </c>
-      <c r="P50" s="16" t="inlineStr"/>
-      <c r="Q50" s="16" t="inlineStr"/>
+      <c r="P50" s="17" t="inlineStr"/>
+      <c r="Q50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n">
+      <c r="A51" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>CARBON CIENTIFICA LTDA</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>44114040000130</t>
         </is>
       </c>
-      <c r="D51" s="18" t="n">
+      <c r="D51" s="19" t="n">
         <v>23127</v>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="18" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>MONOETANOLAMINA PA 1000ML - CARBON lote 11622</t>
         </is>
       </c>
-      <c r="G51" s="18" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>29221100</t>
         </is>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="I51" s="18" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="J51" s="23" t="n">
+      <c r="J51" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="23" t="n">
+      <c r="K51" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="L51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="18" t="inlineStr">
+      <c r="L51" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="19" t="inlineStr">
         <is>
           <t>Matéria-prima (químico orgânico) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P51" s="16" t="inlineStr"/>
-      <c r="Q51" s="16" t="inlineStr"/>
+      <c r="P51" s="17" t="inlineStr"/>
+      <c r="Q51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n">
+      <c r="A52" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>49547438000183</t>
         </is>
       </c>
-      <c r="D52" s="18" t="n">
+      <c r="D52" s="19" t="n">
         <v>6782</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="18" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>PANO ROLO MULTIUSO BRANCO 28x240 INOVEN</t>
         </is>
       </c>
-      <c r="G52" s="18" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>56039240</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
+      <c r="H52" s="19" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="I52" s="18" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J52" s="23" t="n">
+      <c r="J52" s="24" t="n">
         <v>799</v>
       </c>
-      <c r="K52" s="23" t="n">
+      <c r="K52" s="24" t="n">
         <v>95.88</v>
       </c>
-      <c r="L52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="18" t="inlineStr">
+      <c r="L52" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (pano/TNT/EPI) [NCM 56039240]</t>
         </is>
       </c>
-      <c r="P52" s="16" t="inlineStr"/>
-      <c r="Q52" s="16" t="inlineStr"/>
+      <c r="P52" s="17" t="inlineStr"/>
+      <c r="Q52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n">
+      <c r="A53" s="23" t="n">
         <v>46282</v>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>49547438000183</t>
         </is>
       </c>
-      <c r="D53" s="18" t="n">
+      <c r="D53" s="19" t="n">
         <v>6782</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E53" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="18" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>CABO ALUMINIO S ROSCA NOBRE 22MM X 1,40M</t>
         </is>
       </c>
-      <c r="G53" s="18" t="inlineStr">
+      <c r="G53" s="19" t="inlineStr">
         <is>
           <t>76082090</t>
         </is>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="H53" s="19" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="I53" s="18" t="inlineStr">
+      <c r="I53" s="19" t="inlineStr">
         <is>
           <t>1556</t>
         </is>
       </c>
-      <c r="J53" s="23" t="n">
+      <c r="J53" s="24" t="n">
         <v>34.9</v>
       </c>
-      <c r="K53" s="23" t="n">
+      <c r="K53" s="24" t="n">
         <v>6.81</v>
       </c>
-      <c r="L53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="18" t="inlineStr">
+      <c r="L53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="19" t="inlineStr">
         <is>
           <t>Uso e consumo (ferramenta/limpeza) [NCM 76082090]</t>
         </is>
       </c>
-      <c r="P53" s="16" t="inlineStr"/>
-      <c r="Q53" s="16" t="inlineStr"/>
+      <c r="P53" s="17" t="inlineStr"/>
+      <c r="Q53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -30708,8 +30758,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P54" s="16" t="inlineStr"/>
-      <c r="Q54" s="16" t="inlineStr"/>
+      <c r="P54" s="17" t="inlineStr"/>
+      <c r="Q54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -30771,8 +30821,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P55" s="16" t="inlineStr"/>
-      <c r="Q55" s="16" t="inlineStr"/>
+      <c r="P55" s="17" t="inlineStr"/>
+      <c r="Q55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -30831,11 +30881,11 @@
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>Uso e consumo (filme stretch - embalagem de transporte) [NCM 39201099]</t>
-        </is>
-      </c>
-      <c r="P56" s="16" t="inlineStr"/>
-      <c r="Q56" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P56" s="17" t="inlineStr"/>
+      <c r="Q56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -30874,7 +30924,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
@@ -30894,11 +30944,11 @@
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>Embalagem (frasco/tampa/pote plástico) [NCM 39239090]</t>
-        </is>
-      </c>
-      <c r="P57" s="16" t="inlineStr"/>
-      <c r="Q57" s="16" t="inlineStr"/>
+          <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
+        </is>
+      </c>
+      <c r="P57" s="17" t="inlineStr"/>
+      <c r="Q57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -30960,8 +31010,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P58" s="16" t="inlineStr"/>
-      <c r="Q58" s="16" t="inlineStr"/>
+      <c r="P58" s="17" t="inlineStr"/>
+      <c r="Q58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -31023,8 +31073,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P59" s="16" t="inlineStr"/>
-      <c r="Q59" s="16" t="inlineStr"/>
+      <c r="P59" s="17" t="inlineStr"/>
+      <c r="Q59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -31086,8 +31136,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P60" s="16" t="inlineStr"/>
-      <c r="Q60" s="16" t="inlineStr"/>
+      <c r="P60" s="17" t="inlineStr"/>
+      <c r="Q60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -31149,8 +31199,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P61" s="16" t="inlineStr"/>
-      <c r="Q61" s="16" t="inlineStr"/>
+      <c r="P61" s="17" t="inlineStr"/>
+      <c r="Q61" s="17" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -31212,71 +31262,71 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P62" s="16" t="inlineStr"/>
-      <c r="Q62" s="16" t="inlineStr"/>
+      <c r="P62" s="17" t="inlineStr"/>
+      <c r="Q62" s="17" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n">
+      <c r="A63" s="23" t="n">
         <v>46286</v>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>BISPHARMA EMBALAGENS LTDA</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>59610485000188</t>
         </is>
       </c>
-      <c r="D63" s="18" t="n">
+      <c r="D63" s="19" t="n">
         <v>117690</v>
       </c>
-      <c r="E63" s="18" t="n">
+      <c r="E63" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="18" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>COLORACAO HIDRATANTE PROFISSIONAL 60G Item.Ped.:       OP:119087 Cod.Externo:345566</t>
         </is>
       </c>
-      <c r="G63" s="18" t="inlineStr">
+      <c r="G63" s="19" t="inlineStr">
         <is>
           <t>76121000</t>
         </is>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I63" s="18" t="inlineStr">
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J63" s="23" t="n">
+      <c r="J63" s="24" t="n">
         <v>26515.5</v>
       </c>
-      <c r="K63" s="23" t="n">
+      <c r="K63" s="24" t="n">
         <v>2987.66</v>
       </c>
-      <c r="L63" s="23" t="n">
+      <c r="L63" s="24" t="n">
         <v>2987.66</v>
       </c>
-      <c r="M63" s="23" t="n">
+      <c r="M63" s="24" t="n">
         <v>1618.32</v>
       </c>
-      <c r="N63" s="23" t="n">
+      <c r="N63" s="24" t="n">
         <v>1618.32</v>
       </c>
-      <c r="O63" s="18" t="inlineStr">
+      <c r="O63" s="19" t="inlineStr">
         <is>
           <t>Embalagem (tubo de alumínio) [NCM 76121000]</t>
         </is>
       </c>
-      <c r="P63" s="16" t="inlineStr"/>
-      <c r="Q63" s="16" t="inlineStr"/>
+      <c r="P63" s="17" t="inlineStr"/>
+      <c r="Q63" s="17" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -31338,8 +31388,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P64" s="16" t="inlineStr"/>
-      <c r="Q64" s="16" t="inlineStr"/>
+      <c r="P64" s="17" t="inlineStr"/>
+      <c r="Q64" s="17" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -31401,8 +31451,8 @@
           <t>Remessa para industrialização por conta e ordem do adquirente (insumo do cliente) [CFOP 5924]</t>
         </is>
       </c>
-      <c r="P65" s="16" t="inlineStr"/>
-      <c r="Q65" s="16" t="inlineStr"/>
+      <c r="P65" s="17" t="inlineStr"/>
+      <c r="Q65" s="17" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -31464,134 +31514,134 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P66" s="16" t="inlineStr"/>
-      <c r="Q66" s="16" t="inlineStr"/>
+      <c r="P66" s="17" t="inlineStr"/>
+      <c r="Q66" s="17" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="n">
+      <c r="A67" s="7" t="n">
         <v>46287</v>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>MCASSAB COMERCIO E INDUSTRIA LTDA</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>49698723003110</t>
         </is>
       </c>
-      <c r="D67" s="18" t="n">
+      <c r="D67" s="5" t="n">
         <v>275966</v>
       </c>
-      <c r="E67" s="18" t="n">
+      <c r="E67" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="18" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>TRANSCUTOL CG - TB 25 KG</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>29094429</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I67" s="18" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J67" s="23" t="n">
+      <c r="J67" s="6" t="n">
         <v>3873.74</v>
       </c>
-      <c r="K67" s="23" t="n">
+      <c r="K67" s="6" t="n">
         <v>154.95</v>
       </c>
-      <c r="L67" s="23" t="n">
+      <c r="L67" s="6" t="n">
         <v>154.95</v>
       </c>
-      <c r="M67" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="18" t="inlineStr">
-        <is>
-          <t>Matéria-prima (químico orgânico) [NCM 29094429]</t>
-        </is>
-      </c>
-      <c r="P67" s="16" t="inlineStr"/>
-      <c r="Q67" s="16" t="inlineStr"/>
+      <c r="M67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 2911]</t>
+        </is>
+      </c>
+      <c r="P67" s="17" t="inlineStr"/>
+      <c r="Q67" s="17" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="n">
+      <c r="A68" s="7" t="n">
         <v>46288</v>
       </c>
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>HS INKLASER LTDA</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>18858535000163</t>
         </is>
       </c>
-      <c r="D68" s="18" t="n">
+      <c r="D68" s="5" t="n">
         <v>48241</v>
       </c>
-      <c r="E68" s="18" t="n">
+      <c r="E68" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="18" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>CARTUCHO BLK 13 PRETO</t>
         </is>
       </c>
-      <c r="G68" s="18" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>84439923</t>
         </is>
       </c>
-      <c r="H68" s="18" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>2556</t>
-        </is>
-      </c>
-      <c r="J68" s="23" t="n">
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n">
         <v>1074.5</v>
       </c>
-      <c r="K68" s="23" t="n">
+      <c r="K68" s="6" t="n">
         <v>125.11</v>
       </c>
-      <c r="L68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="23" t="n">
+      <c r="L68" s="6" t="n">
+        <v>125.11</v>
+      </c>
+      <c r="M68" s="6" t="n">
         <v>31.95</v>
       </c>
-      <c r="N68" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="18" t="inlineStr">
-        <is>
-          <t>Uso e consumo (suprimento de impressora) [NCM 84439923]</t>
-        </is>
-      </c>
-      <c r="P68" s="16" t="inlineStr"/>
-      <c r="Q68" s="16" t="inlineStr"/>
+      <c r="N68" s="6" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 2101]</t>
+        </is>
+      </c>
+      <c r="P68" s="17" t="inlineStr"/>
+      <c r="Q68" s="17" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -31653,8 +31703,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 6901]</t>
         </is>
       </c>
-      <c r="P69" s="16" t="inlineStr"/>
-      <c r="Q69" s="16" t="inlineStr"/>
+      <c r="P69" s="17" t="inlineStr"/>
+      <c r="Q69" s="17" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -31716,71 +31766,71 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P70" s="16" t="inlineStr"/>
-      <c r="Q70" s="16" t="inlineStr"/>
+      <c r="P70" s="17" t="inlineStr"/>
+      <c r="Q70" s="17" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="n">
+      <c r="A71" s="23" t="n">
         <v>46288</v>
       </c>
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>62514971000107</t>
         </is>
       </c>
-      <c r="D71" s="18" t="n">
+      <c r="D71" s="19" t="n">
         <v>141811</v>
       </c>
-      <c r="E71" s="18" t="n">
+      <c r="E71" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="18" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>CASHMERE - 204510</t>
         </is>
       </c>
-      <c r="G71" s="18" t="inlineStr">
+      <c r="G71" s="19" t="inlineStr">
         <is>
           <t>33029019</t>
         </is>
       </c>
-      <c r="H71" s="18" t="inlineStr">
+      <c r="H71" s="19" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I71" s="18" t="inlineStr">
+      <c r="I71" s="19" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J71" s="23" t="n">
+      <c r="J71" s="24" t="n">
         <v>4794.99</v>
       </c>
-      <c r="K71" s="23" t="n">
+      <c r="K71" s="24" t="n">
         <v>557.29</v>
       </c>
-      <c r="L71" s="23" t="n">
+      <c r="L71" s="24" t="n">
         <v>557.29</v>
       </c>
-      <c r="M71" s="23" t="n">
+      <c r="M71" s="24" t="n">
         <v>150.93</v>
       </c>
-      <c r="N71" s="23" t="n">
+      <c r="N71" s="24" t="n">
         <v>150.93</v>
       </c>
-      <c r="O71" s="18" t="inlineStr">
+      <c r="O71" s="19" t="inlineStr">
         <is>
           <t>Matéria-prima (fragrância/essência) [NCM 33029019]</t>
         </is>
       </c>
-      <c r="P71" s="16" t="inlineStr"/>
-      <c r="Q71" s="16" t="inlineStr"/>
+      <c r="P71" s="17" t="inlineStr"/>
+      <c r="Q71" s="17" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -31842,8 +31892,8 @@
           <t>Nota sem mercadoria (antecipação/financeira) [CFOP 6949 / NCM 00000000]</t>
         </is>
       </c>
-      <c r="P72" s="16" t="inlineStr"/>
-      <c r="Q72" s="16" t="inlineStr"/>
+      <c r="P72" s="17" t="inlineStr"/>
+      <c r="Q72" s="17" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -31905,71 +31955,71 @@
           <t>Nota sem mercadoria (antecipação/financeira) [CFOP 6949 / NCM 00000000]</t>
         </is>
       </c>
-      <c r="P73" s="16" t="inlineStr"/>
-      <c r="Q73" s="16" t="inlineStr"/>
+      <c r="P73" s="17" t="inlineStr"/>
+      <c r="Q73" s="17" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="n">
+      <c r="A74" s="23" t="n">
         <v>46294</v>
       </c>
-      <c r="B74" s="18" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>CHEMYUNION LTDA</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>58309709000820</t>
         </is>
       </c>
-      <c r="D74" s="18" t="n">
+      <c r="D74" s="19" t="n">
         <v>19303</v>
       </c>
-      <c r="E74" s="18" t="n">
+      <c r="E74" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="18" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>Uniox C (20,000)</t>
         </is>
       </c>
-      <c r="G74" s="18" t="inlineStr">
+      <c r="G74" s="19" t="inlineStr">
         <is>
           <t>34024200</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
+      <c r="H74" s="19" t="inlineStr">
         <is>
           <t>6101</t>
         </is>
       </c>
-      <c r="I74" s="18" t="inlineStr">
+      <c r="I74" s="19" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J74" s="23" t="n">
+      <c r="J74" s="24" t="n">
         <v>8747.379999999999</v>
       </c>
-      <c r="K74" s="23" t="n">
+      <c r="K74" s="24" t="n">
         <v>1016.64</v>
       </c>
-      <c r="L74" s="23" t="n">
+      <c r="L74" s="24" t="n">
         <v>1016.64</v>
       </c>
-      <c r="M74" s="23" t="n">
+      <c r="M74" s="24" t="n">
         <v>275.34</v>
       </c>
-      <c r="N74" s="23" t="n">
+      <c r="N74" s="24" t="n">
         <v>275.34</v>
       </c>
-      <c r="O74" s="18" t="inlineStr">
+      <c r="O74" s="19" t="inlineStr">
         <is>
           <t>Matéria-prima (tensoativo) [NCM 34024200]</t>
         </is>
       </c>
-      <c r="P74" s="16" t="inlineStr"/>
-      <c r="Q74" s="16" t="inlineStr"/>
+      <c r="P74" s="17" t="inlineStr"/>
+      <c r="Q74" s="17" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -32031,8 +32081,8 @@
           <t>Matéria-prima (óleos e gorduras) [NCM 15159090]</t>
         </is>
       </c>
-      <c r="P75" s="16" t="inlineStr"/>
-      <c r="Q75" s="16" t="inlineStr"/>
+      <c r="P75" s="17" t="inlineStr"/>
+      <c r="Q75" s="17" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -32094,8 +32144,8 @@
           <t>Embalagem (rótulo/etiqueta) - mas CFOP 5949 (outras saídas: amostra/brinde/remessa) [CFOP 5949]</t>
         </is>
       </c>
-      <c r="P76" s="16" t="inlineStr"/>
-      <c r="Q76" s="16" t="inlineStr"/>
+      <c r="P76" s="17" t="inlineStr"/>
+      <c r="Q76" s="17" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -32157,8 +32207,8 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 6901]</t>
         </is>
       </c>
-      <c r="P77" s="16" t="inlineStr"/>
-      <c r="Q77" s="16" t="inlineStr"/>
+      <c r="P77" s="17" t="inlineStr"/>
+      <c r="Q77" s="17" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -32220,71 +32270,71 @@
           <t>Remessa para industrialização por encomenda (insumo do cliente) [CFOP 5901]</t>
         </is>
       </c>
-      <c r="P78" s="16" t="inlineStr"/>
-      <c r="Q78" s="16" t="inlineStr"/>
+      <c r="P78" s="17" t="inlineStr"/>
+      <c r="Q78" s="17" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="22" t="n">
+      <c r="A79" s="7" t="n">
         <v>46294</v>
       </c>
-      <c r="B79" s="18" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>11340087000162</t>
         </is>
       </c>
-      <c r="D79" s="18" t="n">
+      <c r="D79" s="5" t="n">
         <v>42285</v>
       </c>
-      <c r="E79" s="18" t="n">
+      <c r="E79" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="18" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>KERANUTRI</t>
         </is>
       </c>
-      <c r="G79" s="18" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>38249989</t>
         </is>
       </c>
-      <c r="H79" s="18" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>6102</t>
         </is>
       </c>
-      <c r="I79" s="18" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>2101</t>
         </is>
       </c>
-      <c r="J79" s="23" t="n">
+      <c r="J79" s="6" t="n">
         <v>4278.84</v>
       </c>
-      <c r="K79" s="23" t="n">
+      <c r="K79" s="6" t="n">
         <v>160.71</v>
       </c>
-      <c r="L79" s="23" t="n">
+      <c r="L79" s="6" t="n">
         <v>160.71</v>
       </c>
-      <c r="M79" s="23" t="n">
+      <c r="M79" s="6" t="n">
         <v>261.15</v>
       </c>
-      <c r="N79" s="23" t="n">
+      <c r="N79" s="6" t="n">
         <v>261.15</v>
       </c>
-      <c r="O79" s="18" t="inlineStr">
-        <is>
-          <t>Matéria-prima (preparação química) [NCM 38249989]</t>
-        </is>
-      </c>
-      <c r="P79" s="16" t="inlineStr"/>
-      <c r="Q79" s="16" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
+          <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 2101]</t>
+        </is>
+      </c>
+      <c r="P79" s="17" t="inlineStr"/>
+      <c r="Q79" s="17" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -32346,8 +32396,8 @@
           <t>Insumo (classificação do SPED anterior) [SPED anterior: CFOP 1101]</t>
         </is>
       </c>
-      <c r="P80" s="16" t="inlineStr"/>
-      <c r="Q80" s="16" t="inlineStr"/>
+      <c r="P80" s="17" t="inlineStr"/>
+      <c r="Q80" s="17" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -32409,8 +32459,8 @@
           <t>Matéria-prima (químico inorgânico) [NCM 28321010]</t>
         </is>
       </c>
-      <c r="P81" s="16" t="inlineStr"/>
-      <c r="Q81" s="16" t="inlineStr"/>
+      <c r="P81" s="17" t="inlineStr"/>
+      <c r="Q81" s="17" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -32472,8 +32522,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P82" s="16" t="inlineStr"/>
-      <c r="Q82" s="16" t="inlineStr"/>
+      <c r="P82" s="17" t="inlineStr"/>
+      <c r="Q82" s="17" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -32535,8 +32585,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P83" s="16" t="inlineStr"/>
-      <c r="Q83" s="16" t="inlineStr"/>
+      <c r="P83" s="17" t="inlineStr"/>
+      <c r="Q83" s="17" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -32598,8 +32648,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P84" s="16" t="inlineStr"/>
-      <c r="Q84" s="16" t="inlineStr"/>
+      <c r="P84" s="17" t="inlineStr"/>
+      <c r="Q84" s="17" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -32661,8 +32711,8 @@
           <t>Uso e consumo (classificação do SPED anterior) [SPED anterior: CFOP 1556]</t>
         </is>
       </c>
-      <c r="P85" s="16" t="inlineStr"/>
-      <c r="Q85" s="16" t="inlineStr"/>
+      <c r="P85" s="17" t="inlineStr"/>
+      <c r="Q85" s="17" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -32866,12 +32916,12 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>NF 2564 (outras)</t>
+          <t>NF 2564 (uso)</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>Frete de compra de outras: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
+          <t>Frete de compra de uso: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
         </is>
       </c>
     </row>
@@ -33151,7 +33201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33215,1027 +33265,1019 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Contribuinte como consumidor final</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>GULA COSMETICOS LTDA (30415972000108, IE 9084324601)</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>16 nota(s) com indIEDest=9/indFinal=1 (NF 8966, 8967, 8968, 8969, 8978, 8980, 8981, 8982, 9003, 9006, 9009, 9011, 9013, 9014, 9018, 9019; CFOP 5101, 5102, 6102), sem ICMS-ST, ICMS cheio e IPI na base do ICMS; nas 1 nota(s) do mês como contribuinte houve ST de R$ 865.16. Se o cliente revende, a ST não foi retida - confirmar o cadastro/finalidade com o cliente</t>
         </is>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="25" t="n">
         <v>35221.15</v>
       </c>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr"/>
+      <c r="F5" s="17" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Destinatário x UF</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>GULA COSMETICOS LTDA (30415972000108)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Mesmo CNPJ com endereço em UFs diferentes no mês: PR: NF 8955, 8968, 8969, 8978, 8980, 8981, 8982, 9003, 9006, 9009, 9011, 9013, 9014, 9018, 9019; SP: NF 8966, 8967 - CFOP 6xxx e DIFAL dependem da UF; conferir o cadastro</t>
         </is>
       </c>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="16" t="inlineStr"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Industrialização x retorno</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>NF 8989/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 8993 (5902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <v>600</v>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
+      <c r="F7" s="17" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Industrialização x retorno</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>NF 8999/1 22/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9005 (6902). Retorno de insumo é 5902/6902; como está, R$ 948.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="25" t="n">
         <v>948</v>
       </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Industrialização x retorno</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>NF 9000/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Item 1 (FRASCO IMPRESSO OX 20V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9002 (5902). Retorno de insumo é 5902/6902; como está, R$ 556.50 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="25" t="n">
         <v>556.5</v>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr"/>
+      <c r="F9" s="17" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Industrialização x retorno</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>NF 9020/1 29/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 6124 de industrialização - o mesmo item foi devolvido também na NF 9026 (6902). Retorno de insumo é 5902/6902; como está, R$ 600.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="25" t="n">
         <v>600</v>
       </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr"/>
+      <c r="F10" s="17" t="inlineStr"/>
+      <c r="G10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Industrialização x retorno</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>NF 9021/1 29/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Item 1 (FRASCO IMPRESSO OX 30V 900ML MIX ETERNIZE) é insumo do cliente (CST 41, PIS 49) com CFOP 5124 de industrialização - o mesmo item foi devolvido também na NF 9024 (5902). Retorno de insumo é 5902/6902; como está, R$ 300.00 entra no acumulador de industrialização e na base do PIS/COFINS e do IRPJ/CSLL</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <v>300</v>
       </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr"/>
+      <c r="F11" s="17" t="inlineStr"/>
+      <c r="G11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>XML x Registro ERP</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>NF 8966/1 10/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>UF no XML SP x ERP PR</t>
         </is>
       </c>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>XML x Registro ERP</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>NF 8967/1 11/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>UF no XML SP x ERP PR</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="17" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>NF 8967/1 11/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>1 item(ns) com CFOP 6102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <v>370.33</v>
       </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr"/>
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>NF 8969/1 14/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <v>811.99</v>
       </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
+      <c r="F15" s="17" t="inlineStr"/>
+      <c r="G15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>NF 8978/1 16/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>9 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>1698.59</v>
       </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>19 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="24" t="n">
         <v>11620.79</v>
       </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
+      <c r="F17" s="17" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>NF 8981/1 17/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <v>1691.57</v>
       </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>NF 8982/1 18/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="24" t="n">
         <v>6901.45</v>
       </c>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
+      <c r="F19" s="17" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>NF 9003/1 23/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>4 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <v>156.77</v>
       </c>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="16" t="inlineStr"/>
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>NF 9006/1 23/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="24" t="n">
         <v>302.73</v>
       </c>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
+      <c r="F21" s="17" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>NF 9009/1 23/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>5 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="24" t="n">
         <v>1529.47</v>
       </c>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="16" t="inlineStr"/>
+      <c r="F22" s="17" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>NF 9013/1 28/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>2 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="24" t="n">
         <v>618.45</v>
       </c>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr"/>
+      <c r="G23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>NF 9014/1 28/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="24" t="n">
         <v>148.13</v>
       </c>
-      <c r="F24" s="16" t="inlineStr"/>
-      <c r="G24" s="16" t="inlineStr"/>
+      <c r="F24" s="17" t="inlineStr"/>
+      <c r="G24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>NF 9018/1 29/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>1 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="24" t="n">
         <v>139.49</v>
       </c>
-      <c r="F25" s="16" t="inlineStr"/>
-      <c r="G25" s="16" t="inlineStr"/>
+      <c r="F25" s="17" t="inlineStr"/>
+      <c r="G25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>CFOP revenda x produção</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>NF 9019/1 29/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>41 item(ns) com CFOP 5102 (mercadoria de terceiros) e IPI destacado - produto fabricado pela COSMETICI sai com 5101/6101 (ou 5401 com ST). Conferir CFOP e natureza "VENDA DE MERCADORIAS"</t>
         </is>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="24" t="n">
         <v>6020.39</v>
       </c>
-      <c r="F26" s="16" t="inlineStr"/>
-      <c r="G26" s="16" t="inlineStr"/>
+      <c r="F26" s="17" t="inlineStr"/>
+      <c r="G26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>CT-e sem crédito</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>CT-e 5597996 CAXIAS DO SUL - EXPRESSO SAO MIGUEL S/A</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Frete de compra de outras: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="n">
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Frete de compra de uso: sem crédito - o crédito do frete segue a mercadoria (uso e consumo/outras não creditam - LC 87/96 art. 33, I). ICMS R$ 36.18 não aproveitado</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="n">
         <v>36.18</v>
       </c>
-      <c r="F27" s="16" t="inlineStr"/>
-      <c r="G27" s="16" t="inlineStr"/>
+      <c r="F27" s="17" t="inlineStr"/>
+      <c r="G27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Diferimento 5124</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>5124 para PR com CST 00 (ICMS R$ 108.44) enquanto 35 itens 5124 do mês saíram com diferimento (CST 51). Conferir se o diferimento se aplica a este cliente</t>
         </is>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="24" t="n">
         <v>108.44</v>
       </c>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="16" t="inlineStr"/>
+      <c r="F28" s="17" t="inlineStr"/>
+      <c r="G28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>ALTEC IND.COM.IMP.E EXP.LTDA. (67598292000187)</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="17" t="inlineStr"/>
+      <c r="G29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>BISPHARMA EMBALAGENS LTDA (59610485000188)</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="16" t="inlineStr"/>
-      <c r="G30" s="16" t="inlineStr"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="17" t="inlineStr"/>
+      <c r="G30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>CHEMYUNION LTDA (58309709000820)</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="16" t="inlineStr"/>
-      <c r="G31" s="16" t="inlineStr"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="17" t="inlineStr"/>
+      <c r="G31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>DISTRIBUIDORA INDUSTRIAL PARANAENSE LTDA (04993269000177)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="16" t="inlineStr"/>
-      <c r="G32" s="16" t="inlineStr"/>
+      <c r="E32" s="24" t="n"/>
+      <c r="F32" s="17" t="inlineStr"/>
+      <c r="G32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>ELLOLIMP COMERCIO DE PRODUTOS DE HIGIENE E LIMPEZA LTDA (49547438000183)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>Lunaflexo Tecnologia Adesiva Eireli (06015875000143)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="16" t="inlineStr"/>
-      <c r="G33" s="16" t="inlineStr"/>
+      <c r="E33" s="24" t="n"/>
+      <c r="F33" s="17" t="inlineStr"/>
+      <c r="G33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>HS INKLASER LTDA (18858535000163)</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="16" t="inlineStr"/>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="17" t="inlineStr"/>
+      <c r="G34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>Fornecedor sem histórico</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>Lunaflexo Tecnologia Adesiva Eireli (06015875000143)</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
         </is>
       </c>
-      <c r="E35" s="23" t="n"/>
-      <c r="F35" s="16" t="inlineStr"/>
-      <c r="G35" s="16" t="inlineStr"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="17" t="inlineStr"/>
+      <c r="G35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>MCASSAB COMERCIO E INDUSTRIA LTDA (49698723003110)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="16" t="inlineStr"/>
-      <c r="G36" s="16" t="inlineStr"/>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Industrialização sem insumo</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 39.61) e IPI tributado</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>556.05</v>
+      </c>
+      <c r="F36" s="17" t="inlineStr"/>
+      <c r="G36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>NewProv - Produtos para Laboratório Ltda (73636391000109)</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="16" t="inlineStr"/>
-      <c r="G37" s="16" t="inlineStr"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Industrialização sem insumo</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>NF 8979/1 17/09 BARBARA KAROLAINY DE SOUZA SILVA</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 337.29) e IPI tributado</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>4098</v>
+      </c>
+      <c r="F37" s="17" t="inlineStr"/>
+      <c r="G37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA (11340087000162)</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="16" t="inlineStr"/>
-      <c r="G38" s="16" t="inlineStr"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>NFS-e retenções</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>NFS-e 18 01/09/2026 GENESIS ALIANCA</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Serviço 0401 (medicina) de R$ 728.14, prestador fora do Simples: reter IRRF 1.5% R$ 10.92 + PIS/COFINS/CSLL 4,65% R$ 33.86 = R$ 44.78; descontado na nota R$ 10.92 (diferença R$ 33.86). Conferir pagamento e DARF 1708/5952</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F38" s="17" t="inlineStr"/>
+      <c r="G38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>MÉDIA</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>Fornecedor sem histórico</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>SCENTEC ESSENCIAS E FRAGRANCIAS LTDA (62514971000107)</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Natureza definida pelo NCM (sem histórico no SPED) - confirmar insumo (1101/2101) x uso e consumo (1556/2556)</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="16" t="inlineStr"/>
-      <c r="G39" s="16" t="inlineStr"/>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Produto com tratamento diferente</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>NEUTRALIZANTE ALL NATURE - 500ML (cód. 51)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Mesmo produto vendido no mês com NCM/IPI diferentes: NCM 33059000 IPI CST 51 0% (NF 8966); NCM 33059000 IPI CST 50 14.3% (NF 8980) - conferir o cadastro do produto (IPI a menor se a alíquota correta for a maior)</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="17" t="inlineStr"/>
+      <c r="G39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>Industrialização sem insumo</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 39.61) e IPI tributado</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="n">
-        <v>556.05</v>
-      </c>
-      <c r="F40" s="16" t="inlineStr"/>
-      <c r="G40" s="16" t="inlineStr"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>VOLUMES: 4 CAIXAS</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="17" t="inlineStr"/>
+      <c r="G40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>Industrialização sem insumo</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>NF 8979/1 17/09 BARBARA KAROLAINY DE SOUZA SILVA</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 337.29) e IPI tributado</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="n">
-        <v>4098</v>
-      </c>
-      <c r="F41" s="16" t="inlineStr"/>
-      <c r="G41" s="16" t="inlineStr"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="17" t="inlineStr"/>
+      <c r="G41" s="17" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>NFS-e retenções</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>NFS-e 18 01/09/2026 GENESIS ALIANCA</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Serviço 0401 (medicina) de R$ 728.14, prestador fora do Simples: reter IRRF 1.5% R$ 10.92 + PIS/COFINS/CSLL 4,65% R$ 33.86 = R$ 44.78; descontado na nota R$ 10.92 (diferença R$ 33.86). Conferir pagamento e DARF 1708/5952</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="F42" s="16" t="inlineStr"/>
-      <c r="G42" s="16" t="inlineStr"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="17" t="inlineStr"/>
+      <c r="G42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>Produto com tratamento diferente</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>NEUTRALIZANTE ALL NATURE - 500ML (cód. 51)</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Mesmo produto vendido no mês com NCM/IPI diferentes: NCM 33059000 IPI CST 51 0% (NF 8966); NCM 33059000 IPI CST 50 14.3% (NF 8980) - conferir o cadastro do produto (IPI a menor se a alíquota correta for a maior)</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="n"/>
-      <c r="F43" s="16" t="inlineStr"/>
-      <c r="G43" s="16" t="inlineStr"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="17" t="inlineStr"/>
+      <c r="G43" s="17" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -34250,17 +34292,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>VOLUMES: 4 CAIXAS</t>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
         </is>
       </c>
       <c r="E44" s="6" t="n"/>
-      <c r="F44" s="16" t="inlineStr"/>
-      <c r="G44" s="16" t="inlineStr"/>
+      <c r="F44" s="17" t="inlineStr"/>
+      <c r="G44" s="17" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -34275,13 +34317,13 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr"/>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr"/>
       <c r="E45" s="6" t="n"/>
-      <c r="F45" s="16" t="inlineStr"/>
-      <c r="G45" s="16" t="inlineStr"/>
+      <c r="F45" s="17" t="inlineStr"/>
+      <c r="G45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -34296,17 +34338,17 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="inlineStr">
-        <is>
-          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
         </is>
       </c>
       <c r="E46" s="6" t="n"/>
-      <c r="F46" s="16" t="inlineStr"/>
-      <c r="G46" s="16" t="inlineStr"/>
+      <c r="F46" s="17" t="inlineStr"/>
+      <c r="G46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -34321,13 +34363,13 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="inlineStr"/>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr"/>
       <c r="E47" s="6" t="n"/>
-      <c r="F47" s="16" t="inlineStr"/>
-      <c r="G47" s="16" t="inlineStr"/>
+      <c r="F47" s="17" t="inlineStr"/>
+      <c r="G47" s="17" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -34342,17 +34384,17 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
         </is>
       </c>
       <c r="E48" s="6" t="n"/>
-      <c r="F48" s="16" t="inlineStr"/>
-      <c r="G48" s="16" t="inlineStr"/>
+      <c r="F48" s="17" t="inlineStr"/>
+      <c r="G48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -34367,13 +34409,13 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="inlineStr"/>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr"/>
       <c r="E49" s="6" t="n"/>
-      <c r="F49" s="16" t="inlineStr"/>
-      <c r="G49" s="16" t="inlineStr"/>
+      <c r="F49" s="17" t="inlineStr"/>
+      <c r="G49" s="17" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -34388,17 +34430,17 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="inlineStr">
-        <is>
-          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
         </is>
       </c>
       <c r="E50" s="6" t="n"/>
-      <c r="F50" s="16" t="inlineStr"/>
-      <c r="G50" s="16" t="inlineStr"/>
+      <c r="F50" s="17" t="inlineStr"/>
+      <c r="G50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -34413,13 +34455,13 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="inlineStr"/>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr"/>
       <c r="E51" s="6" t="n"/>
-      <c r="F51" s="16" t="inlineStr"/>
-      <c r="G51" s="16" t="inlineStr"/>
+      <c r="F51" s="17" t="inlineStr"/>
+      <c r="G51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -34434,17 +34476,17 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
         </is>
       </c>
       <c r="E52" s="6" t="n"/>
-      <c r="F52" s="16" t="inlineStr"/>
-      <c r="G52" s="16" t="inlineStr"/>
+      <c r="F52" s="17" t="inlineStr"/>
+      <c r="G52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -34459,13 +34501,13 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="inlineStr"/>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr"/>
       <c r="E53" s="6" t="n"/>
-      <c r="F53" s="16" t="inlineStr"/>
-      <c r="G53" s="16" t="inlineStr"/>
+      <c r="F53" s="17" t="inlineStr"/>
+      <c r="G53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -34480,17 +34522,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="inlineStr">
-        <is>
-          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>PESO BRUTO: 300,000</t>
         </is>
       </c>
       <c r="E54" s="6" t="n"/>
-      <c r="F54" s="16" t="inlineStr"/>
-      <c r="G54" s="16" t="inlineStr"/>
+      <c r="F54" s="17" t="inlineStr"/>
+      <c r="G54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -34505,13 +34547,13 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="inlineStr"/>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr"/>
       <c r="E55" s="6" t="n"/>
-      <c r="F55" s="16" t="inlineStr"/>
-      <c r="G55" s="16" t="inlineStr"/>
+      <c r="F55" s="17" t="inlineStr"/>
+      <c r="G55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -34526,17 +34568,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
         </is>
       </c>
       <c r="E56" s="6" t="n"/>
-      <c r="F56" s="16" t="inlineStr"/>
-      <c r="G56" s="16" t="inlineStr"/>
+      <c r="F56" s="17" t="inlineStr"/>
+      <c r="G56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -34551,13 +34593,13 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="inlineStr"/>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr"/>
       <c r="E57" s="6" t="n"/>
-      <c r="F57" s="16" t="inlineStr"/>
-      <c r="G57" s="16" t="inlineStr"/>
+      <c r="F57" s="17" t="inlineStr"/>
+      <c r="G57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -34572,17 +34614,17 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="inlineStr">
-        <is>
-          <t>PESO BRUTO: 300,000</t>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
+        <is>
+          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
         </is>
       </c>
       <c r="E58" s="6" t="n"/>
-      <c r="F58" s="16" t="inlineStr"/>
-      <c r="G58" s="16" t="inlineStr"/>
+      <c r="F58" s="17" t="inlineStr"/>
+      <c r="G58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -34597,13 +34639,13 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="inlineStr"/>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr"/>
       <c r="E59" s="6" t="n"/>
-      <c r="F59" s="16" t="inlineStr"/>
-      <c r="G59" s="16" t="inlineStr"/>
+      <c r="F59" s="17" t="inlineStr"/>
+      <c r="G59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -34613,22 +34655,22 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Carta de correção</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr">
-        <is>
-          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
       <c r="E60" s="6" t="n"/>
-      <c r="F60" s="16" t="inlineStr"/>
-      <c r="G60" s="16" t="inlineStr"/>
+      <c r="F60" s="17" t="inlineStr"/>
+      <c r="G60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -34638,18 +34680,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Carta de correção</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D61" s="20" t="inlineStr"/>
+          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
       <c r="E61" s="6" t="n"/>
-      <c r="F61" s="16" t="inlineStr"/>
-      <c r="G61" s="16" t="inlineStr"/>
+      <c r="F61" s="17" t="inlineStr"/>
+      <c r="G61" s="17" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -34659,22 +34705,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Carta de correção</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D62" s="20" t="inlineStr">
-        <is>
-          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
+          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
       <c r="E62" s="6" t="n"/>
-      <c r="F62" s="16" t="inlineStr"/>
-      <c r="G62" s="16" t="inlineStr"/>
+      <c r="F62" s="17" t="inlineStr"/>
+      <c r="G62" s="17" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -34684,18 +34730,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Carta de correção</t>
+          <t>Industrialização x retorno</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D63" s="20" t="inlineStr"/>
+          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - corrigir por CC-e</t>
+        </is>
+      </c>
       <c r="E63" s="6" t="n"/>
-      <c r="F63" s="16" t="inlineStr"/>
-      <c r="G63" s="16" t="inlineStr"/>
+      <c r="F63" s="17" t="inlineStr"/>
+      <c r="G63" s="17" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -34705,22 +34755,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>NFS-e retenções</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="inlineStr">
-        <is>
-          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+          <t>NFS-e 9227 01/09/2026 PLUS SANTE</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>Serviço 0421 (atendimento médico móvel) de R$ 342.30: confirmar se há retenção de IRRF/CSRF; descontado R$ 0.00</t>
         </is>
       </c>
       <c r="E64" s="6" t="n"/>
-      <c r="F64" s="16" t="inlineStr"/>
-      <c r="G64" s="16" t="inlineStr"/>
+      <c r="F64" s="17" t="inlineStr"/>
+      <c r="G64" s="17" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -34730,22 +34780,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>PIS/COFINS no XML</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
-        </is>
-      </c>
-      <c r="D65" s="20" t="inlineStr">
-        <is>
-          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+          <t>35 notas 5124/6124</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="inlineStr">
+        <is>
+          <t>O XML informa PIS/COFINS monofásico (CST 02, 2.2%) em R$ 115,057.65 de industrialização (PIS R$ 2,531.30 / COFINS R$ 11,850.96); a apuração usa 0,65%/3% sobre a industrialização, como nos DARFs pagos. Na encomenda de produto monofásico a alíquota concentrada é do encomendante (Lei 11.051/2004, art. 10) - corrigir o cadastro fiscal do ERP (CST 01) e confirmar o entendimento com a contadora</t>
         </is>
       </c>
       <c r="E65" s="6" t="n"/>
-      <c r="F65" s="16" t="inlineStr"/>
-      <c r="G65" s="16" t="inlineStr"/>
+      <c r="F65" s="17" t="inlineStr"/>
+      <c r="G65" s="17" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -34755,22 +34805,24 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>Remessa sem retorno</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D66" s="20" t="inlineStr">
-        <is>
-          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="16" t="inlineStr"/>
-      <c r="G66" s="16" t="inlineStr"/>
+          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>5700</v>
+      </c>
+      <c r="F66" s="17" t="inlineStr"/>
+      <c r="G66" s="17" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -34780,22 +34832,24 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Industrialização x retorno</t>
+          <t>Remessa sem retorno</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
-        </is>
-      </c>
-      <c r="D67" s="20" t="inlineStr">
-        <is>
-          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - corrigir por CC-e</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="16" t="inlineStr"/>
-      <c r="G67" s="16" t="inlineStr"/>
+          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F67" s="17" t="inlineStr"/>
+      <c r="G67" s="17" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -34805,22 +34859,24 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>NFS-e retenções</t>
+          <t>Remessa sem retorno</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>NFS-e 9227 01/09/2026 PLUS SANTE</t>
-        </is>
-      </c>
-      <c r="D68" s="20" t="inlineStr">
-        <is>
-          <t>Serviço 0421 (atendimento médico móvel) de R$ 342.30: confirmar se há retenção de IRRF/CSRF; descontado R$ 0.00</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="16" t="inlineStr"/>
-      <c r="G68" s="16" t="inlineStr"/>
+          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="F68" s="17" t="inlineStr"/>
+      <c r="G68" s="17" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -34830,22 +34886,24 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>PIS/COFINS no XML</t>
+          <t>Remessa sem retorno</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>35 notas 5124/6124</t>
-        </is>
-      </c>
-      <c r="D69" s="20" t="inlineStr">
-        <is>
-          <t>O XML informa PIS/COFINS monofásico (CST 02, 2.2%) em R$ 115,057.65 de industrialização (PIS R$ 2,531.30 / COFINS R$ 11,850.96); a apuração usa 0,65%/3% sobre a industrialização, como nos DARFs pagos. Na encomenda de produto monofásico a alíquota concentrada é do encomendante (Lei 11.051/2004, art. 10) - corrigir o cadastro fiscal do ERP (CST 01) e confirmar o entendimento com a contadora</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="16" t="inlineStr"/>
-      <c r="G69" s="16" t="inlineStr"/>
+          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1964</v>
+      </c>
+      <c r="F69" s="17" t="inlineStr"/>
+      <c r="G69" s="17" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -34860,19 +34918,19 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
-        </is>
-      </c>
-      <c r="D70" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5700</v>
-      </c>
-      <c r="F70" s="16" t="inlineStr"/>
-      <c r="G70" s="16" t="inlineStr"/>
+        <v>5670</v>
+      </c>
+      <c r="F70" s="17" t="inlineStr"/>
+      <c r="G70" s="17" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -34887,19 +34945,19 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D71" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="F71" s="16" t="inlineStr"/>
-      <c r="G71" s="16" t="inlineStr"/>
+        <v>2136</v>
+      </c>
+      <c r="F71" s="17" t="inlineStr"/>
+      <c r="G71" s="17" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -34914,19 +34972,19 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
+          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="F72" s="16" t="inlineStr"/>
-      <c r="G72" s="16" t="inlineStr"/>
+        <v>1112</v>
+      </c>
+      <c r="F72" s="17" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -34941,19 +34999,19 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D73" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
+          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1964</v>
-      </c>
-      <c r="F73" s="16" t="inlineStr"/>
-      <c r="G73" s="16" t="inlineStr"/>
+        <v>667.2</v>
+      </c>
+      <c r="F73" s="17" t="inlineStr"/>
+      <c r="G73" s="17" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -34968,19 +35026,19 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D74" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
+          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>5670</v>
-      </c>
-      <c r="F74" s="16" t="inlineStr"/>
-      <c r="G74" s="16" t="inlineStr"/>
+        <v>2420.01</v>
+      </c>
+      <c r="F74" s="17" t="inlineStr"/>
+      <c r="G74" s="17" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -34995,19 +35053,19 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D75" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
+          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>2136</v>
-      </c>
-      <c r="F75" s="16" t="inlineStr"/>
-      <c r="G75" s="16" t="inlineStr"/>
+        <v>1760</v>
+      </c>
+      <c r="F75" s="17" t="inlineStr"/>
+      <c r="G75" s="17" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -35022,19 +35080,19 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D76" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
+          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1112</v>
-      </c>
-      <c r="F76" s="16" t="inlineStr"/>
-      <c r="G76" s="16" t="inlineStr"/>
+        <v>1408.12</v>
+      </c>
+      <c r="F76" s="17" t="inlineStr"/>
+      <c r="G76" s="17" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -35049,19 +35107,19 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D77" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>667.2</v>
-      </c>
-      <c r="F77" s="16" t="inlineStr"/>
-      <c r="G77" s="16" t="inlineStr"/>
+        <v>2462.03</v>
+      </c>
+      <c r="F77" s="17" t="inlineStr"/>
+      <c r="G77" s="17" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -35071,136 +35129,28 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Remessa sem retorno</t>
+          <t>XML x Registro ERP</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D78" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
+          <t>30 notas de retorno 5902/6902</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>O Registro de Saídas do ERP não lista as notas de retorno simbólico (R$ 13,253.13); no livro/SPED elas entram (C100/C190 com CFOP 5902/6902, sem débito) - conferir no Domínio</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>2420.01</v>
-      </c>
-      <c r="F78" s="16" t="inlineStr"/>
-      <c r="G78" s="16" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Remessa sem retorno</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
-        </is>
-      </c>
-      <c r="D79" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="n">
-        <v>1760</v>
-      </c>
-      <c r="F79" s="16" t="inlineStr"/>
-      <c r="G79" s="16" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>Remessa sem retorno</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
-        </is>
-      </c>
-      <c r="D80" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="n">
-        <v>1408.12</v>
-      </c>
-      <c r="F80" s="16" t="inlineStr"/>
-      <c r="G80" s="16" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Remessa sem retorno</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
-        </is>
-      </c>
-      <c r="D81" s="20" t="inlineStr">
-        <is>
-          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>2462.03</v>
-      </c>
-      <c r="F81" s="16" t="inlineStr"/>
-      <c r="G81" s="16" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>XML x Registro ERP</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>30 notas de retorno 5902/6902</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>O Registro de Saídas do ERP não lista as notas de retorno simbólico (R$ 13,253.13); no livro/SPED elas entram (C100/C190 com CFOP 5902/6902, sem débito) - conferir no Domínio</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="n">
         <v>13253.13</v>
       </c>
-      <c r="F82" s="16" t="inlineStr"/>
-      <c r="G82" s="16" t="inlineStr"/>
+      <c r="F78" s="17" t="inlineStr"/>
+      <c r="G78" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -35228,14 +35178,14 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>1. Vendas de NCM fora da lista monofásica (Lei 10.147/2000, art. 1º, I, b) somam R$ 5,475.65 e estão na base de 2,2%/10,3%, como na planilha de 08/2026: 28470000 (R$ 5,475.65). Se forem tributadas a 0,65%/3%, a diferença é PIS R$ 84.87 e COFINS R$ 399.72 a menor. Confirmar com a contadora.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>2. Insumo de cliente emitido com CFOP 5124/6124 soma R$ 3,004.50 (aba Divergências, "Industrialização x retorno"). Está na base do PIS/COFINS (0,65%/3% = R$ 19.53 + R$ 90.13) e do IRPJ/CSLL. Se a contadora confirmar que é retorno em duplicidade, tirar da base e pedir ao cliente a regularização (CC-e do CFOP não altera valores - Ajuste SINIEF 01/07; senão, nota de entrada/anulação conforme RICMS/PR).</t>
         </is>

--- a/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>86.09</v>
+        <v>717.41</v>
       </c>
     </row>
     <row r="45">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>-0</v>
+        <v>-631.3200000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1175,202 +1175,216 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Ajuste a debito PR000080: ICMS recolhimento antecipado - importado a 4% (8% da base) - R$ 631.32 (NF 275966 MCASSAB COMERCIO E INDUSTRIA LTDA: 309.90; NF 42285 PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA: 321.42)</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Ajuste a credito PR020212: Crédito do ICMS antecipado (mesmo valor - saldo zero, como nos Demonstrativos 07 e 08/2026) - R$ 631.32 (NF 275966 MCASSAB COMERCIO E INDUSTRIA LTDA: 309.90; NF 42285 PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA: 321.42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>ICMS antecipado - entradas interestaduais a 4% (importado): 8% da base</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>NF 275966 MCASSAB COMERCIO E INDUSTRIA LTDA - TRANSCUTOL CG - TB 25 KG - base 3,873.74</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B55" s="6" t="n">
         <v>309.9</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>NF 42285 PROVITAL DO BRASIL COM. DE INSUMOS PARA COSMETICOS LTDA - KERANUTRI - base 4,017.69</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B56" s="6" t="n">
         <v>321.42</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Total antecipado (guia própria; no SPED: E111 PR000080 débito + PR020212 crédito, E113 por nota)</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Total antecipado - na apuração: débito PR000080 e crédito PR020212 de mesmo valor (saldo zero, sem guia própria, como em 07 e 08/2026); E113 por nota</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
         <v>631.3200000000001</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>ICMS-ST (substituto) por UF de destino</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>ICMS-ST retido - PR</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B60" s="6" t="n">
         <v>865.16</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>(-) ST de devoluções</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B61" s="6" t="n">
         <v>-0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>ICMS-ST a recolher PR</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B62" s="9" t="n">
         <v>865.16</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>IPI</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Débitos (saídas)</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B65" s="6" t="n">
         <v>4403.24</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>(-) Créditos (entradas)</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B66" s="6" t="n">
         <v>-2337.69</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>IPI a recolher (negativo = saldo credor)</t>
         </is>
       </c>
-      <c r="B65" s="9">
-        <f>B63+B64</f>
+      <c r="B67" s="9">
+        <f>B65+B66</f>
         <v/>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Conferência dos documentos</t>
         </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Notas de saída autorizadas</t>
-        </is>
-      </c>
-      <c r="B68" s="12" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Notas canceladas (saída e entrada)</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Números inutilizados</t>
+          <t>Notas de saída autorizadas</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Notas de entrada</t>
+          <t>Notas canceladas (saída e entrada)</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>CT-e tomados</t>
+          <t>Números inutilizados</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>Divergências ALTA</t>
-        </is>
-      </c>
-      <c r="B73" s="14" t="n">
-        <v>9</v>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Notas de entrada</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
+          <t>CT-e tomados</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>Divergências ALTA</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
           <t>Divergências (total)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n">
+      <c r="B76" s="12" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Observações para a contadora</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B77" s="12" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
+++ b/Cosmetici/Fiscal/2026-09/Apuracao_Fiscal_Cosmetici_09-2026.xlsx
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77">
@@ -2230,29 +2230,29 @@
       <c r="G21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Serviços</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>NFS-e tomadas: retenção de IRRF e PIS/COFINS/CSLL</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>1 MÉDIA, 1 BAIXA (aba Divergências)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>VERIFICAR</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>Lei 10.833/2003 art. 30 e 31 §3º (dispensa até R$ 10); RIR/2018 art. 714 e 716; IN SRF 459/2004</t>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>NFS-e tomadas: retenções extraídas do documento (sem recálculo)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>21 notas extraídas (aba NFS-e tomadas)</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>Escritura-se o que consta na nota</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr"/>
@@ -33215,7 +33215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 39.61) e IPI tributado</t>
+          <t>CFOP 5124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês - informativo (escriturado conforme o XML, CFOP 5124)</t>
         </is>
       </c>
       <c r="E36" s="24" t="n">
@@ -34140,7 +34140,7 @@
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês. Confirmar o insumo enviado pelo encomendante; se não houve, é venda (5101/6101): PIS/COFINS monofásico 2,2%/10,3% em vez de 0,65%/3% (diferença ~R$ 337.29) e IPI tributado</t>
+          <t>CFOP 6124 sem nota de remessa citada, sem retorno 5902/6902 e sem remessa recebida do cliente no mês - informativo (escriturado conforme o XML, CFOP 6124)</t>
         </is>
       </c>
       <c r="E37" s="24" t="n">
@@ -34157,47 +34157,45 @@
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>NFS-e retenções</t>
+          <t>Produto com tratamento diferente</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>NFS-e 18 01/09/2026 GENESIS ALIANCA</t>
+          <t>NEUTRALIZANTE ALL NATURE - 500ML (cód. 51)</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Serviço 0401 (medicina) de R$ 728.14, prestador fora do Simples: reter IRRF 1.5% R$ 10.92 + PIS/COFINS/CSLL 4,65% R$ 33.86 = R$ 44.78; descontado na nota R$ 10.92 (diferença R$ 33.86). Conferir pagamento e DARF 1708/5952</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="n">
-        <v>33.86</v>
-      </c>
+          <t>Mesmo produto vendido no mês com NCM/IPI diferentes: NCM 33059000 IPI CST 51 0% (NF 8966); NCM 33059000 IPI CST 50 14.3% (NF 8980) - conferir o cadastro do produto (IPI a menor se a alíquota correta for a maior)</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="n"/>
       <c r="F38" s="17" t="inlineStr"/>
       <c r="G38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>MÉDIA</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Produto com tratamento diferente</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>NEUTRALIZANTE ALL NATURE - 500ML (cód. 51)</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo produto vendido no mês com NCM/IPI diferentes: NCM 33059000 IPI CST 51 0% (NF 8966); NCM 33059000 IPI CST 50 14.3% (NF 8980) - conferir o cadastro do produto (IPI a menor se a alíquota correta for a maior)</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="n"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>BAIXA</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Carta de correção</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>VOLUMES: 4 CAIXAS</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="17" t="inlineStr"/>
       <c r="G39" s="17" t="inlineStr"/>
     </row>
@@ -34217,11 +34215,7 @@
           <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
         </is>
       </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>VOLUMES: 4 CAIXAS</t>
-        </is>
-      </c>
+      <c r="D40" s="21" t="inlineStr"/>
       <c r="E40" s="6" t="n"/>
       <c r="F40" s="17" t="inlineStr"/>
       <c r="G40" s="17" t="inlineStr"/>
@@ -34239,10 +34233,14 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>NF 786/1 02/09 YAHWEH PRINT BRASIL LTDA</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr"/>
+          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
+        </is>
+      </c>
       <c r="E41" s="6" t="n"/>
       <c r="F41" s="17" t="inlineStr"/>
       <c r="G41" s="17" t="inlineStr"/>
@@ -34263,11 +34261,7 @@
           <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>INDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NAS NFs 55874 de 21-09-2026</t>
-        </is>
-      </c>
+      <c r="D42" s="21" t="inlineStr"/>
       <c r="E42" s="6" t="n"/>
       <c r="F42" s="17" t="inlineStr"/>
       <c r="G42" s="17" t="inlineStr"/>
@@ -34285,10 +34279,14 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>NF 8992/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr"/>
+          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
+        </is>
+      </c>
       <c r="E43" s="6" t="n"/>
       <c r="F43" s="17" t="inlineStr"/>
       <c r="G43" s="17" t="inlineStr"/>
@@ -34309,11 +34307,7 @@
           <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE: 55874; INDUSTRIALIZACAO EFETUADA NA NFE 8992</t>
-        </is>
-      </c>
+      <c r="D44" s="21" t="inlineStr"/>
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="17" t="inlineStr"/>
       <c r="G44" s="17" t="inlineStr"/>
@@ -34331,10 +34325,14 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>NF 8993/1 21/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr"/>
+          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
+        </is>
+      </c>
       <c r="E45" s="6" t="n"/>
       <c r="F45" s="17" t="inlineStr"/>
       <c r="G45" s="17" t="inlineStr"/>
@@ -34355,11 +34353,7 @@
           <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 55913 de 23-09-2026</t>
-        </is>
-      </c>
+      <c r="D46" s="21" t="inlineStr"/>
       <c r="E46" s="6" t="n"/>
       <c r="F46" s="17" t="inlineStr"/>
       <c r="G46" s="17" t="inlineStr"/>
@@ -34377,10 +34371,14 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>NF 9001/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr"/>
+          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
+        </is>
+      </c>
       <c r="E47" s="6" t="n"/>
       <c r="F47" s="17" t="inlineStr"/>
       <c r="G47" s="17" t="inlineStr"/>
@@ -34401,11 +34399,7 @@
           <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
         </is>
       </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 55913 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9001</t>
-        </is>
-      </c>
+      <c r="D48" s="21" t="inlineStr"/>
       <c r="E48" s="6" t="n"/>
       <c r="F48" s="17" t="inlineStr"/>
       <c r="G48" s="17" t="inlineStr"/>
@@ -34423,10 +34417,14 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>NF 9002/1 22/09 MIX PERFUMARIA LTDA</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="inlineStr"/>
+          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
+        </is>
+      </c>
       <c r="E49" s="6" t="n"/>
       <c r="F49" s="17" t="inlineStr"/>
       <c r="G49" s="17" t="inlineStr"/>
@@ -34447,11 +34445,7 @@
           <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>INSDUSTRIALIZACAO EFETUADA COM INSUMOS ENVIADOS NA NFE 14838 de 23-09-2026|</t>
-        </is>
-      </c>
+      <c r="D50" s="21" t="inlineStr"/>
       <c r="E50" s="6" t="n"/>
       <c r="F50" s="17" t="inlineStr"/>
       <c r="G50" s="17" t="inlineStr"/>
@@ -34469,10 +34463,14 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>NF 9004/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D51" s="21" t="inlineStr"/>
+          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
+        </is>
+      </c>
       <c r="E51" s="6" t="n"/>
       <c r="F51" s="17" t="inlineStr"/>
       <c r="G51" s="17" t="inlineStr"/>
@@ -34493,11 +34491,7 @@
           <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D52" s="21" t="inlineStr">
-        <is>
-          <t>RETORNO SIMBOLICO DOS INSUMOS ENVIADOS NA NFE 14838 DE 23-09-26 ; INDUSTRIALIZACAO EFETUADA NA NFE 9004|</t>
-        </is>
-      </c>
+      <c r="D52" s="21" t="inlineStr"/>
       <c r="E52" s="6" t="n"/>
       <c r="F52" s="17" t="inlineStr"/>
       <c r="G52" s="17" t="inlineStr"/>
@@ -34515,10 +34509,14 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>NF 9005/1 23/09 MIX COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D53" s="21" t="inlineStr"/>
+          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t>PESO BRUTO: 300,000</t>
+        </is>
+      </c>
       <c r="E53" s="6" t="n"/>
       <c r="F53" s="17" t="inlineStr"/>
       <c r="G53" s="17" t="inlineStr"/>
@@ -34539,11 +34537,7 @@
           <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
         </is>
       </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>PESO BRUTO: 300,000</t>
-        </is>
-      </c>
+      <c r="D54" s="21" t="inlineStr"/>
       <c r="E54" s="6" t="n"/>
       <c r="F54" s="17" t="inlineStr"/>
       <c r="G54" s="17" t="inlineStr"/>
@@ -34561,10 +34555,14 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>NF 9016/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr"/>
+          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
+        </is>
+      </c>
       <c r="E55" s="6" t="n"/>
       <c r="F55" s="17" t="inlineStr"/>
       <c r="G55" s="17" t="inlineStr"/>
@@ -34585,11 +34583,7 @@
           <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
         </is>
       </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>QUANTIDADE CORRETA DE VOLUMES - 5 VOLUMES</t>
-        </is>
-      </c>
+      <c r="D56" s="21" t="inlineStr"/>
       <c r="E56" s="6" t="n"/>
       <c r="F56" s="17" t="inlineStr"/>
       <c r="G56" s="17" t="inlineStr"/>
@@ -34607,10 +34601,14 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>NF 9031/1 30/09 BB COSMETICOS - EIRELI</t>
-        </is>
-      </c>
-      <c r="D57" s="21" t="inlineStr"/>
+          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
+        </is>
+      </c>
       <c r="E57" s="6" t="n"/>
       <c r="F57" s="17" t="inlineStr"/>
       <c r="G57" s="17" t="inlineStr"/>
@@ -34631,11 +34629,7 @@
           <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
         </is>
       </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>Entregar:|Rua fl 9 qd 16 lt 01 casa 02, parque das flores |Cep: 74595-261|Goiania - go</t>
-        </is>
-      </c>
+      <c r="D58" s="21" t="inlineStr"/>
       <c r="E58" s="6" t="n"/>
       <c r="F58" s="17" t="inlineStr"/>
       <c r="G58" s="17" t="inlineStr"/>
@@ -34648,15 +34642,19 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Carta de correção</t>
+          <t>Grupo IPI</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>NF 9035/1 30/09 NUTRABELLA COMERCIAL DE COSMETICOS LTDA</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr"/>
+          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+        </is>
+      </c>
       <c r="E59" s="6" t="n"/>
       <c r="F59" s="17" t="inlineStr"/>
       <c r="G59" s="17" t="inlineStr"/>
@@ -34674,12 +34672,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>NF 8939/1 02/09 CANDIDO COMERCIO DE COSMETICOS - EIRELI</t>
+          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
         </is>
       </c>
       <c r="D60" s="21" t="inlineStr">
         <is>
-          <t>2 item(ns) de produto (CFOP 5124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
       <c r="E60" s="6" t="n"/>
@@ -34699,12 +34697,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>NF 8973/1 16/09 JORGE LEAO FERREIRA</t>
+          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>2 item(ns) de produto (CFOP 6124) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
         </is>
       </c>
       <c r="E61" s="6" t="n"/>
@@ -34719,17 +34717,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Grupo IPI</t>
+          <t>Industrialização x retorno</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>NF 8980/1 17/09 GULA COSMETICOS LTDA</t>
+          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
         </is>
       </c>
       <c r="D62" s="21" t="inlineStr">
         <is>
-          <t>3 item(ns) de produto (CFOP 5102) sem grupo de IPI (CST) - conferir o cadastro do produto no ERP</t>
+          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - informativo, escriturado como está no XML</t>
         </is>
       </c>
       <c r="E62" s="6" t="n"/>
@@ -34744,17 +34742,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Industrialização x retorno</t>
+          <t>PIS/COFINS no XML</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>NF 9017/1 28/09 LUAN PATRICK LORANDI 02301366057</t>
+          <t>35 notas 5124/6124</t>
         </is>
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>Informações complementares citam a industrialização na NF 9015, que é de FABIANO RODRIGUES AMARAL (CFOP 6101); a do cliente é a NF 9016 - corrigir por CC-e</t>
+          <t>O XML informa PIS/COFINS monofásico (CST 02, 2.2%) em R$ 115,057.65 de industrialização (PIS R$ 2,531.30 / COFINS R$ 11,850.96); a apuração usa 0,65%/3% sobre a industrialização, como nos DARFs pagos. Na encomenda de produto monofásico a alíquota concentrada é do encomendante (Lei 11.051/2004, art. 10) - informativo - a nota é escriturada como emitida</t>
         </is>
       </c>
       <c r="E63" s="6" t="n"/>
@@ -34769,20 +34767,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>NFS-e retenções</t>
+          <t>Remessa sem retorno</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>NFS-e 9227 01/09/2026 PLUS SANTE</t>
+          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
         </is>
       </c>
       <c r="D64" s="21" t="inlineStr">
         <is>
-          <t>Serviço 0421 (atendimento médico móvel) de R$ 342.30: confirmar se há retenção de IRRF/CSRF; descontado R$ 0.00</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="n"/>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>5700</v>
+      </c>
       <c r="F64" s="17" t="inlineStr"/>
       <c r="G64" s="17" t="inlineStr"/>
     </row>
@@ -34794,20 +34794,22 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>PIS/COFINS no XML</t>
+          <t>Remessa sem retorno</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>35 notas 5124/6124</t>
+          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>O XML informa PIS/COFINS monofásico (CST 02, 2.2%) em R$ 115,057.65 de industrialização (PIS R$ 2,531.30 / COFINS R$ 11,850.96); a apuração usa 0,65%/3% sobre a industrialização, como nos DARFs pagos. Na encomenda de produto monofásico a alíquota concentrada é do encomendante (Lei 11.051/2004, art. 10) - corrigir o cadastro fiscal do ERP (CST 01) e confirmar o entendimento com a contadora</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="n"/>
+          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>65</v>
+      </c>
       <c r="F65" s="17" t="inlineStr"/>
       <c r="G65" s="17" t="inlineStr"/>
     </row>
@@ -34824,16 +34826,16 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>NF 17187 18/09 ONIXSUL COSMETICOS</t>
+          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>5700</v>
+        <v>600</v>
       </c>
       <c r="F66" s="17" t="inlineStr"/>
       <c r="G66" s="17" t="inlineStr"/>
@@ -34851,16 +34853,16 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>NF 4551 21/09 BB COSMETICOS LTDA</t>
+          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5901 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>65</v>
+        <v>1964</v>
       </c>
       <c r="F67" s="17" t="inlineStr"/>
       <c r="G67" s="17" t="inlineStr"/>
@@ -34878,16 +34880,16 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>NF 5027 02/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE Z.R DISTRIBUIÇÃO, NF_e 4013</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>600</v>
+        <v>5670</v>
       </c>
       <c r="F68" s="17" t="inlineStr"/>
       <c r="G68" s="17" t="inlineStr"/>
@@ -34905,16 +34907,16 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>NF 5048 03/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE, VITTA HAIR, OS - 166471</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1964</v>
+        <v>2136</v>
       </c>
       <c r="F69" s="17" t="inlineStr"/>
       <c r="G69" s="17" t="inlineStr"/>
@@ -34932,16 +34934,16 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>NF 5080 09/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 165919 - ONIXSUL COSMETICOS</t>
+          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>5670</v>
+        <v>1112</v>
       </c>
       <c r="F70" s="17" t="inlineStr"/>
       <c r="G70" s="17" t="inlineStr"/>
@@ -34959,16 +34961,16 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>NF 5133 14/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 167120 - F.B. RIBEIRO E SILVA</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>2136</v>
+        <v>667.2</v>
       </c>
       <c r="F71" s="17" t="inlineStr"/>
       <c r="G71" s="17" t="inlineStr"/>
@@ -34986,16 +34988,16 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>NF 5162 15/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5923 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO CLIENTE F.B RIBEIRO, OS 167134</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1112</v>
+        <v>2420.01</v>
       </c>
       <c r="F72" s="17" t="inlineStr"/>
       <c r="G72" s="17" t="inlineStr"/>
@@ -35013,16 +35015,16 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>NF 5170 16/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>667.2</v>
+        <v>1760</v>
       </c>
       <c r="F73" s="17" t="inlineStr"/>
       <c r="G73" s="17" t="inlineStr"/>
@@ -35040,16 +35042,16 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>NF 5233 21/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE AO LCIENTE, BB COSMETICOS, OS- 167541</t>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>2420.01</v>
+        <v>1408.12</v>
       </c>
       <c r="F74" s="17" t="inlineStr"/>
       <c r="G74" s="17" t="inlineStr"/>
@@ -35067,16 +35069,16 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>NF 5235 21/09 JOSE DOMINGOS LINARES LTDA</t>
+          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
         </is>
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>Remessa 5924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle). REFERENTE A OS 166939 - Z.R. DISTRIBUIÇÃO E COMERCIO</t>
+          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>1760</v>
+        <v>2462.03</v>
       </c>
       <c r="F75" s="17" t="inlineStr"/>
       <c r="G75" s="17" t="inlineStr"/>
@@ -35089,82 +35091,28 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Remessa sem retorno</t>
+          <t>XML x Registro ERP</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>NF 8099 14/09 BEPUMP IMPORTACAO E EXPORTACAO LTDA</t>
+          <t>30 notas de retorno 5902/6902</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
+          <t>O Registro de Saídas do ERP não lista as notas de retorno simbólico (R$ 13,253.13); no livro/SPED elas entram (C100/C190 com CFOP 5902/6902, sem débito) - conferir no Domínio</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1408.12</v>
+        <v>13253.13</v>
       </c>
       <c r="F76" s="17" t="inlineStr"/>
       <c r="G76" s="17" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Remessa sem retorno</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>NF 8112 14/09 OUTLET PREMIUM PACK LTDA</t>
-        </is>
-      </c>
-      <c r="D77" s="21" t="inlineStr">
-        <is>
-          <t>Remessa 6924 recebida e ainda sem retorno citado no mês - fica no estoque de terceiros (controle)</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="n">
-        <v>2462.03</v>
-      </c>
-      <c r="F77" s="17" t="inlineStr"/>
-      <c r="G77" s="17" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>BAIXA</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>XML x Registro ERP</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>30 notas de retorno 5902/6902</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>O Registro de Saídas do ERP não lista as notas de retorno simbólico (R$ 13,253.13); no livro/SPED elas entram (C100/C190 com CFOP 5902/6902, sem débito) - conferir no Domínio</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>13253.13</v>
-      </c>
-      <c r="F78" s="17" t="inlineStr"/>
-      <c r="G78" s="17" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
@@ -35198,10 +35146,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>2. Insumo de cliente emitido com CFOP 5124/6124 soma R$ 3,004.50 (aba Divergências, "Industrialização x retorno"). Está na base do PIS/COFINS (0,65%/3% = R$ 19.53 + R$ 90.13) e do IRPJ/CSLL. Se a contadora confirmar que é retorno em duplicidade, tirar da base e pedir ao cliente a regularização (CC-e do CFOP não altera valores - Ajuste SINIEF 01/07; senão, nota de entrada/anulação conforme RICMS/PR).</t>
+          <t>2. Insumo de cliente emitido com CFOP 5124/6124 soma R$ 3,004.50 (aba Divergências, "Industrialização x retorno"). Está na base do PIS/COFINS (0,65%/3% = R$ 19.53 + R$ 90.13) e do IRPJ/CSLL. Informativo: a escrituração segue o XML (nada é alterado).</t>
         </is>
       </c>
     </row>
